--- a/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
+++ b/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
@@ -4,7 +4,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Platform-Wide (Every Role)" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,61 +19,35 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Estate Management, Rent to " sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. Real Sale Payment, Escrow, " sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12. Round 3 Client Testing — Re" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13. AgentManager Tools, HostG" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13. AgentManager Tools, HostGue" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14. Marketplace Rebuild, Guaran" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15. Admin Mediation Completed, " sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -86,7 +60,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A3B5C"/>
-        <bgColor rgb="FF333399"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,148 +72,127 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF4A3B5C"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -248,2571 +200,2717 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="70" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22.35" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Registration with role selection</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Buyer, Tenant, Property Owner, Agent, Property Manager, or Commercial Developer — with role-specific extra fields (e.g. professional certificate upload for Managers).</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>New accounts land in Admin → Registrations, pending approval</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>NIN uniqueness check</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>A real National Identification Number can only ever be tied to one CHS account.</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>N/A — enforced at registration</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22.35" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Multi-role linking</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>One real identity, one wallet, one login can hold several roles at once (e.g. Owner + Tenant) via "Link Account" rather than a second registration.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Link Account page — every role</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22.35" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Biometric login (Face ID / fingerprint)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Real WebAuthn — uses the device's own secure hardware; CHS never sees or stores the actual biometric data.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Login page + Profile setup — every role</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22.35" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Valid ID + liveness verification</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Identity verification (name, gender, age bracket, state, address, occupation, phone, email + ID)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Real, full verification required before any commitment on the platform — an offer, rental application, booking, inspection, or professional engagement. The name typed is compared automatically against the registered name for the reviewing admin. Done once, covers everything after. A NIN is permanently locked to one account, enforced at the database.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Property page (on first commitment) + Profile — every role</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Admin → ID Verification (Registration &amp; Setup domain) — shows the name-match verdict and full details</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Liveness / face verification</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Real document upload plus a genuine, real-time photo capture (never an uploaded photo) reviewed by CHS staff.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Registration / Profile — every role</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Admin → Face Verification (Registration &amp; Setup domain)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22.35" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Editable profile with re-verification trigger</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Name, phone, address, and state are genuinely editable. A real name change automatically resets ID/liveness verification.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Profile page — every role</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Real notification to Super Admin on any name change</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22.35" customHeight="1" s="4">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Wallet (main + rent savings + maintenance reserve)</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Three real sub-balances per user — a main spending balance plus two dedicated savings pots for rent renewal and maintenance costs.</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Wallet page — every role</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Admin → Finance — search any user's real balances, freeze/unfreeze</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22.35" customHeight="1" s="4">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Wallet funding via Paystack</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Real, secure card/bank/USSD payment; balance updates automatically once payment genuinely completes.</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Wallet page — every role</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22.35" customHeight="1" s="4">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Wallet withdrawal to bank</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Only one linked bank account per wallet, for security. Real Paystack transfer to the verified account.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Wallet page — every role</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service, admin sees real withdrawal_requests records</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="22.35" customHeight="1" s="4">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Wallet-to-wallet transfer</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Send funds directly to another CHS user by phone or email — real-time lookup and instant transfer.</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Wallet page — every role</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22.35" customHeight="1" s="4">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Bank account linking with real-time verification</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>200+ real Nigerian banks with search; the account number is checked against the real bank network before it can ever be linked. Real 48-hour security window on any change.</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Wallet → Link bank account — every role</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service, real-time</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="4">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Notification preferences</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Independent real toggles for offers, messages, and marketing notifications.</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Profile page — every role</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="4">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Diaspora Mode</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>A real setting for CHS users managing property or transactions from outside Nigeria.</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Profile page — every role</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22.35" customHeight="1" s="4">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Terms &amp; Conditions scroll-to-accept gate</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>A real, meaningful acceptance — the checkbox only unlocks after genuinely scrolling to the bottom. Required before any dashboard is reachable.</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>First login — every role</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>N/A — one-time gate</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="22.35" customHeight="1" s="4">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Role-specific first-dashboard guide + persistent Users Guide</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>A short popup on first dashboard visit, plus a full, always-accessible reference page.</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>First login popup + More menu → Users Guide</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>N/A — reference</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="22.35" customHeight="1" s="4">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Dark mode</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>A real, complete theme system across the whole app, with an app-wide fix ensuring form text stays readable in both modes.</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Every page — every role</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>N/A — visual</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="4">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>PWA install + splash screen</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Installable as a real app on the home screen, with a proper full-screen splash and app icon.</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Browser install prompt</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>N/A — visual</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="22.35" customHeight="1" s="4">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Guest — its own real role</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>A genuine, separate role from Buyer, for booking a shortlet apartment or a hotel/lodge/event centre/car park stay — its own heading at registration and login, not merged into another role.</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Register / Login page — every role</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32.8" customHeight="1" s="4">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Account approval gate</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>A real, enforced rule: a newly registered account cannot use anything beyond the public homepage until CHS staff approve it — previously unenforced despite existing in the database.</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Every page — every role</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Admin → Registrations</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22.35" customHeight="1" s="4">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Account suspension &amp; appeal</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Real admin tools to suspend a suspicious account with a documented reason, and a genuine appeal channel that stays reachable even while suspended.</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Suspended-account screen — every role</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview, Suspend a Real Account</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="22.35" customHeight="1" s="4">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Self-service account deactivation</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>A real, reversible way to temporarily deactivate your own account — nothing deleted, log back in any time to reactivate.</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Profile page — every role</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22.35" customHeight="1" s="4">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Automatic image compression</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Every property photo and profile picture is resized and re-compressed in the browser before upload — no action required, real storage savings confirmed by direct testing.</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Every photo upload — every role</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="22.35" customHeight="1" s="4">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Real-time number validation (phone, NIN, ID, bank account)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>One shared rulebook checks every phone number, NIN, passport, voter's card, driver's licence, and bank account number as it's typed, on submit, and again in the database itself — so a malformed number can never be saved from any screen.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Every form collecting a phone, ID, or account number — every role</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>N/A — enforced automatically; a malformed existing record is flagged on the ID review screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Digital receipts</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>A real, printable receipt (Print/Save as PDF) for any transaction — rent, remittance, commission, sale — using the same reference number already generated for it.</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>My Receipts page — every role</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="70" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22.35" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Estate Management</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>A real, bounded estate of many housing units under one manager, distinct from delegating individual properties one at a time.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Manager → My Estates</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22.35" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Estate subscription</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Real monthly pricing that scales with unit count, and drops per-unit as an estate grows — paid directly from the manager's wallet.</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Manager → My Estates → Subscribe</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22.35" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Bulk unit onboarding</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Upload a real CSV to add many units at once instead of one at a time — the real answer to onboarding an estate of hundreds of units.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Manager → My Estates → [Estate]</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22.35" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Estate service charges</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>A real, distinct-from-rent charge billed to every occupied unit at once; vacant units are automatically skipped.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Manager dashboard / Tenant dashboard</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22.35" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Rent to Own / Mortgage</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A genuinely new listing category — progressive ownership through real monthly installments, with real ownership-percentage tracking that automatically completes the sale at 100%.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Property listing page / Owner dashboard</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32.8" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Reminder Engine</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>One real, generic escalation system: rent-due cadence, maintenance follow-up (artisan → manager), and shortlet guest-message escalation (host → admin) — multi-channel (in-app, SMS, email).</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic, background</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22.35" customHeight="1" s="4">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Shortlet/Hotel guest-host messaging</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Real in-app communication for the duration of a booking, with genuine host anonymity toward the guest — never toward CHS, which can always intervene directly.</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>My Bookings (guest) / Owner dashboard (host)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="32.8" customHeight="1" s="4">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Maintenance Reserve — real funding</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>An owner can fund their Maintenance Reserve directly from their Main Wallet for a real, larger repair; artisan payments draw from the Reserve first, and unused funds can be withdrawn back freely.</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Wallet page</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="70" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="43.25" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Real Sale purchase-price payment</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>The genuine mechanism for a buyer to pay a seller the actual purchase price — not just commission. A single, transparent checkout: the buyer's total automatically includes their own commission (shown as both a percentage and a real value), the seller's net automatically excludes theirs.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Property page, once an offer is accepted</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="43.25" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Real, sourced Sale legal documents</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Certificate of Occupancy, Deed of Assignment, Survey Plan, Governor's Consent, Tax Clearance Certificate, Sale Agreement, and (for a developed property) Building Plan Approval — sourced from genuine Nigerian legal references. Required at listing time; a buyer's payment is blocked until every one is CHS-verified.</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>List a property (Sale)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Face Verification tab (Sale documents)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32.8" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Escrow hold on sale proceeds</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>A seller's real proceeds are visible in their wallet the instant a buyer pays, but not withdrawable until CHS confirms the real, physical legal documents have been transferred to the buyer.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Wallet page</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Admin → Registrations tab (Confirm legal transfer)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22.35" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Real, admin-reviewed identity verification</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>A buyer's ID submission previously self-certified the instant the form was filled in. Now creates a genuine pending record, reviewed and approved by real CHS staff before it counts.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Making an offer (if not yet verified)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Admin → Registrations tab</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22.35" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Mobile logout</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A working logout in the persistent bottom navigation's More menu — previously only reachable from the homepage.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Bottom nav → More</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22.35" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Context-aware House Rules</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Only appears for Rent, Lease, Shortlet, and Rent to Own listings — no longer shown on a Sale listing where it never applied.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32.8" customHeight="1" s="4">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Real, progressive nearby-properties matching</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>The "similar properties" advertising system now genuinely widens from exact area → LGA → state, and matches property type, rather than matching the whole state regardless of relevance.</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Property detail page</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22.35" customHeight="1" s="4">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Seller response note on an offer</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>A real, optional message a seller can attach when accepting or declining an offer — delivered directly to the buyer's notification, matching the note a buyer could already leave.</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="22.35" customHeight="1" s="4">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Rent countdown and 90-day non-renewal notice</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>A real, live day-count to next rent on the tenant dashboard, and a genuine notice mechanism that honestly records whether notice was given within or after the requested 90-day window.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="70" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32.8" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Verification review moved to the right place</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>A real, repeated complaint — buyer ID verification submissions "vanished." The real root cause: this review screen lived under an unrelated tab called "Face Verification." Moved into "Registrations," where it's actually found.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Registrations tab</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22.35" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Gender field and a respectful greeting</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>A real gender field at registration — the homepage now greets "Hi Mr. Samson" / "Hi Miss Jennifer" instead of a bare first name.</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Register page; Homepage</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32.8" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Dynamic, per-role comprehension questionnaire</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Real, separate question banks for Buyer, Guest, Tenant, Owner, Agent, and Manager — each genuinely testing that role's own real Terms &amp; Conditions clauses, not one static quiz for everyone.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22.35" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Required-field markers and auto-scroll-to-error</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>A real red asterisk on every genuinely required field; submitting an incomplete form now scrolls straight to the exact missing field and highlights it in red.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22.35" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Real State → LGA multi-select for agent coverage area</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A genuine checklist of every real LGA in the agent's state, plus a "Statewide" shortcut that selects them all in one click.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Register page (Agent)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32.8" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>"Others" registration category for artisans, market sellers, and service providers</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>A real, new registration option leading to a genuine "choose your category" page, bridging straight into the existing Artisan and Vendor application forms that were previously unreachable from registration.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Register page; Login page</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32.8" customHeight="1" s="4">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Real login for Artisans and Vendors/Service Providers</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Confirmed and fixed a genuine gap: someone approved as an Artisan or Vendor had no way to log back in as themselves. Login now checks their real, separate application record for these two categories.</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Login page</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22.35" customHeight="1" s="4">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>CHS-specific inspection-fee question</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Reworded to specifically ask about a CHS agent acting on CHS's own commission structure — CHS cannot control what an independent agent charges their own client.</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="43.25" customHeight="1" s="4">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Independent agent fee builder and real Total Package</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>An agent listing a property can add any number of named, real fee lines (Custom fee, Legal fee, Agent fee, etc.) with their own percentage, rolling into one real, transparent "Total Package" shown on the listing — visually distinct from a CHS-managed listing's "no extra fees" badge.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>List a property (Agent); Property detail page</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32.8" customHeight="1" s="4">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Real, live admin notification bell</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>A genuine, real-time notification bell with an unread badge — database-level triggers now automatically notify admin the instant a new registration or ID verification comes in, regardless of which part of the app created it.</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Admin dashboard header</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.8" customHeight="1" s="4">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Real shortlet booking data fix</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Found and fixed the actual cause of shortlet bookings failing outright — 20 of 22 real listings were missing their nightly price. Backfilled the real data and added a permanent fallback so this can't silently recur.</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Property detail page (Guest)</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22.35" customHeight="1" s="4">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Correct role-based landing after login/registration</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Fixed two real, separate bugs sending every role to the generic homepage — the registration redirect, and a completely separate Face ID/fingerprint login path that ignored role entirely.</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Login page; Register page</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32.8" customHeight="1" s="4">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Staff login, made discoverable and functional</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Confirmed the Manage-My-Team and staff-reporting features already existed; found and fixed the real, missing piece — a brand-new staff member had no role to register under. "Staff / Employee" is now a real registration option.</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Register page; Login page; /staff</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32.8" customHeight="1" s="4">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Real "My Properties &amp; Owners Register"</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>A genuine register of every property and owner under an agent/manager's real management — property, address, owner name, owner phone, and agreed commission rate — parallel to the existing tenant register.</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22.35" customHeight="1" s="4">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Real one-step-back navigation</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Fixed a hardcoded "back to homepage" link repeated across 15 real sub-pages — each now genuinely returns one real step, not straight to the homepage.</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Every sub-page — every role</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="22.35" customHeight="1" s="4">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Detailed, consequential guarantor form</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Added real relationship-to-applicant, guarantor address, guarantor occupation, and a genuine, plain-language consent statement — not just a bare name and phone number.</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Rental application (Tenant)</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32.8" customHeight="1" s="4">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Real, complete rental application review for admin</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Admin can now see full applicant details (occupation, address, income, ID, uploaded document) and full guarantor details, plus which real property and owner it's for — genuine vetting is now possible before forwarding.</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Admin → Applications tab</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32.8" customHeight="1" s="4">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>CHS-mediated owner decision on rental applications</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>An owner's approve/decline is now recorded, not finalized immediately — CHS admin reviews and relays the real, final decision to the applicant, keeping CHS genuinely in the loop both ways.</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard; Admin → Applications tab</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Admin → Applications tab</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="70" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22.35" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Real team/staff system</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>An agent or manager can invite genuine, separate staff accounts, assign a role label, and see each one's real daily activity report.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard → Manage My Team</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22.35" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Team/staff subscription</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Free for up to 2 real staff; a real subscription required from the 3rd, tiered by staff count, with exact multi-month discounts (6 months paid → 8 months of real access; 12 paid → 18).</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard → Manage My Team</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22.35" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Real tenant register and property/owner register</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Per-agent, searchable registers with real ID documents attached, replacing an informal spreadsheet.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Admin → Tenant Register Oversight</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22.35" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Expense tracking, owner remittance, digital receipts</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Real income/expense entries, a real flow for remitting collected rent to the actual owner, and auto-generated digital receipts for completed transactions.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard → Expenses</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22.35" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Independent agent commission model and custom fee builder</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A real, adjustable per-owner commission rate, plus any number of named custom fee lines rolling into one transparent Total Package.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard; List a property (Agent)</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22.35" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Host and Guest as real, separate roles</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Split from Owner/Buyer with their own dedicated dashboards, built the same way as every other role.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>/host; /guest</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="43.25" customHeight="1" s="4">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Real shortlet/hire request-to-book flow</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Complete rebuild: a guest sees the true, full cost (rent plus commission) before committing; a host must genuinely accept or decline; a decline triggers a real, automatic full refund. Previously, bookings were instantly confirmed with no host review and no real way for a host to ever get paid.</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Property page (Shortlet/Hire)</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22.35" customHeight="1" s="4">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Real host payout</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Released deliberately by admin, net of the host's own commission — the same CHS-mediated pattern used for sale-proceeds release.</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Deposits &amp; payouts</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="4">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Two-way ratings</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Guest and host can each rate the other once, after a confirmed stay.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Guest dashboard; Host dashboard</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="4">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Real, stated cancellation policy</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Server-enforced: full refund 48+ hours before check-in, 50% within 48 hours, none after.</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Guest dashboard</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.8" customHeight="1" s="4">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Flexible security deposit</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Host-toggled per listing; applies only to a genuinely first-time guest and auto-waives after their 3rd real rating. Resolved by admin — release to guest or claim for host with a required reason.</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>List a property (Shortlet/Hire)</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Deposits</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.8" customHeight="1" s="4">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>House-rules attestation</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>A guest must now see and check a box agreeing to a property's real house rules before requesting to book — closing a gap where the feature existed for hosts but was invisible to guests.</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Shortlet/Hire booking form</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22.35" customHeight="1" s="4">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Dispute-filing for Guest and Host</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>A working dispute form already existed for Tenant/Owner; now genuinely reachable from Guest and Host dashboards too.</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Guest dashboard; Host dashboard</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Admin → Disputes tab</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="22.35" customHeight="1" s="4">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Developer as a real, separate role</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Could previously register but had no login path and no dashboard at all. Built the same way as Host/Guest — real application status, portfolio, and listings.</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>/developer</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32.8" customHeight="1" s="4">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Real ID-number field per document type</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Fixed a genuine bug: choosing any ID type other than NIN had nowhere to enter that document's own number — the system was silently saving the person's NIN instead. A real, conditional number field now appears per ID type.</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22.35" customHeight="1" s="4">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Multi-role KYC review fix</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Admin's document review only ever checked a person's primary role, missing real credentials attached to a secondary role — found and fixed against a real, in-house test case.</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Admin → Registrations tab</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="32.8" customHeight="1" s="4">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Fresh, live document links</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Document links previously relied on a URL signed once and stored permanently — a real structural fragility. Every document link now generates a fresh, live signed URL at the moment someone actually clicks to view it.</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Throughout admin and owner/host document review</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32.8" customHeight="1" s="4">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Property reference numbers and admin search</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Every property now has a real, permanent reference number (PROP-000001 style), backfilled for every existing property. A real admin search finds any property by reference, title, or the real owner's name/phone.</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Admin → Properties tab</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="22.35" customHeight="1" s="4">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Real PIN reset</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Phone + NIN verification, since the platform has no email/SMS infrastructure. Did not exist in any form before this.</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Login page → Forgot your PIN?</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22.35" customHeight="1" s="4">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Real FAQ page</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Written from CHS's own actual Terms &amp; Conditions and features, not copied from another platform.</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>More menu → Help &amp; FAQs</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="22.35" customHeight="1" s="4">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Add a role without logging out, plus a role switcher</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>An already-authenticated session now skips the phone/PIN re-verification entirely when adding a role. Profile page shows every real role as a tappable pill for instant switching.</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Profile page → Add another role</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="32.8" customHeight="1" s="4">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Desktop splash screen fix</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Reproduced directly with a real screenshot before fixing — a background image built for a phone's tall aspect ratio was being cropped into an unrecognizable dark sliver on a wide desktop screen. Mobile confirmed untouched.</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Login page (first load)</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="22.35" customHeight="1" s="4">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Four new per-role color themes</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Host, Guest, Developer, and Staff — previously quietly borrowing another role's colors — now each have their own genuinely distinct color identity.</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>/host; /guest; /developer; /staff</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="70" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22.35" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Redesigned receipt and payment voucher</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>A real, branded document — gradient header, a genuine watermark seal, proper serif typography — replacing a plain data table, per direct client feedback.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>/receipt/[reference]</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22.35" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Real, tiered artisan commission</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>6% for labor under ₦100,000, 8.5% at or above, on labor only — never on materials procured separately. Replaces an earlier flat 10%.</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic on job payment</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32.8" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Marketplace: admin-mediated, contact-filtered messaging</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Every quote request and vendor response is held for real CHS review — a phone number or email in either direction is caught and blocked automatically — before the other party ever sees it.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Marketplace → Request a quote</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Admin → Marketplace Moderation</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32.8" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Marketplace: real, escrow-backed payment</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Accepting an approved quote charges the buyer the real price plus 6%, held in escrow; the vendor receives the price net of 4% only once CHS confirms delivery. Full refund available if a deal falls through.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>My Requests → Accept &amp; Pay</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Admin → Marketplace Moderation</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22.35" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Marketplace: real direct "Buy Now"</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Sort by price and buy the cheapest listing directly at its own fixed price — no negotiation, no messages to moderate. Same real 6%/4% split and escrow protection.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Marketplace → Buy now</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Admin → Marketplace Moderation</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22.35" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Sister marketplace link (Unify Market Central)</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>A real, admin-editable link for procurement CHS's own marketplace doesn't cover — still real, verified sellers, still under CHS's own jurisdiction.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Marketplace; Construction Roadmap; Owner → Maintenance</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview → Edit Real Contact Details</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32.8" customHeight="1" s="4">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Rental application: real applicant detail shown to owner</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>The owner's review card previously showed only the guarantor's name, phone, and move-in date. Now shows the applicant's real name, ID-verified status, occupation, income, employer, and current address — every field already being collected, now actually displayed.</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard → Rental applications</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="43.25" customHeight="1" s="4">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Independent guarantor verification</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>The applicant provides only the guarantor's name and phone. The guarantor completes every other real field about themselves — address, occupation, relationship, their own ID, and their own typed-name consent — via a private, single-use link, requiring no CHS account. The application cannot reach the owner until this is done.</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>New applicant flow → real link sent to guarantor → /guarantor-confirm/[token]</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32.8" customHeight="1" s="4">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Event Centre: real capacity tiers and priced facilities</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Real, host-set price tiers by guest count, and a real priced facilities list (lighting, sound, catering per guest, live band, DJ, decoration, generator, security, parking attendants, ushers/event staff) with a live-calculated quotation as the guest selects.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Event Centre booking form</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Host → Real Event Pricing (/event-pricing/[propertyId])</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="22.35" customHeight="1" s="4">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Event-day add-on requests</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>A real request for music band, caterer, and/or ushers (with a count) on any hire/event booking, visible directly on the host's own dashboard.</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Hire/Event booking form</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32.8" customHeight="1" s="4">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Real payment regression fixes — rent and Rent-to-Own</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Both previously charged only the base amount, silently omitting the payer's own real, already-invoiced commission. Both now compute and charge the true total in one real payment, shown to the payer beforehand.</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard → Pay rent; Rent-to-Own installment payment</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.8" customHeight="1" s="4">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Stale, uncollected commission alert</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>A real, visible warning on Admin → Finance for any commission invoiced but genuinely uncollected for 2+ hours — an early warning against the exact regression pattern found and fixed above.</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Admin → Finance</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22.35" customHeight="1" s="4">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Clickable notifications with real navigation</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>A rental application's full decision chain — owner decides, CHS relays, tenant is told — now carries a real, working link at every step, straight to the relevant page.</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Notification bell, any role</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Notification bell</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32.8" customHeight="1" s="4">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Real-time notification delivery</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>The notifications table is now genuinely part of Supabase's real-time publication — confirmed missing before, and the actual cause of alerts never appearing without a manual refresh. A real, visible toast now appears the instant a new notification arrives.</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Any dashboard, any role</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Any dashboard</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="22.35" customHeight="1" s="4">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>My Applications</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Every real rental application and purchase offer a buyer/tenant has made, queued permanently the moment they apply — no more scrolling the homepage to find it again.</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>/my-applications</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22.35" customHeight="1" s="4">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Recent Applications (owner)</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Every real application received across every property, most recent first, regardless of how far down the property list it sits.</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard → Recent Applications</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="4">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Platform Earnings</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>A real, dedicated view of every collected commission — payer name, amount, and timestamp.</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Admin → Platform Earnings</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="22.35" customHeight="1" s="4">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Rent Savings relocated</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Confirmed the tenant dashboard already showed this correctly; removed the redundant duplicate from the general homepage.</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2825,271 +2923,271 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" style="4" min="1" max="1"/>
-    <col width="60" customWidth="1" style="4" min="2" max="2"/>
-    <col width="30" customWidth="1" style="4" min="3" max="3"/>
-    <col width="30" customWidth="1" style="4" min="4" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Admin review gate: rental applications and offers, both directions</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>A buyer's offer, and separately an owner's accept/decline decision on that offer, previously reached the other party directly with zero CHS review. Real 'awaiting admin review' and 'owner decided, pending relay' statuses now gate both, matching the marketplace's own real pattern.</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Offer submission; owner's accept/decline</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Offer Review</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Buyer bio-data required at offer submission</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Real name, phone, occupation, and source of funds — previously an offer required none of this. Shown to admin for real verification; deliberately kept off the owner's own screen, where contact stays mediated through the real message thread instead.</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Property page → Make an offer</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Offer Review</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Real document review at the point of listing approval</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>The screen where admin approves a new listing previously showed only the title and location, with zero visibility into the real uploaded legal documents. Every document now shows directly on the approval card, with its own view link and verify/reject action — and for Sale properties, the 'Verify' button is genuinely disabled, not just a warning, until every document and the owner's own ID are confirmed verified.</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Admin → Properties</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Category-aware bedroom display</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Land and other non-residential categories no longer show a bedroom count, regardless of what any individual record's data happens to contain — a real, permanent, shared safeguard rather than a one-off data fix.</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Any property listing/detail page</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Real bedroom/bathroom/toilet/room dropdowns</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Replacing plain number inputs with real, selectable dropdowns; a genuinely new, separate toilets count (previously conflated with bathrooms); a repeatable 'Others' facility field for anything not covered.</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>List a property</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Processed History</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>A real, permanent archive of every rental application, offer, property listing, and registration CHS has ever decided on — nothing disappears once approved or rejected, the same principle as an old message staying in a real inbox.</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Admin → Processed History</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Audit Trail</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>A real, permanent, tamper-evident log — no update or delete permission exists for anyone, by design. Covers property decisions, dispute rulings, escrow fund release, account suspension, every admin relay action, referral payouts, marketplace moderation, and agent management changes. Genuinely ongoing — not yet every action in the app.</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Admin → Audit Log</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Feature Explainer (InfoTip)</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>A real, reusable, mobile-first tap/hover explainer, live on 16+ previously-confusing terms across buyer, owner, and tenant screens — commission, escrow, guarantor, CHS Agent ID, rent auto-pay, and others. Genuinely ongoing across the app's 100+ features.</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Throughout the app, next to the relevant term</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Property manager listing access</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Managers previously could not list a property at all; agents already could. Fixed to match the identical, existing pattern — no separate database restriction ever existed, only a frontend role gate that had never included managers.</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>List a property</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Real room-video system</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>A genuine, cost-free alternative to a paid virtual-tour service. Record or upload a short, real video per room on a new or existing listing; a buyer/tenant can request a specific additional video if unsatisfied, and track that request's real status. Every video plays directly on the property page.</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>List/edit a property; Property page → Request a video</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Document Site</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Every current reference document — User's Guide, Terms &amp; Conditions, Feature Catalog, Handover Notes, Fix Tracker, Property Manager Guide, System Documentation — bundled directly into the app for one-tap download.</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Admin → Document Site</t>
         </is>
@@ -3102,2412 +3200,2426 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="70" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22.35" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Location + price search</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Filter by state, LGA, area, property type, minimum bedrooms, and a real minimum/maximum price range.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Homepage search — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Rent / Sale / Shortlet tabs</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Real filtering of the whole catalog by purpose.</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Homepage — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22.35" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Saved Properties &amp; Saved Searches</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Save individual listings, or save a whole search to be matched automatically as new listings arrive.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Saved page — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22.35" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Making an offer (sale)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Propose a real price directly to the owner; goes through a real CHS Sale Approvals checkpoint before anything moves to escrow.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Property detail page — Buyer</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Admin → Sale Approvals (Owner/Buyer/Tenant domain)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22.35" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Rental application</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>A real application, screened by CHS staff before the owner ever sees it.</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Property detail page — Tenant</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Rental application + independent guarantor confirmation</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>A real application, screened by CHS staff before the owner ever sees it. The applicant provides only their guarantor's name and phone number; the guarantor completes everything else — address, occupation, their own ID, a real proof of address, and a signed confirmation — independently, through their own private link, and cannot share the applicant's surname.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Property detail page — Tenant; guarantor's own link</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Admin → Applications (Owner/Buyer/Tenant domain)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22.35" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Inspection booking + transport fee</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Real fee calculated per-person based on distance; a genuine 12-hour minimum notice enforced by the database itself.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Property detail page — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Admin → Inspections (Owner/Buyer/Tenant domain)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22.35" customHeight="1" s="4">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Buyer/Tenant Readiness Score</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>A real questionnaire (timeline, funds ready, decision-maker) plus verification and inspection-attendance history — shown to owners, never a fee or gate.</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Inspection booking form — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>N/A — computed live</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22.35" customHeight="1" s="4">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Shortlet booking</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Paid instantly through the wallet, held in real escrow until check-in is confirmed. Real guest verification required.</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Property detail page — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22.35" customHeight="1" s="4">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Rent-to-Own</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Where offered, a real monthly amount counting toward eventual ownership, shown directly on the listing.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Property detail page — Buyer</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>N/A — set by owner at listing time</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="4">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>House Rules acknowledgment</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>A real, documented agreement a tenant acknowledges as part of their tenancy.</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard, per tenancy</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>N/A — set by owner</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22.35" customHeight="1" s="4">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Property Condition Report</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Documented and photographed at move-in — real evidence-based liability instead of a caution-fee guess.</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Condition Report page — Tenant</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22.35" customHeight="1" s="4">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Formal Notices</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Real formal communications (e.g. rent reminders, lease notices) from owner/CHS, viewable and expandable.</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>N/A — sent by owner/CHS</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="4">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Owner–tenant message thread</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>A real, direct messaging channel per tenancy.</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard, per tenancy</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22.35" customHeight="1" s="4">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Raise a Dispute</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>A real, two-sided dispute process — CHS's internal resolution is the first step before arbitration or courts.</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard + Owner dashboard</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Admin → Disputes (Customer Care domain)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="22.35" customHeight="1" s="4">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Talk to an Agent (Concierge)</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Describe a property need in free text or voice instead of using search filters — a real request CHS follows up on personally.</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Bottom nav → Property request — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Admin → Concierge, within Owner/Buyer/Tenant domain</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="22.35" customHeight="1" s="4">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Urgent &amp; Emergency Sale browsing</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Real, discounted, time-boxed listings shown in a dedicated homepage row with the real deadline.</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Homepage — Buyer</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>N/A — browsing only</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="22.35" customHeight="1" s="4">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Market data (average prices, demand trend)</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Real, genuine data (not placeholder figures) on current prices and search-driven demand patterns.</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Bottom nav → Average prices / Demand trend</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22.35" customHeight="1" s="4">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Engage CHS — buy a construction project</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Full request flow with real specifications, document checklist, two-way chat, and the Construction Roadmap tool.</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Engage CHS page — Buyer / Owner</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Admin → Engage CHS (Super Admin only)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32.8" customHeight="1" s="4">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Hotel, Event Centre, Hall, Car Park, Cinema &amp; Recreational/Sports booking</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>A real, instant "Book now" flow — not a rental application — for any genuine guest venue, correctly categorized and commissioned. A business-lease "hire" listing (e.g. a filling station) correctly stays on the rental-application path instead.</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Property detail page — Buyer / Guest</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22.35" customHeight="1" s="4">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Auto-pay rent from a dedicated savings wallet</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>An optional, real toggle — rent pays itself the moment it's due from a separate Rent Savings balance, or stays fully manual if left off.</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard, per tenancy</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="32.8" customHeight="1" s="4">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Rent held in real escrow</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Paid rent is not released to the landlord immediately. Held until the tenant files a genuinely clean move-in report, or 14 days pass with nothing raised — the same real protection a buyer's money gets. An open fault or a flagged report item pauses release for admin review.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Tenant &amp; Owner dashboards, wallet — Tenant / Owner</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Admin → Escrow Oversight (Owner/Buyer/Tenant domain) — release early, or review a flagged hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Subsequent-year rent — no repeat tenant commission</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>The system now genuinely knows a renewal from a first payment. From year two onward, the tenant pays CHS nothing further — only the landlord, at a real, reduced 3%. Shown live on both the tenant's and owner's rent countdown.</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Tenant &amp; Owner dashboards, rent countdown</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="22.35" customHeight="1" s="4">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Move-out condition report + real court affidavit</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>A genuine move-out counterpart to the existing move-in report, with a real, required court-issued affidavit upload — now actually visible to the landlord, which it never was before.</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Condition Report page — Tenant; visible on Owner dashboard</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22.35" customHeight="1" s="4">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Non-renewal notice with a real message</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>A genuine optional message sent to the landlord along with the notice — previously a bare, wordless click.</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard, per tenancy</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="32.8" customHeight="1" s="4">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Real street address on every listing</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>A required, specific address (e.g. "House 12, Shagari Road") — not just a general neighborhood — visible on the tenant's own dashboard and usable for real fault/payment tracing.</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>List a property form; Tenant dashboard</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Admin analytics, traceable by real address</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="70" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22.35" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>List a property</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Photos, location, price, purpose, bedrooms, and special terms (rent-to-own, house rules). Starts unverified.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard → List a property</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Properties (Owner/Buyer/Tenant domain)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22.35" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Property verification</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>CHS reviews every listing before it's publicly visible — the real meaning behind "CHS Verified."</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Properties (Owner/Buyer/Tenant domain)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Fixed-tier promotion (7/30/90-Day Boost)</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>One-off paid tier, debited directly from the wallet.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Promote page, per listing</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32.8" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Credit-based promotion (pause anytime)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Real, shared credit balance across every listing; each listing charged separately per real day it's on, based on real location/size cost. Real ranking (Category A–D + literal Top 10/20 position) against the same real local market.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Promote page, per listing</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic, database-driven</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="22.35" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Urgent &amp; Emergency Sale activation</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Requires the listing already verified and owner ID-verified. Real original price, discount, and deadline shown to buyers.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard → 🚨 Urgent Sale</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Notified via general notifications on activation</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22.35" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Managing offers &amp; rental applications</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Real accept/reject decisions on real, CHS-screened offers and applications.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Admin → Sale Approvals / Applications</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22.35" customHeight="1" s="4">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Inspection management + Readiness Score visibility</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>See each real requester's readiness score; mark real attendance/no-show after the scheduled time passes.</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard, per property</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Admin → Inspections</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="4">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Delegating to a Property Manager</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Hands maintenance and certain approvals to a registered Manager; reversible any time.</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="4">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Property analytics</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Real view counts, inspection counts, and interest counts — not fixed placeholder numbers.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Analytics page, per listing</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="4">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Editing a live listing</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Real edits to an already-published property.</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Edit listing page</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22.35" customHeight="1" s="4">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Engage CHS for a professional service</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Full Property Management, Sale Negotiation, Construction Monitoring, Project Management, Renovation — each with its own real terms and fee schedule.</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Engage CHS page — Owner</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Admin → Engage CHS (Super Admin only)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32.8" customHeight="1" s="4">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Download verified sale documents</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>The actual, CHS-verified legal documents (Certificate of Occupancy, Deed of Assignment, etc.) genuinely downloadable by a paying buyer directly — previously only ever tracked as a physical-dispatch status with no real digital access.</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Property detail page, after payment — Buyer</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32.8" customHeight="1" s="4">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Accept an offer at negotiated terms, mid-chat</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>A real conversion point that didn't exist before — accept at a different final price than the original offer, with an optional condition (e.g. a payment deadline), directly from the ongoing negotiation.</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard, per offer</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="70" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22.35" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Unique referral link</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>A real code (e.g. CHS-AG-0024) automatically attached to every property link generated — always opens the property directly on CHS.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22.35" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Automatic commission attribution</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>If a referred visitor completes a real transaction on that property, CHS automatically attributes and credits the commission.</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Referral fees (Agent Relations domain)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22.35" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Real referral tracking (masked for privacy)</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Real deal stage, earnings this month, and total earned — served from a privacy-conscious masked view.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Admin → Referral fees</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32.8" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Managing an agent-managed property's own commission</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>For a property under full agent authority, set your own real market rate (e.g. 10-15%) with the client — CHS charges the client nothing extra, taking a real, capped 3% only from your own earnings.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard, per managed property</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32.8" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Per-owner commission rate — one real, standing rate</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A genuine, editable rate per real owner relationship, not re-entered per property — reviewable and adjustable any time, applying automatically to every property you manage for that owner, including new ones.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard → Your Real Commission Rate Per Owner</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22.35" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Digital remittance to an owner's wallet</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Rent collected in person, remitted straight into the real owner's wallet with your agreed commission auto-deducted — a real, permanent reference either side can point to.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard → Remit Collected Rent to an Owner</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Admin → Finance, real remittances table</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22.35" customHeight="1" s="4">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>A real tenant register</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Full biodata, property details, and a real auto-generated reference number (e.g. TEN-000001) for every tenant you manage — plus real ID and selfie verification.</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>My Tenant Register page</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22.35" customHeight="1" s="4">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>A real mini-admin — your own team</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Add real, separate staff accounts by phone number, assign a role, and see their genuine daily activity reports — the same kind of oversight CHS itself runs on.</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard → Manage My Team</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22.35" customHeight="1" s="4">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Multiple linked bank accounts</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Up to 4 real, Paystack-verified bank accounts — a genuine business need for agents working across multiple banking relationships, unlike every other role which stays single-account.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Profile → Linked bank accounts</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22.35" customHeight="1" s="4">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Expenses &amp; income tracking</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Real salary, rent, transport, logistics, and commission income entries — a genuine net position, not just a spending log.</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>My Expenses &amp; Income page</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22.35" customHeight="1" s="4">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>My real activity report</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>A genuine, date-range (week/month/quarter) report of commission earned, deals closed, and tenancies managed.</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard → Generate my activity report</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="70" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22.35" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Delegated property management</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Owners can delegate specific properties; maintenance and certain approvals route to the manager directly.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Manager dashboard</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22.35" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Management termination</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>An owner can reverse delegation any time, handing responsibilities back.</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard (trigger) / Manager dashboard (effect)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32.8" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Posting a maintenance job for quotation</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Real job posts that verified artisans can quote on, ranked by a transparent rating/reliability/experience/equipment formula.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Manager dashboard</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Admin → Maintenance (Artisan/Developer/PM/Vendor domain)</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22.35" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Rating an artisan</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Real, genuine ratings after a completed job.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Manager dashboard, per completed job</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22.35" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Owner-occupier support in estates</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Register a real occupant who owns their unit outright (no tenancy) alongside genuine tenants in the same estate — correctly counted in occupancy and included in service-charge billing.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Manager dashboard, per estate unit</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="43.25" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Per-owner commission rate, digital remittance, tenant register, mini-admin team, multiple bank accounts, expenses tracking</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Every real business tool built for agents this round applies identically to managers — the same standing per-owner rate, the same digital remittance, the same tenant register and team system.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Manager dashboard — same real pages as Agent</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22.35" customHeight="1" s="4">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>My real activity report — across all my estates</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>A genuine, date-range report of new tenancies, service charges billed and collected, and maintenance resolved across every estate you manage.</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>My Estates page → Generate my activity report</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="70" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32.8" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Developer registration &amp; review</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>A real application reviewed by CHS before projects go live.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Register / Developer dashboard</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Developers (Artisan/Developer/PM/Vendor domain)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Listing development projects</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Estates, instalment plans, and investment plans.</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Developer dashboard</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Developers</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="70" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32.8" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Vendor registration &amp; verification</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Reviewed by CHS before listings go live — the same trust standard applied platform-wide.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Become a Vendor / Vendor dashboard</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Vendors (Artisan/Developer/PM/Vendor domain)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22.35" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Listing products &amp; bundles</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Real materials/services catalog, browsable by category on the Marketplace.</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Vendor dashboard (list) + Marketplace page (browse)</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Service quote requests</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Real incoming requests for a quote on a specific service.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Vendor dashboard</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Referral fee tracking</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Real fees on deals connected through the Marketplace.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Vendor dashboard</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Admin → Referral fees</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="70" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32.8" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Artisan registration &amp; verification</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Real trades, years of experience, certification, and equipment tier (with photo/receipt backing) — reviewed before quoting is allowed.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Become an Artisan / Artisan dashboard</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Artisans (Artisan/Developer/PM/Vendor domain)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="22.35" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Quoting on maintenance jobs</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Real quotes ranked by a transparent formula: rating/reliability first, experience second, equipment third.</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Artisan dashboard</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Maintenance</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22.35" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Full-management job priority</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>For any property under full CHS management, maintenance work goes first and exclusively to verified CHS Maintenance Agents.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Automatic — Artisan</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Job dispute resolution</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Either the artisan or the client can raise a genuine, two-sided dispute about a completed job.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Artisan dashboard</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Admin → Disputes</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Ratings received</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Real, visible rating history.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Artisan dashboard</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="70" customWidth="1" style="3" min="2" max="2"/>
-    <col width="28" customWidth="1" style="3" min="3" max="4"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>How it works</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (user)</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Where to find it (admin)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="22.35" customHeight="1" s="4">
-      <c r="A2" s="6" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Super Admin role</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>One real account, practically involved in every part of the platform — handles Finance and Engage CHS directly, and ratifies every sub-admin's high-stakes decision.</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Admin dashboard</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="32.8" customHeight="1" s="4">
-      <c r="A3" s="6" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Five real sub-admin domains</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Customer Care, Registration &amp; Setup, Owner/Buyer/Tenant, Agent Relations, Artisan/Developer/PM/Vendor — each sub-admin only sees and acts within their own domain, enforced at the database level.</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Admin dashboard, tab-gated per domain</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview → Assign an admin role</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="22.35" customHeight="1" s="4">
-      <c r="A4" s="6" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Code-based admin login approval</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>A sub-admin's correct password alone isn't enough — a real code is generated and sent to the Super Admin, who must approve that specific login.</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Sub-admin login flow</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview — pending login approvals</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="22.35" customHeight="1" s="4">
-      <c r="A5" s="6" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>High-stakes approval queue</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Routine sub-admin actions apply immediately; financial and verification decisions are held pending real Super Admin sign-off.</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Admin dashboard, across relevant tabs</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview — pending sub-admin actions</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="53.7" customHeight="1" s="4">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Trace an Account</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Search any real user by phone/email/name and see their full wallet balance + transaction history, promotion credits + active promotions, construction roadmap unlocks, linked bank account, and Engage CHS requests — all in one place. The real fix for resolving a support issue ("I paid but nothing happened") the way a phone network traces an account from just a phone number.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Admin → 🔎 Trace an Account (Super Admin only)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="22.35" customHeight="1" s="4">
-      <c r="A7" s="6" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Sub-admin action history</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>A real, permanent audit log of every resolved sub-admin request — previously, once approved or rejected, a request simply vanished with no record.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview → View sub-admin action history</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22.35" customHeight="1" s="4">
-      <c r="A8" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Pre-launch admin test mode</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Super Admin can preview any real dashboard using their own account, never a real user's data, with a visible banner the whole time.</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>N/A — testing tool</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview → Switch role for testing</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="4">
-      <c r="A9" s="6" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Search any real user's wallet, view all three real balances, freeze/unfreeze.</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Admin → Finance</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="4">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Sale Approvals</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>The real checkpoint between an accepted offer and money moving to escrow.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Admin → Sale Approvals</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="4">
-      <c r="A11" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Face Verification (Liveness)</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Real human review of each real-time capture.</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Admin → Face Verification</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="4">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Registrations</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Approve or reject new real accounts.</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Admin → Registrations</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="4">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Applications</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Real rental application review before an owner ever sees it.</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Admin → Applications</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="4">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Real listing verification before it's publicly visible.</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Admin → Properties</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="4">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Disputes</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Real, two-sided dispute resolution across tenancies and artisan jobs.</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Admin → Disputes</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="4">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Feedback</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>General platform suggestions/complaints, not tied to a specific transaction.</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Admin → Feedback</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="22.35" customHeight="1" s="4">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Engage CHS</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Real professional-service requests: specifications, document checklist, two-way chat, roadmap access — Super Admin only, per direct instruction.</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Admin → Engage CHS</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="4">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Vendors</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Real marketplace vendor verification.</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Admin → Vendors</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="4">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Referral fees</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Real agent/vendor commission tracking and payout, routed through the approval queue.</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Admin → Referral fees</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="4">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Real fault report routing to the right artisan/manager.</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Admin → Maintenance</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="4">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Artisans</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Real trade/equipment verification before an artisan can quote.</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Admin → Artisans</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="4">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Inspections</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Real upcoming inspection oversight across the whole platform.</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Admin → Inspections</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="4">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Developers</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Real developer application review.</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Admin → Developers</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="32.8" customHeight="1" s="4">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Real, date-range analytics report</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>A genuine, filterable (today/week/month/quarter) record of properties sold, new tenancies, shortlet bookings, new listings, new users, and total commission revenue by transaction type — not just a live, un-datable snapshot.</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Admin → Analytics</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="22.35" customHeight="1" s="4">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Suspend a real account, with a genuine appeal process</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Suspend by phone number with a required, documented reason; a real appeal queue to approve (reinstate) or deny.</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="22.35" customHeight="1" s="4">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>CHS staff daily report</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Any real internal admin staff member can submit their own daily activity report, visible to the super admin.</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview → Submit My Daily Report</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="32.8" customHeight="1" s="4">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Critical data-protection fixes</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>A direct security audit found and closed a real, proven exposure — any logged-in user could previously read another user's NIN, phone, and ID documents. Fixed at both the database and file-storage level, re-verified after the fix.</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>N/A — platform-wide</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>See the separate Security Audit report</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="22.35" customHeight="1" s="4">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Missing database indexes added</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Dozens of real foreign-key columns had no index — invisible at small scale, a genuine slowdown waiting to happen as real data grows. Added across every high-traffic table.</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>N/A — platform-wide</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>See the separate Scalability Assessment report</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="22.35" customHeight="1" s="4">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Real, editable Contact Us details</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Four real, distinct contact emails (Support, Inquiry, Engage CHS, Admin) and two real phone numbers — genuinely admin-editable at any time, not hardcoded into the app.</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>More menu → Contact us — every role</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview → Edit Real Contact Details</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
+++ b/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
@@ -16,12 +16,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Vendor &amp; Marketplace" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. Artisan" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. Admin &amp; Platform Management" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Estate Management, Rent to " sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. Real Sale Payment, Escrow, " sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Estate Management, Rent to" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. Real Sale Payment, Escrow," sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12. Round 3 Client Testing — Re" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13. AgentManager Tools, HostGue" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13. Agent-Manager Tools, Host-G" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14. Marketplace Rebuild, Guaran" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15. Admin Mediation Completed, " sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15. Admin Mediation Completed," sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16. Hotel, Lodge, Shortlet &amp; Ev" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40,14 +41,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <sz val="9"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -59,7 +57,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4A3B5C"/>
+        <fgColor rgb="002B2521"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,10 +73,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -446,16 +449,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -483,17 +486,17 @@
           <t>Registration with role selection</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Buyer, Tenant, Property Owner, Agent, Property Manager, or Commercial Developer — with role-specific extra fields (e.g. professional certificate upload for Managers).</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>New accounts land in Admin → Registrations, pending approval</t>
         </is>
@@ -505,17 +508,17 @@
           <t>NIN uniqueness check</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>A real National Identification Number can only ever be tied to one CHS account.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>N/A — enforced at registration</t>
         </is>
@@ -527,17 +530,17 @@
           <t>Multi-role linking</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>One real identity, one wallet, one login can hold several roles at once (e.g. Owner + Tenant) via "Link Account" rather than a second registration.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Link Account page — every role</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -549,17 +552,17 @@
           <t>Biometric login (Face ID / fingerprint)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Real WebAuthn — uses the device's own secure hardware; CHS never sees or stores the actual biometric data.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Login page + Profile setup — every role</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -571,17 +574,17 @@
           <t>Identity verification (name, gender, age bracket, state, address, occupation, phone, email + ID)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Real, full verification required before any commitment on the platform — an offer, rental application, booking, inspection, or professional engagement. The name typed is compared automatically against the registered name for the reviewing admin. Done once, covers everything after. A NIN is permanently locked to one account, enforced at the database.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Property page (on first commitment) + Profile — every role</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Admin → ID Verification (Registration &amp; Setup domain) — shows the name-match verdict and full details</t>
         </is>
@@ -590,196 +593,196 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Liveness / face verification</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Real document upload plus a genuine, real-time photo capture (never an uploaded photo) reviewed by CHS staff.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Registration / Profile — every role</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Admin → Face Verification (Registration &amp; Setup domain)</t>
+          <t>Automated Verification System (AVS) — Phase 1: document text match</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>A real first-pass check admin can trigger with one button: reads the actual uploaded ID image using Claude's real vision capability, extracts the printed name and ID number, and compares them against what the applicant typed. A clean match is shown plainly; any discrepancy is flagged with both values shown side by side so admin reviews a specific problem rather than re-reading the whole document. Does not confirm the document is genuine or that a face matches — that remains a human judgment call, or a future Phase 2 using a licensed identity-verification provider (Dojah/VerifyMe/Youverify), a separate cost decision not yet made.</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Admin → ID Verification — 🤖 Verify Automatically button on each submission</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Requires an ANTHROPIC_API_KEY secret to be configured on the Supabase project</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Editable profile with re-verification trigger</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Name, phone, address, and state are genuinely editable. A real name change automatically resets ID/liveness verification.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Profile page — every role</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Real notification to Super Admin on any name change</t>
+          <t>Liveness / face verification</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Real document upload plus a genuine, real-time photo capture (never an uploaded photo) reviewed by CHS staff.</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Registration / Profile — every role</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Face Verification (Registration &amp; Setup domain)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Wallet (main + rent savings + maintenance reserve)</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Three real sub-balances per user — a main spending balance plus two dedicated savings pots for rent renewal and maintenance costs.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Wallet page — every role</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Admin → Finance — search any user's real balances, freeze/unfreeze</t>
+          <t>Editable profile with re-verification trigger</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Name, phone, address, and state are genuinely editable. A real name change automatically resets ID/liveness verification.</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Profile page — every role</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Real notification to Super Admin on any name change</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Wallet funding via Paystack</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Real, secure card/bank/USSD payment; balance updates automatically once payment genuinely completes.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+          <t>Wallet (main + rent savings + maintenance reserve)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Three real sub-balances per user — a main spending balance plus two dedicated savings pots for rent renewal and maintenance costs.</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Wallet page — every role</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Finance — search any user's real balances, freeze/unfreeze</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Wallet withdrawal to bank</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Only one linked bank account per wallet, for security. Real Paystack transfer to the verified account.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+          <t>Wallet funding via Paystack</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Real, secure card/bank/USSD payment; balance updates automatically once payment genuinely completes.</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Wallet page — every role</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>N/A — self-service, admin sees real withdrawal_requests records</t>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Wallet-to-wallet transfer</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Send funds directly to another CHS user by phone or email — real-time lookup and instant transfer.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+          <t>Wallet withdrawal to bank</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Only one linked bank account per wallet, for security. Real Paystack transfer to the verified account.</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Wallet page — every role</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>N/A — self-service, admin sees real withdrawal_requests records</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Bank account linking with real-time verification</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>200+ real Nigerian banks with search; the account number is checked against the real bank network before it can ever be linked. Real 48-hour security window on any change.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Wallet → Link bank account — every role</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>N/A — self-service, real-time</t>
+          <t>Wallet-to-wallet transfer</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Send funds directly to another CHS user by phone or email — real-time lookup and instant transfer.</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Wallet page — every role</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Notification preferences</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Independent real toggles for offers, messages, and marketing notifications.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Profile page — every role</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
+          <t>Bank account linking with real-time verification</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>200+ real Nigerian banks with search; the account number is checked against the real bank network before it can ever be linked. Real 48-hour security window on any change.</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Wallet → Link bank account — every role</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>N/A — self-service, real-time</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Diaspora Mode</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>A real setting for CHS users managing property or transactions from outside Nigeria.</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+          <t>Notification preferences</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Independent real toggles for offers, messages, and marketing notifications.</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Profile page — every role</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -788,86 +791,86 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Terms &amp; Conditions scroll-to-accept gate</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>A real, meaningful acceptance — the checkbox only unlocks after genuinely scrolling to the bottom. Required before any dashboard is reachable.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>First login — every role</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>N/A — one-time gate</t>
+          <t>Diaspora Mode</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>A real setting for CHS users managing property or transactions from outside Nigeria.</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Profile page — every role</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Role-specific first-dashboard guide + persistent Users Guide</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>A short popup on first dashboard visit, plus a full, always-accessible reference page.</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>First login popup + More menu → Users Guide</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>N/A — reference</t>
+          <t>Terms &amp; Conditions scroll-to-accept gate</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>A real, meaningful acceptance — the checkbox only unlocks after genuinely scrolling to the bottom. Required before any dashboard is reachable. The Terms carry a version number: when they change (Version 3, October 2026, rewrote term 11 on bookings), everyone is shown what is new and asked to accept once more. Every acceptance is logged permanently with the version and the exact time, and the log cannot be altered.</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>First login — every role</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>N/A — one-time gate per version</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Dark mode</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>A real, complete theme system across the whole app, with an app-wide fix ensuring form text stays readable in both modes.</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Every page — every role</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>N/A — visual</t>
+          <t>Role-specific first-dashboard guide + persistent Users Guide</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>A short popup on first dashboard visit, plus a full, always-accessible reference page.</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>First login popup + More menu → Users Guide</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>N/A — reference</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>PWA install + splash screen</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>Installable as a real app on the home screen, with a proper full-screen splash and app icon.</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Browser install prompt</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+          <t>Dark mode</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>A real, complete theme system across the whole app, with an app-wide fix ensuring form text stays readable in both modes.</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Every page — every role</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>N/A — visual</t>
         </is>
@@ -876,152 +879,174 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Guest — its own real role</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>A genuine, separate role from Buyer, for booking a shortlet apartment or a hotel/lodge/event centre/car park stay — its own heading at registration and login, not merged into another role.</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Register / Login page — every role</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
+          <t>PWA install + splash screen</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Installable as a real app on the home screen, with a proper full-screen splash and app icon.</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Browser install prompt</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>N/A — visual</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Account approval gate</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>A real, enforced rule: a newly registered account cannot use anything beyond the public homepage until CHS staff approve it — previously unenforced despite existing in the database.</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Every page — every role</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Admin → Registrations</t>
+          <t>Guest — its own real role</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>A genuine, separate role from Buyer, for booking a shortlet apartment or a hotel/lodge/event centre/car park stay — its own heading at registration and login, not merged into another role.</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Register / Login page — every role</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Account suspension &amp; appeal</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Real admin tools to suspend a suspicious account with a documented reason, and a genuine appeal channel that stays reachable even while suspended.</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Suspended-account screen — every role</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Admin → Overview, Suspend a Real Account</t>
+          <t>Account approval gate</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>A real, enforced rule: a newly registered account cannot use anything beyond the public homepage until CHS staff approve it — previously unenforced despite existing in the database.</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Every page — every role</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Registrations</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Self-service account deactivation</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>A real, reversible way to temporarily deactivate your own account — nothing deleted, log back in any time to reactivate.</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Profile page — every role</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
+          <t>Account suspension &amp; appeal</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Real admin tools to suspend a suspicious account with a documented reason, and a genuine appeal channel that stays reachable even while suspended.</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Suspended-account screen — every role</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Overview, Suspend a Real Account</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Automatic image compression</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Every property photo and profile picture is resized and re-compressed in the browser before upload — no action required, real storage savings confirmed by direct testing.</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Every photo upload — every role</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>N/A — automatic</t>
+          <t>Self-service account deactivation</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>A real, reversible way to temporarily deactivate your own account — nothing deleted, log back in any time to reactivate.</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Profile page — every role</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Real-time number validation (phone, NIN, ID, bank account)</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>One shared rulebook checks every phone number, NIN, passport, voter's card, driver's licence, and bank account number as it's typed, on submit, and again in the database itself — so a malformed number can never be saved from any screen.</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Every form collecting a phone, ID, or account number — every role</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>N/A — enforced automatically; a malformed existing record is flagged on the ID review screen</t>
+          <t>Automatic image compression</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Every property photo and profile picture is resized and re-compressed in the browser before upload — no action required, real storage savings confirmed by direct testing.</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Every photo upload — every role</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>N/A — automatic</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>Real-time number validation (phone, NIN, ID, bank account)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>One shared rulebook checks every phone number, NIN, passport, voter's card, driver's licence, and bank account number as it's typed, on submit, and again in the database itself — so a malformed number can never be saved from any screen.</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Every form collecting a phone, ID, or account number — every role</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>N/A — enforced automatically; a malformed existing record is flagged on the ID review screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t>Digital receipts</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>A real, printable receipt (Print/Save as PDF) for any transaction — rent, remittance, commission, sale — using the same reference number already generated for it.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>My Receipts page — every role</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1041,13 +1066,13 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -1075,17 +1100,17 @@
           <t>Estate Management</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>A real, bounded estate of many housing units under one manager, distinct from delegating individual properties one at a time.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Manager → My Estates</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Admin → Overview</t>
         </is>
@@ -1097,17 +1122,17 @@
           <t>Estate subscription</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Real monthly pricing that scales with unit count, and drops per-unit as an estate grows — paid directly from the manager's wallet.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Manager → My Estates → Subscribe</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1119,17 +1144,17 @@
           <t>Bulk unit onboarding</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Upload a real CSV to add many units at once instead of one at a time — the real answer to onboarding an estate of hundreds of units.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Manager → My Estates → [Estate]</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1141,17 +1166,17 @@
           <t>Estate service charges</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>A real, distinct-from-rent charge billed to every occupied unit at once; vacant units are automatically skipped.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Manager dashboard / Tenant dashboard</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1163,17 +1188,17 @@
           <t>Rent to Own / Mortgage</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>A genuinely new listing category — progressive ownership through real monthly installments, with real ownership-percentage tracking that automatically completes the sale at 100%.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Property listing page / Owner dashboard</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1185,17 +1210,17 @@
           <t>Reminder Engine</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>One real, generic escalation system: rent-due cadence, maintenance follow-up (artisan → manager), and shortlet guest-message escalation (host → admin) — multi-channel (in-app, SMS, email).</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>N/A — automatic, background</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1207,19 +1232,19 @@
           <t>Shortlet/Hotel guest-host messaging</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Real in-app communication for the duration of a booking, with genuine host anonymity toward the guest — never toward CHS, which can always intervene directly.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>My Bookings (guest) / Owner dashboard (host)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Guest and host never deal with each other directly: every message goes through CHS. Until a booking is paid, each message waits for CHS review and the other side cannot read it; after payment it is delivered at once. Phone numbers and email addresses are refused at all times. The guest never sees who the host is; the host sees the guest's name and a CHS reference, never their phone number.</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>My Bookings (guest) / Owner &amp; Host dashboards (host)</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings → message review</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1254,17 @@
           <t>Maintenance Reserve — real funding</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>An owner can fund their Maintenance Reserve directly from their Main Wallet for a real, larger repair; artisan payments draw from the Reserve first, and unused funds can be withdrawn back freely.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Wallet page</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1259,13 +1284,13 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -1293,17 +1318,17 @@
           <t>Real Sale purchase-price payment</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>The genuine mechanism for a buyer to pay a seller the actual purchase price — not just commission. A single, transparent checkout: the buyer's total automatically includes their own commission (shown as both a percentage and a real value), the seller's net automatically excludes theirs.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Property page, once an offer is accepted</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1315,17 +1340,17 @@
           <t>Real, sourced Sale legal documents</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Certificate of Occupancy, Deed of Assignment, Survey Plan, Governor's Consent, Tax Clearance Certificate, Sale Agreement, and (for a developed property) Building Plan Approval — sourced from genuine Nigerian legal references. Required at listing time; a buyer's payment is blocked until every one is CHS-verified.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>List a property (Sale)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Admin → Face Verification tab (Sale documents)</t>
         </is>
@@ -1337,17 +1362,17 @@
           <t>Escrow hold on sale proceeds</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>A seller's real proceeds are visible in their wallet the instant a buyer pays, but not withdrawable until CHS confirms the real, physical legal documents have been transferred to the buyer.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Wallet page</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Admin → Registrations tab (Confirm legal transfer)</t>
         </is>
@@ -1359,17 +1384,17 @@
           <t>Real, admin-reviewed identity verification</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>A buyer's ID submission previously self-certified the instant the form was filled in. Now creates a genuine pending record, reviewed and approved by real CHS staff before it counts.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Making an offer (if not yet verified)</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Admin → Registrations tab</t>
         </is>
@@ -1381,17 +1406,17 @@
           <t>Mobile logout</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>A working logout in the persistent bottom navigation's More menu — previously only reachable from the homepage.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Bottom nav → More</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1403,17 +1428,17 @@
           <t>Context-aware House Rules</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Only appears for Rent, Lease, Shortlet, and Rent to Own listings — no longer shown on a Sale listing where it never applied.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1425,17 +1450,17 @@
           <t>Real, progressive nearby-properties matching</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>The "similar properties" advertising system now genuinely widens from exact area → LGA → state, and matches property type, rather than matching the whole state regardless of relevance.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Property detail page</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1447,17 +1472,17 @@
           <t>Seller response note on an offer</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>A real, optional message a seller can attach when accepting or declining an offer — delivered directly to the buyer's notification, matching the note a buyer could already leave.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1469,17 +1494,17 @@
           <t>Rent countdown and 90-day non-renewal notice</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>A real, live day-count to next rent on the tenant dashboard, and a genuine notice mechanism that honestly records whether notice was given within or after the requested 90-day window.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Tenant dashboard</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1499,13 +1524,13 @@
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -1533,17 +1558,17 @@
           <t>Verification review moved to the right place</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>A real, repeated complaint — buyer ID verification submissions "vanished." The real root cause: this review screen lived under an unrelated tab called "Face Verification." Moved into "Registrations," where it's actually found.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Admin → Registrations tab</t>
         </is>
@@ -1555,17 +1580,17 @@
           <t>Gender field and a respectful greeting</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>A real gender field at registration — the homepage now greets "Hi Mr. Samson" / "Hi Miss Jennifer" instead of a bare first name.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Register page; Homepage</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1577,17 +1602,17 @@
           <t>Dynamic, per-role comprehension questionnaire</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Real, separate question banks for Buyer, Guest, Tenant, Owner, Agent, and Manager — each genuinely testing that role's own real Terms &amp; Conditions clauses, not one static quiz for everyone.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1599,17 +1624,17 @@
           <t>Required-field markers and auto-scroll-to-error</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>A real red asterisk on every genuinely required field; submitting an incomplete form now scrolls straight to the exact missing field and highlights it in red.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1621,17 +1646,17 @@
           <t>Real State → LGA multi-select for agent coverage area</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>A genuine checklist of every real LGA in the agent's state, plus a "Statewide" shortcut that selects them all in one click.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Register page (Agent)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1643,17 +1668,17 @@
           <t>"Others" registration category for artisans, market sellers, and service providers</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>A real, new registration option leading to a genuine "choose your category" page, bridging straight into the existing Artisan and Vendor application forms that were previously unreachable from registration.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Register page; Login page</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1665,17 +1690,17 @@
           <t>Real login for Artisans and Vendors/Service Providers</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Confirmed and fixed a genuine gap: someone approved as an Artisan or Vendor had no way to log back in as themselves. Login now checks their real, separate application record for these two categories.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Login page</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1687,17 +1712,17 @@
           <t>CHS-specific inspection-fee question</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Reworded to specifically ask about a CHS agent acting on CHS's own commission structure — CHS cannot control what an independent agent charges their own client.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1709,17 +1734,17 @@
           <t>Independent agent fee builder and real Total Package</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>An agent listing a property can add any number of named, real fee lines (Custom fee, Legal fee, Agent fee, etc.) with their own percentage, rolling into one real, transparent "Total Package" shown on the listing — visually distinct from a CHS-managed listing's "no extra fees" badge.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>List a property (Agent); Property detail page</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1731,17 +1756,17 @@
           <t>Real, live admin notification bell</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>A genuine, real-time notification bell with an unread badge — database-level triggers now automatically notify admin the instant a new registration or ID verification comes in, regardless of which part of the app created it.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Admin dashboard header</t>
         </is>
@@ -1753,17 +1778,17 @@
           <t>Real shortlet booking data fix</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Found and fixed the actual cause of shortlet bookings failing outright — 20 of 22 real listings were missing their nightly price. Backfilled the real data and added a permanent fallback so this can't silently recur.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Property detail page (Guest)</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1775,17 +1800,17 @@
           <t>Correct role-based landing after login/registration</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Fixed two real, separate bugs sending every role to the generic homepage — the registration redirect, and a completely separate Face ID/fingerprint login path that ignored role entirely.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Login page; Register page</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1797,17 +1822,17 @@
           <t>Staff login, made discoverable and functional</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Confirmed the Manage-My-Team and staff-reporting features already existed; found and fixed the real, missing piece — a brand-new staff member had no role to register under. "Staff / Employee" is now a real registration option.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Register page; Login page; /staff</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1819,17 +1844,17 @@
           <t>Real "My Properties &amp; Owners Register"</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>A genuine register of every property and owner under an agent/manager's real management — property, address, owner name, owner phone, and agreed commission rate — parallel to the existing tenant register.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1841,17 +1866,17 @@
           <t>Real one-step-back navigation</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Fixed a hardcoded "back to homepage" link repeated across 15 real sub-pages — each now genuinely returns one real step, not straight to the homepage.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Every sub-page — every role</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1863,17 +1888,17 @@
           <t>Detailed, consequential guarantor form</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Added real relationship-to-applicant, guarantor address, guarantor occupation, and a genuine, plain-language consent statement — not just a bare name and phone number.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Rental application (Tenant)</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1885,17 +1910,17 @@
           <t>Real, complete rental application review for admin</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Admin can now see full applicant details (occupation, address, income, ID, uploaded document) and full guarantor details, plus which real property and owner it's for — genuine vetting is now possible before forwarding.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Admin → Applications tab</t>
         </is>
@@ -1907,17 +1932,17 @@
           <t>CHS-mediated owner decision on rental applications</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>An owner's approve/decline is now recorded, not finalized immediately — CHS admin reviews and relays the real, final decision to the applicant, keeping CHS genuinely in the loop both ways.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Owner dashboard; Admin → Applications tab</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Admin → Applications tab</t>
         </is>
@@ -1937,13 +1962,13 @@
   <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -1971,17 +1996,17 @@
           <t>Real team/staff system</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>An agent or manager can invite genuine, separate staff accounts, assign a role label, and see each one's real daily activity report.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard → Manage My Team</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1993,17 +2018,17 @@
           <t>Team/staff subscription</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Free for up to 2 real staff; a real subscription required from the 3rd, tiered by staff count, with exact multi-month discounts (6 months paid → 8 months of real access; 12 paid → 18).</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard → Manage My Team</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2015,17 +2040,17 @@
           <t>Real tenant register and property/owner register</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Per-agent, searchable registers with real ID documents attached, replacing an informal spreadsheet.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Admin → Tenant Register Oversight</t>
         </is>
@@ -2037,17 +2062,17 @@
           <t>Expense tracking, owner remittance, digital receipts</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Real income/expense entries, a real flow for remitting collected rent to the actual owner, and auto-generated digital receipts for completed transactions.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard → Expenses</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2059,17 +2084,17 @@
           <t>Independent agent commission model and custom fee builder</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>A real, adjustable per-owner commission rate, plus any number of named custom fee lines rolling into one transparent Total Package.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Agent dashboard; List a property (Agent)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2081,17 +2106,17 @@
           <t>Host and Guest as real, separate roles</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Split from Owner/Buyer with their own dedicated dashboards, built the same way as every other role.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>/host; /guest</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2103,19 +2128,19 @@
           <t>Real shortlet/hire request-to-book flow</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Complete rebuild: a guest sees the true, full cost (rent plus commission) before committing; a host must genuinely accept or decline; a decline triggers a real, automatic full refund. Previously, bookings were instantly confirmed with no host review and no real way for a host to ever get paid.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Superseded by the request-first flow (section 16). History: first rebuilt so a guest saw the true, full cost before committing and a host had to accept or decline; the guest was then charged at request time. Since October 2026 nothing is charged until the host has confirmed the dates.</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Property page (Shortlet/Hire)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings</t>
         </is>
       </c>
     </row>
@@ -2125,17 +2150,17 @@
           <t>Real host payout</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Released deliberately by admin, net of the host's own commission — the same CHS-mediated pattern used for sale-proceeds release.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Deposits &amp; payouts</t>
         </is>
@@ -2147,17 +2172,17 @@
           <t>Two-way ratings</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Guest and host can each rate the other once, after a confirmed stay.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Guest dashboard; Host dashboard</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2169,17 +2194,17 @@
           <t>Real, stated cancellation policy</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Server-enforced: full refund 48+ hours before check-in, 50% within 48 hours, none after.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Guest dashboard</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2191,17 +2216,17 @@
           <t>Flexible security deposit</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Host-toggled per listing; applies only to a genuinely first-time guest and auto-waives after their 3rd real rating. Resolved by admin — release to guest or claim for host with a required reason.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>List a property (Shortlet/Hire)</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Deposits</t>
         </is>
@@ -2213,17 +2238,17 @@
           <t>House-rules attestation</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>A guest must now see and check a box agreeing to a property's real house rules before requesting to book — closing a gap where the feature existed for hosts but was invisible to guests.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Shortlet/Hire booking form</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2235,17 +2260,17 @@
           <t>Dispute-filing for Guest and Host</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>A working dispute form already existed for Tenant/Owner; now genuinely reachable from Guest and Host dashboards too.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Guest dashboard; Host dashboard</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Admin → Disputes tab</t>
         </is>
@@ -2257,17 +2282,17 @@
           <t>Developer as a real, separate role</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Could previously register but had no login path and no dashboard at all. Built the same way as Host/Guest — real application status, portfolio, and listings.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>/developer</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2279,17 +2304,17 @@
           <t>Real ID-number field per document type</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Fixed a genuine bug: choosing any ID type other than NIN had nowhere to enter that document's own number — the system was silently saving the person's NIN instead. A real, conditional number field now appears per ID type.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2301,17 +2326,17 @@
           <t>Multi-role KYC review fix</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Admin's document review only ever checked a person's primary role, missing real credentials attached to a secondary role — found and fixed against a real, in-house test case.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Admin → Registrations tab</t>
         </is>
@@ -2323,17 +2348,17 @@
           <t>Fresh, live document links</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Document links previously relied on a URL signed once and stored permanently — a real structural fragility. Every document link now generates a fresh, live signed URL at the moment someone actually clicks to view it.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Throughout admin and owner/host document review</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2345,17 +2370,17 @@
           <t>Property reference numbers and admin search</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Every property now has a real, permanent reference number (PROP-000001 style), backfilled for every existing property. A real admin search finds any property by reference, title, or the real owner's name/phone.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Admin → Properties tab</t>
         </is>
@@ -2367,17 +2392,17 @@
           <t>Real PIN reset</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Phone + NIN verification, since the platform has no email/SMS infrastructure. Did not exist in any form before this.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Login page → Forgot your PIN?</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2389,17 +2414,17 @@
           <t>Real FAQ page</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Written from CHS's own actual Terms &amp; Conditions and features, not copied from another platform.</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>More menu → Help &amp; FAQs</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2411,17 +2436,17 @@
           <t>Add a role without logging out, plus a role switcher</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>An already-authenticated session now skips the phone/PIN re-verification entirely when adding a role. Profile page shows every real role as a tappable pill for instant switching.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Profile page → Add another role</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2433,17 +2458,17 @@
           <t>Desktop splash screen fix</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Reproduced directly with a real screenshot before fixing — a background image built for a phone's tall aspect ratio was being cropped into an unrecognizable dark sliver on a wide desktop screen. Mobile confirmed untouched.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Login page (first load)</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2455,17 +2480,17 @@
           <t>Four new per-role color themes</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Host, Guest, Developer, and Staff — previously quietly borrowing another role's colors — now each have their own genuinely distinct color identity.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>/host; /guest; /developer; /staff</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2485,13 +2510,13 @@
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -2519,17 +2544,17 @@
           <t>Redesigned receipt and payment voucher</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>A real, branded document — gradient header, a genuine watermark seal, proper serif typography — replacing a plain data table, per direct client feedback.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>/receipt/[reference]</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2541,17 +2566,17 @@
           <t>Real, tiered artisan commission</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>6% for labor under ₦100,000, 8.5% at or above, on labor only — never on materials procured separately. Replaces an earlier flat 10%.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>N/A — automatic on job payment</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2563,17 +2588,17 @@
           <t>Marketplace: admin-mediated, contact-filtered messaging</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Every quote request and vendor response is held for real CHS review — a phone number or email in either direction is caught and blocked automatically — before the other party ever sees it.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Marketplace → Request a quote</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Admin → Marketplace Moderation</t>
         </is>
@@ -2585,17 +2610,17 @@
           <t>Marketplace: real, escrow-backed payment</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Accepting an approved quote charges the buyer the real price plus 6%, held in escrow; the vendor receives the price net of 4% only once CHS confirms delivery. Full refund available if a deal falls through.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>My Requests → Accept &amp; Pay</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Admin → Marketplace Moderation</t>
         </is>
@@ -2607,17 +2632,17 @@
           <t>Marketplace: real direct "Buy Now"</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Sort by price and buy the cheapest listing directly at its own fixed price — no negotiation, no messages to moderate. Same real 6%/4% split and escrow protection.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Marketplace → Buy now</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Admin → Marketplace Moderation</t>
         </is>
@@ -2629,17 +2654,17 @@
           <t>Sister marketplace link (Unify Market Central)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>A real, admin-editable link for procurement CHS's own marketplace doesn't cover — still real, verified sellers, still under CHS's own jurisdiction.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Marketplace; Construction Roadmap; Owner → Maintenance</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Admin → Overview → Edit Real Contact Details</t>
         </is>
@@ -2651,17 +2676,17 @@
           <t>Rental application: real applicant detail shown to owner</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>The owner's review card previously showed only the guarantor's name, phone, and move-in date. Now shows the applicant's real name, ID-verified status, occupation, income, employer, and current address — every field already being collected, now actually displayed.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Owner dashboard → Rental applications</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2673,17 +2698,17 @@
           <t>Independent guarantor verification</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>The applicant provides only the guarantor's name and phone. The guarantor completes every other real field about themselves — address, occupation, relationship, their own ID, and their own typed-name consent — via a private, single-use link, requiring no CHS account. The application cannot reach the owner until this is done.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>New applicant flow → real link sent to guarantor → /guarantor-confirm/[token]</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2695,17 +2720,17 @@
           <t>Event Centre: real capacity tiers and priced facilities</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Real, host-set price tiers by guest count, and a real priced facilities list (lighting, sound, catering per guest, live band, DJ, decoration, generator, security, parking attendants, ushers/event staff) with a live-calculated quotation as the guest selects.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Event Centre booking form</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Host → Real Event Pricing (/event-pricing/[propertyId])</t>
         </is>
@@ -2717,17 +2742,17 @@
           <t>Event-day add-on requests</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>A real request for music band, caterer, and/or ushers (with a count) on any hire/event booking, visible directly on the host's own dashboard.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Hire/Event booking form</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2739,17 +2764,17 @@
           <t>Real payment regression fixes — rent and Rent-to-Own</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Both previously charged only the base amount, silently omitting the payer's own real, already-invoiced commission. Both now compute and charge the true total in one real payment, shown to the payer beforehand.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Tenant dashboard → Pay rent; Rent-to-Own installment payment</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2761,17 +2786,17 @@
           <t>Stale, uncollected commission alert</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>A real, visible warning on Admin → Finance for any commission invoiced but genuinely uncollected for 2+ hours — an early warning against the exact regression pattern found and fixed above.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Admin → Finance</t>
         </is>
@@ -2783,17 +2808,17 @@
           <t>Clickable notifications with real navigation</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>A rental application's full decision chain — owner decides, CHS relays, tenant is told — now carries a real, working link at every step, straight to the relevant page.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Notification bell, any role</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Notification bell</t>
         </is>
@@ -2805,17 +2830,17 @@
           <t>Real-time notification delivery</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>The notifications table is now genuinely part of Supabase's real-time publication — confirmed missing before, and the actual cause of alerts never appearing without a manual refresh. A real, visible toast now appears the instant a new notification arrives.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Any dashboard, any role</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Any dashboard</t>
         </is>
@@ -2827,17 +2852,17 @@
           <t>My Applications</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Every real rental application and purchase offer a buyer/tenant has made, queued permanently the moment they apply — no more scrolling the homepage to find it again.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>/my-applications</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2849,17 +2874,17 @@
           <t>Recent Applications (owner)</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Every real application received across every property, most recent first, regardless of how far down the property list it sits.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Owner dashboard → Recent Applications</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2871,17 +2896,17 @@
           <t>Platform Earnings</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>A real, dedicated view of every collected commission — payer name, amount, and timestamp.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Admin → Platform Earnings</t>
         </is>
@@ -2893,17 +2918,17 @@
           <t>Rent Savings relocated</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Confirmed the tenant dashboard already showed this correctly; removed the redundant duplicate from the general homepage.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Tenant dashboard</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2923,13 +2948,13 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -2957,17 +2982,17 @@
           <t>Admin review gate: rental applications and offers, both directions</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>A buyer's offer, and separately an owner's accept/decline decision on that offer, previously reached the other party directly with zero CHS review. Real 'awaiting admin review' and 'owner decided, pending relay' statuses now gate both, matching the marketplace's own real pattern.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Offer submission; owner's accept/decline</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Admin → Offer Review</t>
         </is>
@@ -2979,17 +3004,17 @@
           <t>Buyer bio-data required at offer submission</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Real name, phone, occupation, and source of funds — previously an offer required none of this. Shown to admin for real verification; deliberately kept off the owner's own screen, where contact stays mediated through the real message thread instead.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Property page → Make an offer</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Admin → Offer Review</t>
         </is>
@@ -3001,17 +3026,17 @@
           <t>Real document review at the point of listing approval</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>The screen where admin approves a new listing previously showed only the title and location, with zero visibility into the real uploaded legal documents. Every document now shows directly on the approval card, with its own view link and verify/reject action — and for Sale properties, the 'Verify' button is genuinely disabled, not just a warning, until every document and the owner's own ID are confirmed verified.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Admin → Properties</t>
         </is>
@@ -3023,17 +3048,17 @@
           <t>Category-aware bedroom display</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Land and other non-residential categories no longer show a bedroom count, regardless of what any individual record's data happens to contain — a real, permanent, shared safeguard rather than a one-off data fix.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Any property listing/detail page</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3045,17 +3070,17 @@
           <t>Real bedroom/bathroom/toilet/room dropdowns</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Replacing plain number inputs with real, selectable dropdowns; a genuinely new, separate toilets count (previously conflated with bathrooms); a repeatable 'Others' facility field for anything not covered.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>List a property</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3067,17 +3092,17 @@
           <t>Processed History</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>A real, permanent archive of every rental application, offer, property listing, and registration CHS has ever decided on — nothing disappears once approved or rejected, the same principle as an old message staying in a real inbox.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Admin → Processed History</t>
         </is>
@@ -3089,17 +3114,17 @@
           <t>Audit Trail</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>A real, permanent, tamper-evident log — no update or delete permission exists for anyone, by design. Covers property decisions, dispute rulings, escrow fund release, account suspension, every admin relay action, referral payouts, marketplace moderation, and agent management changes. Genuinely ongoing — not yet every action in the app.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Admin → Audit Log</t>
         </is>
@@ -3111,17 +3136,17 @@
           <t>Feature Explainer (InfoTip)</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>A real, reusable, mobile-first tap/hover explainer, live on 16+ previously-confusing terms across buyer, owner, and tenant screens — commission, escrow, guarantor, CHS Agent ID, rent auto-pay, and others. Genuinely ongoing across the app's 100+ features.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Throughout the app, next to the relevant term</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3133,17 +3158,17 @@
           <t>Property manager listing access</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Managers previously could not list a property at all; agents already could. Fixed to match the identical, existing pattern — no separate database restriction ever existed, only a frontend role gate that had never included managers.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>List a property</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3155,17 +3180,17 @@
           <t>Real room-video system</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>A genuine, cost-free alternative to a paid virtual-tour service. Record or upload a short, real video per room on a new or existing listing; a buyer/tenant can request a specific additional video if unsatisfied, and track that request's real status. Every video plays directly on the property page.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>List/edit a property; Property page → Request a video</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3177,19 +3202,347 @@
           <t>Document Site</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Every current reference document — User's Guide, Terms &amp; Conditions, Feature Catalog, Handover Notes, Fix Tracker, Property Manager Guide, System Documentation — bundled directly into the app for one-tap download.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Admin → Document Site</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>How it works</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Where to find it (user)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Where to find it (admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Availability calendar for guests</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Before asking to book, a guest sees every date as available (green, with ‘n left’ where a place has several rooms), requested by another guest (amber, may reopen) or booked (red, crossed out). A guest can check out on the day the next guest arrives. A banner guides the steps — tap arrival, then departure; tapping a later date extends the stay, a date inside it shortens it, and Clear dates resets. It refreshes every minute and clears chosen dates that someone else takes meanwhile, with an explanation. Guests see dates and counts only, never another guest's details. Event centres and halls use the same calendar one day at a time.</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Property page → booking form — Buyer / Guest</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Rooms and room types</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Each hotel, lodge, shortlet or venue listing has individual rooms, grouped into types (Executive, Standard…) with an optional own nightly price and maximum guests. Hosts create rooms in bulk (type “101-112, 201, 204”). A guest picks a type and the system assigns a free room, named in My Bookings once the booking is paid.</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Host dashboard → Rooms &amp; calendar</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Double-booking guard</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Two guests can never hold the same room on the same night — enforced inside the database, so no screen, timing or shortcut can get around it. Back-to-back stays are allowed. The dates are held from the moment a request is sent, before anything else happens; if they are gone the request fails and the guest is not charged.</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Automatic — every booking</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Host Rooms &amp; Calendar console</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>A hotel-style chart (rooms down the side, 14 days across). The host records walk-in guests, blocks rooms, or marks every free room unavailable for a period (“Fully booked or closed”). A guest's booking or request cannot be deleted from here; a room with upcoming guests cannot be switched off. One tap — “My calendar is accurate” — confirms a listing, or all of a host's listings at once. A listing's placeholder room can be renamed to a real room number.</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Host dashboard / Owner dashboard → Rooms &amp; Calendar</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings → stale-calendar alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Calendar reminders and stale-calendar alert</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Hosts receive a reminder at 7 am Nigerian time, once a day, until they confirm their calendar. Admin sees a red list of every active hotel, lodge or venue whose calendar has not been confirmed in 3+ days, with the host's phone, number of rooms and pending requests.</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Host notification</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Request-first booking order</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>The guest sends a request and nothing is charged; CHS relays it to the host; the host confirms the dates are free; the guest then pays within a short window; only then are the dates confirmed. The price is fixed when the request is sent. Every stage holds the dates and has a deadline; overdue stages settle themselves every 5 minutes (an unanswered or unpaid request lapses with nothing to refund; an older request paid at request time is refunded exactly).</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Property page → My Bookings — Buyer / Guest</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Urgency lanes and time limits</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>How long each step may take depends on how soon the stay starts (Nigerian time). Standard (more than 3 days away): CHS relays within 4 hours at most, the host has 24 hours, the guest 6 hours to pay. Soon (1–3 days): 30 minutes, 6 hours, 2 hours. Express (today): 10 minutes, 30 minutes, 20 minutes, and an expected arrival time is required. For Soon and Express the guest's wallet must already hold the full amount when the request is sent. Every figure is an adjustable setting.</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Booking form + My Bookings</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Platform settings (booking_*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Admin relay queue</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Every request comes to CHS first, in every lane — guest and host never deal directly. The queue lists requests in three groups (waiting to be relayed, with the host, waiting for the guest to pay), urgent first and in red, each with a countdown and the host's phone number. Admin relays with one tap and an optional note, or declines with a reason (the guest pays nothing). A short automatic relay remains only as a safety net if nobody acts, with an alert to admin.</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Pay-now card and live countdown</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>My Bookings and the Guest dashboard show where a booking stands in plain words with a live countdown. When the host confirms, a green card shows the exact amount and breakdown with a Pay now button; a wallet shortfall gives a clear message and a Top up link. An unpaid request can be withdrawn at any time at no cost. The page after sending a request says “Request sent — nothing has been charged”.</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>My Bookings / Guest dashboard</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Host requests panel</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>A red panel at the very top of both the Owner and Host dashboards lists every request awaiting the host: the hotel, the guest's name with a CHS identity-verified mark and a CHS reference (never their phone number or ID), dates, expected arrival, what the host would receive, a countdown, and Confirm — dates are free / Decline. Urgent requests are flagged. The notification links to the right dashboard for the person's role.</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Owner dashboard / Host dashboard (top)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Message review and contact-detail filter</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Messages between a guest and a host are reviewed by CHS before delivery until the booking is paid (one setting keeps review on for paid bookings too); the other side cannot read an unreviewed message, even by querying the database; messages cannot be written into the table directly. Phone numbers and email addresses are refused for everyone, always. The shared filter ignores ordinary dates, times and numbers but still catches disguised numbers, and also protects offers and the marketplace.</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>My Bookings / Host dashboard (Messages)</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings → message review</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Payment, commission and payout</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>The guest pays price + CHS service fee (+ a refundable deposit where required), held in escrow. Both CHS commissions — the guest's and the host's — are recorded as collected at the moment the guest pays, as with rent and sale. Both payout routes — the guest confirming check-in, and admin's Release — go through one routine that refuses anything not actually held and pays the host the price net of CHS's commission.</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Wallet / My Bookings</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Escrow Oversight; Platform Earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Cancellation and refunds</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>An unpaid request is withdrawn at no cost. A paid booking cancelled 48+ hours before check-in is refunded in full (and CHS keeps no commission); within 48 hours, 50%; on or after check-in, none; a booking the host never confirmed is always refunded in full; a security deposit is always returned. The part not refunded is split: the unrefunded stay price goes to the host as compensation for the dates held (less CHS's commission on it; the host's share is a setting, default 100%) and CHS keeps its service fee on it. The guest, host and admin are each told the exact amounts, and refund + host + CHS always equals what was paid. If a host fails to honour a confirmed booking, term 36 applies instead.</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>My Bookings / Guest dashboard</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Escrow Oversight</t>
         </is>
       </c>
     </row>
@@ -3207,13 +3560,13 @@
   <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -3241,17 +3594,17 @@
           <t>Location + price search</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Filter by state, LGA, area, property type, minimum bedrooms, and a real minimum/maximum price range.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Homepage search — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -3263,17 +3616,17 @@
           <t>Rent / Sale / Shortlet tabs</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Real filtering of the whole catalog by purpose.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Homepage — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3285,17 +3638,17 @@
           <t>Saved Properties &amp; Saved Searches</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Save individual listings, or save a whole search to be matched automatically as new listings arrive.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Saved page — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -3307,17 +3660,17 @@
           <t>Making an offer (sale)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Propose a real price directly to the owner; goes through a real CHS Sale Approvals checkpoint before anything moves to escrow.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Property detail page — Buyer</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Admin → Sale Approvals (Owner/Buyer/Tenant domain)</t>
         </is>
@@ -3329,17 +3682,17 @@
           <t>Rental application + independent guarantor confirmation</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>A real application, screened by CHS staff before the owner ever sees it. The applicant provides only their guarantor's name and phone number; the guarantor completes everything else — address, occupation, their own ID, a real proof of address, and a signed confirmation — independently, through their own private link, and cannot share the applicant's surname.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Property detail page — Tenant; guarantor's own link</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Admin → Applications (Owner/Buyer/Tenant domain)</t>
         </is>
@@ -3351,17 +3704,17 @@
           <t>Inspection booking + transport fee</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Real fee calculated per-person based on distance; a genuine 12-hour minimum notice enforced by the database itself.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Property detail page — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Admin → Inspections (Owner/Buyer/Tenant domain)</t>
         </is>
@@ -3373,17 +3726,17 @@
           <t>Buyer/Tenant Readiness Score</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>A real questionnaire (timeline, funds ready, decision-maker) plus verification and inspection-attendance history — shown to owners, never a fee or gate.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Inspection booking form — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>N/A — computed live</t>
         </is>
@@ -3395,19 +3748,19 @@
           <t>Shortlet booking</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Paid instantly through the wallet, held in real escrow until check-in is confirmed. Real guest verification required.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Property detail page — Buyer / Tenant</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Booked request-first: the guest picks dates on the availability calendar and sends a request — nothing is charged. CHS passes it to the host, who confirms the dates are free; the guest then pays within a short window and the payment is held in escrow until check-in is confirmed. Real guest verification required. See section 16 for the full flow.</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Property detail page → My Bookings — Buyer / Guest</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings</t>
         </is>
       </c>
     </row>
@@ -3417,17 +3770,17 @@
           <t>Rent-to-Own</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Where offered, a real monthly amount counting toward eventual ownership, shown directly on the listing.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Property detail page — Buyer</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>N/A — set by owner at listing time</t>
         </is>
@@ -3439,17 +3792,17 @@
           <t>House Rules acknowledgment</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>A real, documented agreement a tenant acknowledges as part of their tenancy.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Tenant dashboard, per tenancy</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>N/A — set by owner</t>
         </is>
@@ -3461,17 +3814,17 @@
           <t>Property Condition Report</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Documented and photographed at move-in — real evidence-based liability instead of a caution-fee guess.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Condition Report page — Tenant</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -3483,17 +3836,17 @@
           <t>Formal Notices</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Real formal communications (e.g. rent reminders, lease notices) from owner/CHS, viewable and expandable.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Tenant dashboard</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>N/A — sent by owner/CHS</t>
         </is>
@@ -3505,17 +3858,17 @@
           <t>Owner–tenant message thread</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>A real, direct messaging channel per tenancy.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Tenant dashboard, per tenancy</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -3527,17 +3880,17 @@
           <t>Raise a Dispute</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>A real, two-sided dispute process — CHS's internal resolution is the first step before arbitration or courts.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Tenant dashboard + Owner dashboard</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Admin → Disputes (Customer Care domain)</t>
         </is>
@@ -3549,17 +3902,17 @@
           <t>Talk to an Agent (Concierge)</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Describe a property need in free text or voice instead of using search filters — a real request CHS follows up on personally.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Bottom nav → Property request — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Admin → Concierge, within Owner/Buyer/Tenant domain</t>
         </is>
@@ -3571,17 +3924,17 @@
           <t>Urgent &amp; Emergency Sale browsing</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Real, discounted, time-boxed listings shown in a dedicated homepage row with the real deadline.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Homepage — Buyer</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>N/A — browsing only</t>
         </is>
@@ -3593,17 +3946,17 @@
           <t>Market data (average prices, demand trend)</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Real, genuine data (not placeholder figures) on current prices and search-driven demand patterns.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Bottom nav → Average prices / Demand trend</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -3615,17 +3968,17 @@
           <t>Engage CHS — buy a construction project</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Full request flow with real specifications, document checklist, two-way chat, and the Construction Roadmap tool.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Engage CHS page — Buyer / Owner</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Admin → Engage CHS (Super Admin only)</t>
         </is>
@@ -3637,19 +3990,19 @@
           <t>Hotel, Event Centre, Hall, Car Park, Cinema &amp; Recreational/Sports booking</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>A real, instant "Book now" flow — not a rental application — for any genuine guest venue, correctly categorized and commissioned. A business-lease "hire" listing (e.g. a filling station) correctly stays on the rental-application path instead.</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Property detail page — Buyer / Guest</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>N/A — self-service</t>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>A real request-first booking flow — not a rental application — for any genuine guest venue, correctly categorized and commissioned: send a request (nothing charged), CHS relays it, the venue confirms, the guest pays within a short window. A business-lease “hire” listing (e.g. a filling station) correctly stays on the rental-application path instead.</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Property detail page → My Bookings — Buyer / Guest</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings</t>
         </is>
       </c>
     </row>
@@ -3659,17 +4012,17 @@
           <t>Auto-pay rent from a dedicated savings wallet</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>An optional, real toggle — rent pays itself the moment it's due from a separate Rent Savings balance, or stays fully manual if left off.</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Tenant dashboard, per tenancy</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -3681,17 +4034,17 @@
           <t>Rent held in real escrow</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Paid rent is not released to the landlord immediately. Held until the tenant files a genuinely clean move-in report, or 14 days pass with nothing raised — the same real protection a buyer's money gets. An open fault or a flagged report item pauses release for admin review.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Tenant &amp; Owner dashboards, wallet — Tenant / Owner</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Admin → Escrow Oversight (Owner/Buyer/Tenant domain) — release early, or review a flagged hold</t>
         </is>
@@ -3703,17 +4056,17 @@
           <t>Subsequent-year rent — no repeat tenant commission</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>The system now genuinely knows a renewal from a first payment. From year two onward, the tenant pays CHS nothing further — only the landlord, at a real, reduced 3%. Shown live on both the tenant's and owner's rent countdown.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Tenant &amp; Owner dashboards, rent countdown</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>N/A — automatic</t>
         </is>
@@ -3725,17 +4078,17 @@
           <t>Move-out condition report + real court affidavit</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>A genuine move-out counterpart to the existing move-in report, with a real, required court-issued affidavit upload — now actually visible to the landlord, which it never was before.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>Condition Report page — Tenant; visible on Owner dashboard</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -3747,17 +4100,17 @@
           <t>Non-renewal notice with a real message</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>A genuine optional message sent to the landlord along with the notice — previously a bare, wordless click.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Tenant dashboard, per tenancy</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -3769,17 +4122,17 @@
           <t>Real street address on every listing</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>A required, specific address (e.g. "House 12, Shagari Road") — not just a general neighborhood — visible on the tenant's own dashboard and usable for real fault/payment tracing.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>List a property form; Tenant dashboard</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Admin analytics, traceable by real address</t>
         </is>
@@ -3799,13 +4152,13 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -3833,17 +4186,17 @@
           <t>List a property</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Photos, location, price, purpose, bedrooms, and special terms (rent-to-own, house rules). Starts unverified.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Owner dashboard → List a property</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Admin → Properties (Owner/Buyer/Tenant domain)</t>
         </is>
@@ -3855,17 +4208,17 @@
           <t>Property verification</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>CHS reviews every listing before it's publicly visible — the real meaning behind "CHS Verified."</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Admin → Properties (Owner/Buyer/Tenant domain)</t>
         </is>
@@ -3877,17 +4230,17 @@
           <t>Fixed-tier promotion (7/30/90-Day Boost)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>One-off paid tier, debited directly from the wallet.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Promote page, per listing</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -3899,17 +4252,17 @@
           <t>Credit-based promotion (pause anytime)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Real, shared credit balance across every listing; each listing charged separately per real day it's on, based on real location/size cost. Real ranking (Category A–D + literal Top 10/20 position) against the same real local market.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Promote page, per listing</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>N/A — automatic, database-driven</t>
         </is>
@@ -3921,17 +4274,17 @@
           <t>Urgent &amp; Emergency Sale activation</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Requires the listing already verified and owner ID-verified. Real original price, discount, and deadline shown to buyers.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Owner dashboard → 🚨 Urgent Sale</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Notified via general notifications on activation</t>
         </is>
@@ -3943,17 +4296,17 @@
           <t>Managing offers &amp; rental applications</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Real accept/reject decisions on real, CHS-screened offers and applications.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Admin → Sale Approvals / Applications</t>
         </is>
@@ -3965,17 +4318,17 @@
           <t>Inspection management + Readiness Score visibility</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>See each real requester's readiness score; mark real attendance/no-show after the scheduled time passes.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Owner dashboard, per property</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Admin → Inspections</t>
         </is>
@@ -3987,17 +4340,17 @@
           <t>Delegating to a Property Manager</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Hands maintenance and certain approvals to a registered Manager; reversible any time.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4009,17 +4362,17 @@
           <t>Property analytics</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Real view counts, inspection counts, and interest counts — not fixed placeholder numbers.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Analytics page, per listing</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4031,17 +4384,17 @@
           <t>Editing a live listing</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Real edits to an already-published property.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Edit listing page</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4053,17 +4406,17 @@
           <t>Engage CHS for a professional service</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Full Property Management, Sale Negotiation, Construction Monitoring, Project Management, Renovation — each with its own real terms and fee schedule.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Engage CHS page — Owner</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Admin → Engage CHS (Super Admin only)</t>
         </is>
@@ -4075,17 +4428,17 @@
           <t>Download verified sale documents</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>The actual, CHS-verified legal documents (Certificate of Occupancy, Deed of Assignment, etc.) genuinely downloadable by a paying buyer directly — previously only ever tracked as a physical-dispatch status with no real digital access.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Property detail page, after payment — Buyer</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4097,17 +4450,17 @@
           <t>Accept an offer at negotiated terms, mid-chat</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>A real conversion point that didn't exist before — accept at a different final price than the original offer, with an optional condition (e.g. a payment deadline), directly from the ongoing negotiation.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Owner dashboard, per offer</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4127,13 +4480,13 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -4161,17 +4514,17 @@
           <t>Unique referral link</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>A real code (e.g. CHS-AG-0024) automatically attached to every property link generated — always opens the property directly on CHS.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Agent dashboard</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4183,17 +4536,17 @@
           <t>Automatic commission attribution</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>If a referred visitor completes a real transaction on that property, CHS automatically attributes and credits the commission.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Agent dashboard</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Admin → Referral fees (Agent Relations domain)</t>
         </is>
@@ -4205,17 +4558,17 @@
           <t>Real referral tracking (masked for privacy)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Real deal stage, earnings this month, and total earned — served from a privacy-conscious masked view.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Agent dashboard</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Admin → Referral fees</t>
         </is>
@@ -4227,17 +4580,17 @@
           <t>Managing an agent-managed property's own commission</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>For a property under full agent authority, set your own real market rate (e.g. 10-15%) with the client — CHS charges the client nothing extra, taking a real, capped 3% only from your own earnings.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Agent dashboard, per managed property</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4249,17 +4602,17 @@
           <t>Per-owner commission rate — one real, standing rate</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>A genuine, editable rate per real owner relationship, not re-entered per property — reviewable and adjustable any time, applying automatically to every property you manage for that owner, including new ones.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Agent dashboard → Your Real Commission Rate Per Owner</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4271,17 +4624,17 @@
           <t>Digital remittance to an owner's wallet</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Rent collected in person, remitted straight into the real owner's wallet with your agreed commission auto-deducted — a real, permanent reference either side can point to.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Agent dashboard → Remit Collected Rent to an Owner</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Admin → Finance, real remittances table</t>
         </is>
@@ -4293,17 +4646,17 @@
           <t>A real tenant register</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Full biodata, property details, and a real auto-generated reference number (e.g. TEN-000001) for every tenant you manage — plus real ID and selfie verification.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>My Tenant Register page</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4315,17 +4668,17 @@
           <t>A real mini-admin — your own team</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Add real, separate staff accounts by phone number, assign a role, and see their genuine daily activity reports — the same kind of oversight CHS itself runs on.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Agent dashboard → Manage My Team</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4337,17 +4690,17 @@
           <t>Multiple linked bank accounts</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Up to 4 real, Paystack-verified bank accounts — a genuine business need for agents working across multiple banking relationships, unlike every other role which stays single-account.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Profile → Linked bank accounts</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4359,17 +4712,17 @@
           <t>Expenses &amp; income tracking</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Real salary, rent, transport, logistics, and commission income entries — a genuine net position, not just a spending log.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>My Expenses &amp; Income page</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4381,17 +4734,17 @@
           <t>My real activity report</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>A genuine, date-range (week/month/quarter) report of commission earned, deals closed, and tenancies managed.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Agent dashboard → Generate my activity report</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4411,13 +4764,13 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -4445,17 +4798,17 @@
           <t>Delegated property management</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Owners can delegate specific properties; maintenance and certain approvals route to the manager directly.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Manager dashboard</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4467,17 +4820,17 @@
           <t>Management termination</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>An owner can reverse delegation any time, handing responsibilities back.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Owner dashboard (trigger) / Manager dashboard (effect)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4489,17 +4842,17 @@
           <t>Posting a maintenance job for quotation</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Real job posts that verified artisans can quote on, ranked by a transparent rating/reliability/experience/equipment formula.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Manager dashboard</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Admin → Maintenance (Artisan/Developer/PM/Vendor domain)</t>
         </is>
@@ -4511,17 +4864,17 @@
           <t>Rating an artisan</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Real, genuine ratings after a completed job.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Manager dashboard, per completed job</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4533,17 +4886,17 @@
           <t>Owner-occupier support in estates</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Register a real occupant who owns their unit outright (no tenancy) alongside genuine tenants in the same estate — correctly counted in occupancy and included in service-charge billing.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Manager dashboard, per estate unit</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4555,17 +4908,17 @@
           <t>Per-owner commission rate, digital remittance, tenant register, mini-admin team, multiple bank accounts, expenses tracking</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Every real business tool built for agents this round applies identically to managers — the same standing per-owner rate, the same digital remittance, the same tenant register and team system.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Manager dashboard — same real pages as Agent</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4577,17 +4930,17 @@
           <t>My real activity report — across all my estates</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>A genuine, date-range report of new tenancies, service charges billed and collected, and maintenance resolved across every estate you manage.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>My Estates page → Generate my activity report</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4607,13 +4960,13 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -4641,17 +4994,17 @@
           <t>Developer registration &amp; review</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>A real application reviewed by CHS before projects go live.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Register / Developer dashboard</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Admin → Developers (Artisan/Developer/PM/Vendor domain)</t>
         </is>
@@ -4663,17 +5016,17 @@
           <t>Listing development projects</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Estates, instalment plans, and investment plans.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Developer dashboard</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Admin → Developers</t>
         </is>
@@ -4693,13 +5046,13 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -4727,17 +5080,17 @@
           <t>Vendor registration &amp; verification</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Reviewed by CHS before listings go live — the same trust standard applied platform-wide.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Become a Vendor / Vendor dashboard</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Admin → Vendors (Artisan/Developer/PM/Vendor domain)</t>
         </is>
@@ -4749,17 +5102,17 @@
           <t>Listing products &amp; bundles</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Real materials/services catalog, browsable by category on the Marketplace.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Vendor dashboard (list) + Marketplace page (browse)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4771,17 +5124,17 @@
           <t>Service quote requests</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Real incoming requests for a quote on a specific service.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Vendor dashboard</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4793,17 +5146,17 @@
           <t>Referral fee tracking</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Real fees on deals connected through the Marketplace.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Vendor dashboard</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Admin → Referral fees</t>
         </is>
@@ -4823,13 +5176,13 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -4857,17 +5210,17 @@
           <t>Artisan registration &amp; verification</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Real trades, years of experience, certification, and equipment tier (with photo/receipt backing) — reviewed before quoting is allowed.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Become an Artisan / Artisan dashboard</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Admin → Artisans (Artisan/Developer/PM/Vendor domain)</t>
         </is>
@@ -4879,17 +5232,17 @@
           <t>Quoting on maintenance jobs</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Real quotes ranked by a transparent formula: rating/reliability first, experience second, equipment third.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Artisan dashboard</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Admin → Maintenance</t>
         </is>
@@ -4901,17 +5254,17 @@
           <t>Full-management job priority</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>For any property under full CHS management, maintenance work goes first and exclusively to verified CHS Maintenance Agents.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Automatic — Artisan</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>N/A — automatic</t>
         </is>
@@ -4923,17 +5276,17 @@
           <t>Job dispute resolution</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Either the artisan or the client can raise a genuine, two-sided dispute about a completed job.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Artisan dashboard</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Admin → Disputes</t>
         </is>
@@ -4945,17 +5298,17 @@
           <t>Ratings received</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Real, visible rating history.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Artisan dashboard</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4975,13 +5328,13 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Feature</t>
@@ -5009,17 +5362,17 @@
           <t>Super Admin role</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>One real account, practically involved in every part of the platform — handles Finance and Engage CHS directly, and ratifies every sub-admin's high-stakes decision.</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Admin dashboard</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Admin → Overview</t>
         </is>
@@ -5031,17 +5384,17 @@
           <t>Five real sub-admin domains</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Customer Care, Registration &amp; Setup, Owner/Buyer/Tenant, Agent Relations, Artisan/Developer/PM/Vendor — each sub-admin only sees and acts within their own domain, enforced at the database level.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Admin dashboard, tab-gated per domain</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Admin → Overview → Assign an admin role</t>
         </is>
@@ -5053,17 +5406,17 @@
           <t>Code-based admin login approval</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>A sub-admin's correct password alone isn't enough — a real code is generated and sent to the Super Admin, who must approve that specific login.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Sub-admin login flow</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Admin → Overview — pending login approvals</t>
         </is>
@@ -5075,17 +5428,17 @@
           <t>High-stakes approval queue</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Routine sub-admin actions apply immediately; financial and verification decisions are held pending real Super Admin sign-off.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Admin dashboard, across relevant tabs</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Admin → Overview — pending sub-admin actions</t>
         </is>
@@ -5097,17 +5450,17 @@
           <t>Trace an Account</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Search any real user by phone/email/name and see their full wallet balance + transaction history, promotion credits + active promotions, construction roadmap unlocks, linked bank account, and Engage CHS requests — all in one place. The real fix for resolving a support issue ("I paid but nothing happened") the way a phone network traces an account from just a phone number.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Admin → 🔎 Trace an Account (Super Admin only)</t>
         </is>
@@ -5119,17 +5472,17 @@
           <t>Sub-admin action history</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>A real, permanent audit log of every resolved sub-admin request — previously, once approved or rejected, a request simply vanished with no record.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Admin → Overview → View sub-admin action history</t>
         </is>
@@ -5141,17 +5494,17 @@
           <t>Pre-launch admin test mode</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Super Admin can preview any real dashboard using their own account, never a real user's data, with a visible banner the whole time.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>N/A — testing tool</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Admin → Overview → Switch role for testing</t>
         </is>
@@ -5163,17 +5516,17 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Search any real user's wallet, view all three real balances, freeze/unfreeze.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Admin → Finance</t>
         </is>
@@ -5185,17 +5538,17 @@
           <t>Sale Approvals</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>The real checkpoint between an accepted offer and money moving to escrow.</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Admin → Sale Approvals</t>
         </is>
@@ -5207,17 +5560,17 @@
           <t>Face Verification (Liveness)</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Real human review of each real-time capture.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Admin → Face Verification</t>
         </is>
@@ -5229,17 +5582,17 @@
           <t>Registrations</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Approve or reject new real accounts.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Admin → Registrations</t>
         </is>
@@ -5251,17 +5604,17 @@
           <t>Applications</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Real rental application review before an owner ever sees it.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Admin → Applications</t>
         </is>
@@ -5273,17 +5626,17 @@
           <t>Properties</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Real listing verification before it's publicly visible.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Admin → Properties</t>
         </is>
@@ -5295,17 +5648,17 @@
           <t>Disputes</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Real, two-sided dispute resolution across tenancies and artisan jobs.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Admin → Disputes</t>
         </is>
@@ -5317,17 +5670,17 @@
           <t>Feedback</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>General platform suggestions/complaints, not tied to a specific transaction.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Admin → Feedback</t>
         </is>
@@ -5339,17 +5692,17 @@
           <t>Engage CHS</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Real professional-service requests: specifications, document checklist, two-way chat, roadmap access — Super Admin only, per direct instruction.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Admin → Engage CHS</t>
         </is>
@@ -5361,17 +5714,17 @@
           <t>Vendors</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Real marketplace vendor verification.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Admin → Vendors</t>
         </is>
@@ -5383,17 +5736,17 @@
           <t>Referral fees</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Real agent/vendor commission tracking and payout, routed through the approval queue.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Admin → Referral fees</t>
         </is>
@@ -5405,17 +5758,17 @@
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Real fault report routing to the right artisan/manager.</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Admin → Maintenance</t>
         </is>
@@ -5427,17 +5780,17 @@
           <t>Artisans</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Real trade/equipment verification before an artisan can quote.</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Admin → Artisans</t>
         </is>
@@ -5449,17 +5802,17 @@
           <t>Inspections</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Real upcoming inspection oversight across the whole platform.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Admin → Inspections</t>
         </is>
@@ -5471,17 +5824,17 @@
           <t>Developers</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Real developer application review.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>Admin → Developers</t>
         </is>
@@ -5493,17 +5846,17 @@
           <t>Real, date-range analytics report</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>A genuine, filterable (today/week/month/quarter) record of properties sold, new tenancies, shortlet bookings, new listings, new users, and total commission revenue by transaction type — not just a live, un-datable snapshot.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>Admin → Analytics</t>
         </is>
@@ -5515,17 +5868,17 @@
           <t>Suspend a real account, with a genuine appeal process</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Suspend by phone number with a required, documented reason; a real appeal queue to approve (reinstate) or deny.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Admin → Overview</t>
         </is>
@@ -5537,17 +5890,17 @@
           <t>CHS staff daily report</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Any real internal admin staff member can submit their own daily activity report, visible to the super admin.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>Admin → Overview → Submit My Daily Report</t>
         </is>
@@ -5559,17 +5912,17 @@
           <t>Critical data-protection fixes</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>A direct security audit found and closed a real, proven exposure — any logged-in user could previously read another user's NIN, phone, and ID documents. Fixed at both the database and file-storage level, re-verified after the fix.</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>N/A — platform-wide</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>See the separate Security Audit report</t>
         </is>
@@ -5581,17 +5934,17 @@
           <t>Missing database indexes added</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Dozens of real foreign-key columns had no index — invisible at small scale, a genuine slowdown waiting to happen as real data grows. Added across every high-traffic table.</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>N/A — platform-wide</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>See the separate Scalability Assessment report</t>
         </is>
@@ -5603,17 +5956,17 @@
           <t>Real, editable Contact Us details</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Four real, distinct contact emails (Support, Inquiry, Engage CHS, Admin) and two real phone numbers — genuinely admin-editable at any time, not hardcoded into the app.</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>More menu → Contact us — every role</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Admin → Overview → Edit Real Contact Details</t>
         </is>

--- a/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
+++ b/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>A genuinely new listing category — progressive ownership through real monthly installments, with real ownership-percentage tracking that automatically completes the sale at 100%.</t>
+          <t>A genuinely new listing category — progressive ownership through monthly instalments, labelled “Mortgage (Rent to Own)” in the app. The buyer must be fully verified and the owner must approve the request. Each instalment is paid from the wallet (instalment + 5.5% buyer commission), the owner is credited at once (instalment − 4.5%), and the buyer's ownership percentage is worked out exactly from what has been paid. The final instalment is only what is still owed. A property can have only one active agreement: approving one buyer declines the other pending requests. At 100% the property is marked sold. The owner sees the buyer's name and a CHS reference, never their phone number.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -3229,7 +3229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3461,86 +3461,130 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Host requests panel</t>
+          <t>Arrival confirmation and prompt payout</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>A red panel at the very top of both the Owner and Host dashboards lists every request awaiting the host: the hotel, the guest's name with a CHS identity-verified mark and a CHS reference (never their phone number or ID), dates, expected arrival, what the host would receive, a countdown, and Confirm — dates are free / Decline. Urgent requests are flagged. The notification links to the right dashboard for the person's role.</t>
+          <t>Booking is prepaid: the guest pays first, and the host is paid when the guest ARRIVES — not after the stay. From the check-in day the guest ticks a short checklist on their booking: they have arrived and can get in, the property matches its listing, each listed facility (or each facility booked, for a venue) is present and working, and everything is in good order, with an optional message. That releases the host's payout at once and sends the message to the host and to CHS. If something is wrong the guest reports a problem instead: the money stays held and CHS and the host are alerted. If the guest says nothing, the payout is released automatically 24 hours after the 2 pm check-in time unless a problem was reported. A host whose guest has arrived can ask CHS to release; CHS sees the request, whether the guest has confirmed, and releases with one tap. Older pay-first bookings are released by CHS from its list.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Owner dashboard / Host dashboard (top)</t>
+          <t>My Bookings / Guest dashboard (guest); Owner &amp; Host dashboards (host)</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Admin → Shortlet/Hire Bookings → stays awaiting release</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Message review and contact-detail filter</t>
+          <t>House rules for hotels, lodges, venues and hosts</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Messages between a guest and a host are reviewed by CHS before delivery until the booking is paid (one setting keeps review on for paid bookings too); the other side cannot read an unreviewed message, even by querying the database; messages cannot be written into the table directly. Phone numbers and email addresses are refused for everyone, always. The shared filter ignores ordinary dates, times and numbers but still catches disguised numbers, and also protects offers and the marketplace.</t>
+          <t>Any shortlet, hotel, lodge, event-centre or other hire listing can carry a House Rules document, uploaded by the owner from the Owner dashboard or by a host from the Host dashboard. Guests must read and acknowledge it before they can send a booking request.</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>My Bookings / Host dashboard (Messages)</t>
+          <t>Owner dashboard / Host dashboard → listing → House rules; booking form (guest)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Admin → Shortlet/Hire Bookings → message review</t>
+          <t>Admin → listing review</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Payment, commission and payout</t>
+          <t>Host requests panel</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>The guest pays price + CHS service fee (+ a refundable deposit where required), held in escrow. Both CHS commissions — the guest's and the host's — are recorded as collected at the moment the guest pays, as with rent and sale. Both payout routes — the guest confirming check-in, and admin's Release — go through one routine that refuses anything not actually held and pays the host the price net of CHS's commission.</t>
+          <t>A red panel at the very top of both the Owner and Host dashboards lists every request awaiting the host: the hotel, the guest's name with a CHS identity-verified mark and a CHS reference (never their phone number or ID), dates, expected arrival, what the host would receive, a countdown, and Confirm — dates are free / Decline. Urgent requests are flagged. The notification links to the right dashboard for the person's role.</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Wallet / My Bookings</t>
+          <t>Owner dashboard / Host dashboard (top)</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Admin → Escrow Oversight; Platform Earnings</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Message review and contact-detail filter</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Messages between a guest and a host are reviewed by CHS before delivery until the booking is paid (one setting keeps review on for paid bookings too); the other side cannot read an unreviewed message, even by querying the database; messages cannot be written into the table directly. Phone numbers and email addresses are refused for everyone, always. The shared filter ignores ordinary dates, times and numbers but still catches disguised numbers, and also protects offers and the marketplace.</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>My Bookings / Host dashboard (Messages)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings → message review</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Payment, commission and payout</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>The guest pays before arriving; CHS holds the money only until the guest arrives and confirms. Both CHS commissions — the guest's and the host's — are recorded as collected at the moment the guest pays, as with rent and sale. The host's net payout is released the moment the guest confirms arrival (see the next entry), by admin on a host's request, or automatically 24 hours after check-in; all three go through one routine that refuses anything not actually held and pays the host the price net of CHS's commission.</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Wallet / My Bookings</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Escrow Oversight; Platform Earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t>Cancellation and refunds</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>An unpaid request is withdrawn at no cost. A paid booking cancelled 48+ hours before check-in is refunded in full (and CHS keeps no commission); within 48 hours, 50%; on or after check-in, none; a booking the host never confirmed is always refunded in full; a security deposit is always returned. The part not refunded is split: the unrefunded stay price goes to the host as compensation for the dates held (less CHS's commission on it; the host's share is a setting, default 100%) and CHS keeps its service fee on it. The guest, host and admin are each told the exact amounts, and refund + host + CHS always equals what was paid. If a host fails to honour a confirmed booking, term 36 applies instead.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>My Bookings / Guest dashboard</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Admin → Escrow Oversight</t>
         </is>

--- a/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
+++ b/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -659,127 +659,127 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Wallet (main + rent savings + maintenance reserve)</t>
+          <t>Payment safety notice — wallet only</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Three real sub-balances per user — a main spending balance plus two dedicated savings pots for rent renewal and maintenance costs.</t>
+          <t>The rule that every payment on CHS is made through the person's own CHS Wallet, and that nobody ever pays a person or a bank account, is shown to everyone: a slim line at the top of every page; a prominent card on the Wallet, Login and Registration pages; and a short line beside every pay button (booking pay cards, rent, rent-to-own, offers, inspections, and wherever the payment-protection notice appears). It is also in the FAQ, the in-app guide and the Users Guide, and was sent to every user as a notification. CHS staff and agents never ask anyone to pay into a personal account or share a PIN.</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Wallet page — every role</t>
+          <t>Every page · Wallet · Login · Registration · beside every pay button</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Admin → Finance — search any user's real balances, freeze/unfreeze</t>
+          <t>N/A — automatic</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Wallet funding via Paystack</t>
+          <t>Wallet security layers (transfers and withdrawals)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Real, secure card/bank/USSD payment; balance updates automatically once payment genuinely completes.</t>
+          <t>Protection that proves the account holder is really the one moving money, and limits the damage if they are not. (1) A separate 6-digit transaction PIN, stored hashed, asked for on every transfer and bank withdrawal once set, locked for 30 minutes after 5 wrong tries (compulsory for everyone once CHS switches it on). (2) Only ID-verified users may send money to another CHS user. (3) Limits: per transfer, per day, per hour, and a lower cap on a first transfer to a new recipient for 24 hours. (4) Money received from another CHS user can be used inside CHS but cannot be withdrawn to a bank for 24 hours. (5) A daily withdrawal limit. (6) Instant alerts to the sender and the recipient; large transfers alert admins. (7) A one-tap Freeze my wallet for the account holder (only CHS can lift it). (8) Report this transfer: the amount is held in the recipient's wallet and admins can reverse it while the money is there. (9) Wallet rows are locked during a transfer and a balance can never go below zero. Every number is a setting. Second tranche: (10) Unfamiliar-device checks — the app registers each device; a device new to the account alerts the holder and, for 24 hours, a transfer or withdrawal from it needs a code texted to the phone (once SMS codes are switched on) or is capped at ₦50,000. (11) Texted one-time codes — 6 digits, hashed, valid 10 minutes, 5 tries, 3 requests per 10 minutes, delivered by SMS only (never shown in the app); required at or above ₦200,000 (transfers) / ₦100,000 (withdrawals) or from a new device when switched on; if the SMS cannot be sent the transaction is refused. (12) Money added by card cannot be withdrawn to a bank for 24 hours. (13) An automatic scan every 15 minutes flags unusual patterns (many senders to one wallet, a new account receiving a lot, money going in circles, rapid outflow, a locked PIN) for an admin to clear or freeze.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Wallet page — every role</t>
+          <t>Wallet → Wallet security; transfer and withdrawal forms; beside every sent transfer</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>N/A — self-service</t>
+          <t>Admin → Wallet Security (reports, reverse, dismiss, freeze recipient); settings in platform_settings</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Wallet withdrawal to bank</t>
+          <t>Seller's request to release sale money</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Only one linked bank account per wallet, for security. Real Paystack transfer to the verified account.</t>
+          <t>After a property is paid for, the seller's proceeds (price less CHS commission) are held. They are released when the buyer confirms the documents arrived, when CHS confirms delivery, or when the seller asks: the seller taps Request release of my money on the Owner dashboard; CHS sees the request with the delivery record, verifies delivery from the platform's records or by phoning the buyer (recording which), then approves or declines with a reason; the buyer is told the seller says delivery is done so a false claim can be disputed. Every route releases exactly that sale's own held amount, refuses an unpaid or already-released sale, and never touches other money held in the same wallet.</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Wallet page — every role</t>
+          <t>Owner dashboard → sold property → Request release of my money</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>N/A — self-service, admin sees real withdrawal_requests records</t>
+          <t>Admin → Escrow Oversight → Property sale escrow</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Wallet-to-wallet transfer</t>
+          <t>Rent to Own: the owner can decline</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Send funds directly to another CHS user by phone or email — real-time lookup and instant transfer.</t>
+          <t>A request CHS has passed to the owner can be approved or declined. Declining needs a short reason (no contact details), which CHS passes to the buyer; nothing was charged. The owner sees the request at the top of their dashboard, with the CHS reference and never the buyer's phone number.</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Wallet page — every role</t>
+          <t>Owner dashboard → Mortgage (Rent to Own) requests</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>N/A — self-service</t>
+          <t>Admin → Rent-to-Own Requests</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Bank account linking with real-time verification</t>
+          <t>Wallet (main + rent savings + maintenance reserve)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>200+ real Nigerian banks with search; the account number is checked against the real bank network before it can ever be linked. Real 48-hour security window on any change.</t>
+          <t>Three real sub-balances per user — a main spending balance plus two dedicated savings pots for rent renewal and maintenance costs.</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Wallet → Link bank account — every role</t>
+          <t>Wallet page — every role</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>N/A — self-service, real-time</t>
+          <t>Admin → Finance — search any user's real balances, freeze/unfreeze</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Notification preferences</t>
+          <t>Wallet funding via Paystack</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Independent real toggles for offers, messages, and marketing notifications.</t>
+          <t>Real, secure card/bank/USSD payment; balance updates automatically once payment genuinely completes.</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Profile page — every role</t>
+          <t>Wallet page — every role</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -791,262 +791,350 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Diaspora Mode</t>
+          <t>Wallet withdrawal to bank</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>A real setting for CHS users managing property or transactions from outside Nigeria.</t>
+          <t>Only one linked bank account per wallet, for security. Real Paystack transfer to the verified account.</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Profile page — every role</t>
+          <t>Wallet page — every role</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>N/A — self-service</t>
+          <t>N/A — self-service, admin sees real withdrawal_requests records</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Terms &amp; Conditions scroll-to-accept gate</t>
+          <t>Wallet-to-wallet transfer</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>A real, meaningful acceptance — the checkbox only unlocks after genuinely scrolling to the bottom. Required before any dashboard is reachable. The Terms carry a version number: when they change (Version 3, October 2026, rewrote term 11 on bookings), everyone is shown what is new and asked to accept once more. Every acceptance is logged permanently with the version and the exact time, and the log cannot be altered.</t>
+          <t>Send funds directly to another CHS user by phone or email — real-time lookup and instant transfer.</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>First login — every role</t>
+          <t>Wallet page — every role</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>N/A — one-time gate per version</t>
+          <t>N/A — self-service</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Role-specific first-dashboard guide + persistent Users Guide</t>
+          <t>Bank account linking with real-time verification</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>A short popup on first dashboard visit, plus a full, always-accessible reference page.</t>
+          <t>200+ real Nigerian banks with search; the account number is checked against the real bank network before it can ever be linked. Real 48-hour security window on any change.</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>First login popup + More menu → Users Guide</t>
+          <t>Wallet → Link bank account — every role</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>N/A — reference</t>
+          <t>N/A — self-service, real-time</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Dark mode</t>
+          <t>Notification preferences</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>A real, complete theme system across the whole app, with an app-wide fix ensuring form text stays readable in both modes.</t>
+          <t>Independent real toggles for offers, messages, and marketing notifications.</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Every page — every role</t>
+          <t>Profile page — every role</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>N/A — visual</t>
+          <t>N/A — self-service</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>PWA install + splash screen</t>
+          <t>Diaspora Mode</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Installable as a real app on the home screen, with a proper full-screen splash and app icon.</t>
+          <t>A real setting for CHS users managing property or transactions from outside Nigeria.</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Browser install prompt</t>
+          <t>Profile page — every role</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>N/A — visual</t>
+          <t>N/A — self-service</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Guest — its own real role</t>
+          <t>Terms &amp; Conditions scroll-to-accept gate</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>A genuine, separate role from Buyer, for booking a shortlet apartment or a hotel/lodge/event centre/car park stay — its own heading at registration and login, not merged into another role.</t>
+          <t>A real, meaningful acceptance — the checkbox only unlocks after genuinely scrolling to the bottom. Required before any dashboard is reachable. The Terms carry a version number: when they change (Version 3, October 2026, rewrote term 11 on bookings), everyone is shown what is new and asked to accept once more. Every acceptance is logged permanently with the version and the exact time, and the log cannot be altered.</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Register / Login page — every role</t>
+          <t>First login — every role</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>N/A — self-service</t>
+          <t>N/A — one-time gate per version</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Account approval gate</t>
+          <t>Role-specific first-dashboard guide + persistent Users Guide</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>A real, enforced rule: a newly registered account cannot use anything beyond the public homepage until CHS staff approve it — previously unenforced despite existing in the database.</t>
+          <t>A short popup on first dashboard visit, plus a full, always-accessible reference page.</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Every page — every role</t>
+          <t>First login popup + More menu → Users Guide</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Admin → Registrations</t>
+          <t>N/A — reference</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Account suspension &amp; appeal</t>
+          <t>Dark mode</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Real admin tools to suspend a suspicious account with a documented reason, and a genuine appeal channel that stays reachable even while suspended.</t>
+          <t>A real, complete theme system across the whole app, with an app-wide fix ensuring form text stays readable in both modes.</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Suspended-account screen — every role</t>
+          <t>Every page — every role</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Admin → Overview, Suspend a Real Account</t>
+          <t>N/A — visual</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Self-service account deactivation</t>
+          <t>PWA install + splash screen</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>A real, reversible way to temporarily deactivate your own account — nothing deleted, log back in any time to reactivate.</t>
+          <t>Installable as a real app on the home screen, with a proper full-screen splash and app icon.</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Profile page — every role</t>
+          <t>Browser install prompt</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>N/A — self-service</t>
+          <t>N/A — visual</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Automatic image compression</t>
+          <t>Guest — its own real role</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Every property photo and profile picture is resized and re-compressed in the browser before upload — no action required, real storage savings confirmed by direct testing.</t>
+          <t>A genuine, separate role from Buyer, for booking a shortlet apartment or a hotel/lodge/event centre/car park stay — its own heading at registration and login, not merged into another role.</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Every photo upload — every role</t>
+          <t>Register / Login page — every role</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>N/A — automatic</t>
+          <t>N/A — self-service</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Real-time number validation (phone, NIN, ID, bank account)</t>
+          <t>Account approval gate</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>One shared rulebook checks every phone number, NIN, passport, voter's card, driver's licence, and bank account number as it's typed, on submit, and again in the database itself — so a malformed number can never be saved from any screen.</t>
+          <t>A real, enforced rule: a newly registered account cannot use anything beyond the public homepage until CHS staff approve it — previously unenforced despite existing in the database.</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Every form collecting a phone, ID, or account number — every role</t>
+          <t>Every page — every role</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>N/A — enforced automatically; a malformed existing record is flagged on the ID review screen</t>
+          <t>Admin → Registrations</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>Account suspension &amp; appeal</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Real admin tools to suspend a suspicious account with a documented reason, and a genuine appeal channel that stays reachable even while suspended.</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Suspended-account screen — every role</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Overview, Suspend a Real Account</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Self-service account deactivation</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>A real, reversible way to temporarily deactivate your own account — nothing deleted, log back in any time to reactivate.</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Profile page — every role</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Automatic image compression</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Every property photo and profile picture is resized and re-compressed in the browser before upload — no action required, real storage savings confirmed by direct testing.</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Every photo upload — every role</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>N/A — automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Real-time number validation (phone, NIN, ID, bank account)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>One shared rulebook checks every phone number, NIN, passport, voter's card, driver's licence, and bank account number as it's typed, on submit, and again in the database itself — so a malformed number can never be saved from any screen.</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Every form collecting a phone, ID, or account number — every role</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>N/A — enforced automatically; a malformed existing record is flagged on the ID review screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>Digital receipts</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>A real, printable receipt (Print/Save as PDF) for any transaction — rent, remittance, commission, sale — using the same reference number already generated for it.</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>My Receipts page — every role</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1190,7 +1278,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>A genuinely new listing category — progressive ownership through monthly instalments, labelled “Mortgage (Rent to Own)” in the app. The buyer must be fully verified and the owner must approve the request. Each instalment is paid from the wallet (instalment + 5.5% buyer commission), the owner is credited at once (instalment − 4.5%), and the buyer's ownership percentage is worked out exactly from what has been paid. The final instalment is only what is still owed. A property can have only one active agreement: approving one buyer declines the other pending requests. At 100% the property is marked sold. The owner sees the buyer's name and a CHS reference, never their phone number.</t>
+          <t>A genuinely new listing category — progressive ownership through monthly instalments, labelled “Mortgage (Rent to Own)” in the app. The buyer must be fully verified. Every request goes to CHS first: admin relays it to the owner or rejects it with a reason (Admin → Rent-to-Own Requests), and only a relayed request can be approved by the owner (shown at the top of the Owner dashboard). Each instalment is paid from the wallet (instalment + 5.5% buyer commission), the owner is credited at once (instalment − 4.5%), and the buyer's ownership percentage is worked out exactly from what has been paid. The final instalment is only what is still owed. A property can have only one active agreement: approving one buyer declines the other pending requests. At 100% the property is marked sold. The owner sees the buyer's name and a CHS reference, never their phone number.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2507,7 +2595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2629,127 +2717,127 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Marketplace: real direct "Buy Now"</t>
+          <t>Marketplace: detailed product listings</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Sort by price and buy the cheapest listing directly at its own fixed price — no negotiation, no messages to moderate. Same real 6%/4% split and escrow protection.</t>
+          <t>A product is described the way established marketplaces describe goods: brand, model, condition (new / refurbished / used), price and unit, stock quantity, SKU, a specification set that is different for each category (for Electronics: product type, size or capacity, features, power, voltage, energy rating, dimensions, weight, what is in the box; for Furniture: type, material, dimensions, assembly, style; and so on), the options a buyer chooses (colour, size, capacity …), warranty, delivery information and up to six photos. Required fields are marked. A service provider instead gives licence, years in operation, team size, response time, availability and what is included.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Marketplace → Buy now</t>
+          <t>Vendor dashboard → Add a listing</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Admin → Marketplace Moderation</t>
+          <t>Admin → Marketplace</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Sister marketplace link (Unify Market Central)</t>
+          <t>Marketplace: stock and automatic sold-out</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>A real, admin-editable link for procurement CHS's own marketplace doesn't cover — still real, verified sellers, still under CHS's own jurisdiction.</t>
+          <t>Each listing carries a stock count. When the stock reaches zero the listing is marked Sold out by itself, and it reopens when restocked. The vendor dashboard shows a clear Active / Sold out status badge with an editable stock figure, separate from the manual 'Mark as sold out' action.</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Marketplace; Construction Roadmap; Owner → Maintenance</t>
+          <t>Vendor dashboard</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Admin → Overview → Edit Real Contact Details</t>
+          <t>N/A — automatic</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Rental application: real applicant detail shown to owner</t>
+          <t>Marketplace: orders record what was bought</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>The owner's review card previously showed only the guarantor's name, phone, and move-in date. Now shows the applicant's real name, ID-verified status, occupation, income, employer, and current address — every field already being collected, now actually displayed.</t>
+          <t>An order records the quantity, the options the buyer chose (colour, size …) and the delivery address, takes stock off, and refuses more than is in stock, an option the vendor does not offer, a missing address, or a product from a vendor CHS has not verified. The buyer sees brand, specification, warranty, delivery information and stock on a details sheet before paying from the wallet.</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Owner dashboard → Rental applications</t>
+          <t>Marketplace → View details &amp; buy</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Admin → Marketplace Moderation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Independent guarantor verification</t>
+          <t>Marketplace: real direct "Buy Now"</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>The applicant provides only the guarantor's name and phone. The guarantor completes every other real field about themselves — address, occupation, relationship, their own ID, and their own typed-name consent — via a private, single-use link, requiring no CHS account. The application cannot reach the owner until this is done.</t>
+          <t>Sort by price and buy the cheapest listing directly at its own fixed price — no negotiation, no messages to moderate. Same real 6%/4% split and escrow protection.</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>New applicant flow → real link sent to guarantor → /guarantor-confirm/[token]</t>
+          <t>Marketplace → Buy now</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Admin → Marketplace Moderation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Event Centre: real capacity tiers and priced facilities</t>
+          <t>Sister marketplace link (Unify Market Central)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Real, host-set price tiers by guest count, and a real priced facilities list (lighting, sound, catering per guest, live band, DJ, decoration, generator, security, parking attendants, ushers/event staff) with a live-calculated quotation as the guest selects.</t>
+          <t>A real, admin-editable link for procurement CHS's own marketplace doesn't cover — still real, verified sellers, still under CHS's own jurisdiction.</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Event Centre booking form</t>
+          <t>Marketplace; Construction Roadmap; Owner → Maintenance</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Host → Real Event Pricing (/event-pricing/[propertyId])</t>
+          <t>Admin → Overview → Edit Real Contact Details</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Event-day add-on requests</t>
+          <t>Rental application: real applicant detail shown to owner</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>A real request for music band, caterer, and/or ushers (with a count) on any hire/event booking, visible directly on the host's own dashboard.</t>
+          <t>The owner's review card previously showed only the guarantor's name, phone, and move-in date. Now shows the applicant's real name, ID-verified status, occupation, income, employer, and current address — every field already being collected, now actually displayed.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Hire/Event booking form</t>
+          <t>Owner dashboard → Rental applications</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -2761,17 +2849,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Real payment regression fixes — rent and Rent-to-Own</t>
+          <t>Independent guarantor verification</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Both previously charged only the base amount, silently omitting the payer's own real, already-invoiced commission. Both now compute and charge the true total in one real payment, shown to the payer beforehand.</t>
+          <t>The applicant provides only the guarantor's name and phone. The guarantor completes every other real field about themselves — address, occupation, relationship, their own ID, and their own typed-name consent — via a private, single-use link, requiring no CHS account. The application cannot reach the owner until this is done.</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Tenant dashboard → Pay rent; Rent-to-Own installment payment</t>
+          <t>New applicant flow → real link sent to guarantor → /guarantor-confirm/[token]</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2783,152 +2871,218 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Stale, uncollected commission alert</t>
+          <t>Event Centre: real capacity tiers and priced facilities</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>A real, visible warning on Admin → Finance for any commission invoiced but genuinely uncollected for 2+ hours — an early warning against the exact regression pattern found and fixed above.</t>
+          <t>Real, host-set price tiers by guest count, and a real priced facilities list (lighting, sound, catering per guest, live band, DJ, decoration, generator, security, parking attendants, ushers/event staff) with a live-calculated quotation as the guest selects.</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>N/A — admin only</t>
+          <t>Event Centre booking form</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Admin → Finance</t>
+          <t>Host → Real Event Pricing (/event-pricing/[propertyId])</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Clickable notifications with real navigation</t>
+          <t>Event-day add-on requests</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>A rental application's full decision chain — owner decides, CHS relays, tenant is told — now carries a real, working link at every step, straight to the relevant page.</t>
+          <t>A real request for music band, caterer, and/or ushers (with a count) on any hire/event booking, visible directly on the host's own dashboard.</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Notification bell, any role</t>
+          <t>Hire/Event booking form</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Notification bell</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Real-time notification delivery</t>
+          <t>Real payment regression fixes — rent and Rent-to-Own</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>The notifications table is now genuinely part of Supabase's real-time publication — confirmed missing before, and the actual cause of alerts never appearing without a manual refresh. A real, visible toast now appears the instant a new notification arrives.</t>
+          <t>Both previously charged only the base amount, silently omitting the payer's own real, already-invoiced commission. Both now compute and charge the true total in one real payment, shown to the payer beforehand.</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Any dashboard, any role</t>
+          <t>Tenant dashboard → Pay rent; Rent-to-Own installment payment</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Any dashboard</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>My Applications</t>
+          <t>Stale, uncollected commission alert</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Every real rental application and purchase offer a buyer/tenant has made, queued permanently the moment they apply — no more scrolling the homepage to find it again.</t>
+          <t>A real, visible warning on Admin → Finance for any commission invoiced but genuinely uncollected for 2+ hours — an early warning against the exact regression pattern found and fixed above.</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>/my-applications</t>
+          <t>N/A — admin only</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>N/A — self-service</t>
+          <t>Admin → Finance</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Recent Applications (owner)</t>
+          <t>Clickable notifications with real navigation</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Every real application received across every property, most recent first, regardless of how far down the property list it sits.</t>
+          <t>A rental application's full decision chain — owner decides, CHS relays, tenant is told — now carries a real, working link at every step, straight to the relevant page.</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Owner dashboard → Recent Applications</t>
+          <t>Notification bell, any role</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>N/A — self-service</t>
+          <t>Notification bell</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Platform Earnings</t>
+          <t>Real-time notification delivery</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>A real, dedicated view of every collected commission — payer name, amount, and timestamp.</t>
+          <t>The notifications table is now genuinely part of Supabase's real-time publication — confirmed missing before, and the actual cause of alerts never appearing without a manual refresh. A real, visible toast now appears the instant a new notification arrives.</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>N/A — admin only</t>
+          <t>Any dashboard, any role</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Admin → Platform Earnings</t>
+          <t>Any dashboard</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>My Applications</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Every real rental application and purchase offer a buyer/tenant has made, queued permanently the moment they apply — no more scrolling the homepage to find it again.</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>/my-applications</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Recent Applications (owner)</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Every real application received across every property, most recent first, regardless of how far down the property list it sits.</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Owner dashboard → Recent Applications</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>N/A — self-service</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Platform Earnings</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>A real, dedicated view of every collected commission — payer name, amount, and timestamp.</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>N/A — admin only</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Platform Earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>Rent Savings relocated</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Confirmed the tenant dashboard already showed this correctly; removed the redundant duplicate from the general homepage.</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Tenant dashboard</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3750,7 +3904,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Real fee calculated per-person based on distance; a genuine 12-hour minimum notice enforced by the database itself.</t>
+          <t>A physical inspection is a last resort: photographs, room videos and requests for more of either are free. If a buyer or tenant still insists on visiting, the WHOLE round-trip transport cost is theirs — not split with the owner, not carried by CHS — at ₦150 per km each way, from where the CHS agent actually sets off. Booking takes nothing; CHS assigns an agent and records their takeoff point and distance, which fixes the final cost. The requester then pays it FROM THEIR WALLET (My Inspections); it is held until the visit and released to the agent (also if the requester does not attend). Refunded in full if the owner or CHS cancels or the requester cancels 12+ hours ahead; inside 12 hours it goes to the agent. A visit not paid for 2 hours before it is due lapses with nothing charged. A genuine 12-hour minimum notice is enforced by the database itself.</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -5126,7 +5280,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Reviewed by CHS before listings go live — the same trust standard applied platform-wide.</t>
+          <t>Three clearly separate sign-up paths: ARTISAN (trades such as plumbing and electrical), VENDOR (sells goods: Interior Design, Furniture, Bedding &amp; Textiles, Electronics &amp; Home Appliances, Kitchen, Building Materials) and SERVICE PROVIDER (Security, Cleaning, Fumigation &amp; Pest Control, Facilities Maintenance). Each shows only its own categories. State and LGA are dropdowns (the LGA list follows the chosen state), a service provider ticks the states it covers, and required fields are marked. Every registration alerts the responsible admins automatically (bell notification, a marker on the Vendors / Artisans tab), and CHS reviews it under Verification before the listings go public.</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
+++ b/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
@@ -23,6 +23,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14. Marketplace Rebuild, Guaran" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15. Admin Mediation Completed," sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16. Hotel, Lodge, Shortlet &amp; Ev" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17. Mortgage Through CHS, Manua" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1278,17 +1279,17 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>A genuinely new listing category — progressive ownership through monthly instalments, labelled “Mortgage (Rent to Own)” in the app. The buyer must be fully verified. Every request goes to CHS first: admin relays it to the owner or rejects it with a reason (Admin → Rent-to-Own Requests), and only a relayed request can be approved by the owner (shown at the top of the Owner dashboard). Each instalment is paid from the wallet (instalment + 5.5% buyer commission), the owner is credited at once (instalment − 4.5%), and the buyer's ownership percentage is worked out exactly from what has been paid. The final instalment is only what is still owed. A property can have only one active agreement: approving one buyer declines the other pending requests. At 100% the property is marked sold. The owner sees the buyer's name and a CHS reference, never their phone number.</t>
+          <t>A listing category for progressive ownership through monthly instalments, labelled “Mortgage (Rent to Own)” in the app. The buyer must be fully verified and gives their name, phone, occupation, source of funds and address before the request is sent. Every request and every owner answer goes to CHS first: admin relays the request to the owner or rejects it with a reason, and relays the owner's approval or decline to the buyer. The buyer can pay one instalment or any larger amount up to the full balance; every payment goes from the wallet to CHS (instalment + 5.5% buyer commission), is held, and is released to the owner (instalment − 4.5%) by admin, singly or with Release all. The final payment is held until the property documents are handed over. At 100% the property is marked sold. The owner sees the buyer only as a first name and initial plus a CHS reference, never the phone number or full name.</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Property listing page / Owner dashboard</t>
+          <t>Property listing page / Buyer Mortgage page / Owner dashboard</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Admin → Rent-to-Own: every agreement newest first, with Payments to release</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3571,178 +3572,638 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Admin relay queue</t>
+          <t>Instant Confirm (hotels)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Every request comes to CHS first, in every lane — guest and host never deal directly. The queue lists requests in three groups (waiting to be relayed, with the host, waiting for the guest to pay), urgent first and in red, each with a countdown and the host's phone number. Admin relays with one tap and an optional note, or declines with a reason (the guest pays nothing). A short automatic relay remains only as a safety net if nobody acts, with an alert to admin.</t>
+          <t>A host can switch on Instant Confirm for a listing. A guest then sees Book now: they pay from their CHS wallet at once and the room is confirmed with no waiting and no admin relay. It is live only while the host's calendar has been confirmed in the last 12 hours, and never for a suspended or inactive listing; otherwise guests see the normal request flow. The host is still paid only after the guest arrives and confirms.</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Host dashboard → listing → Instant Confirm; booking form → Book now</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Admin → Shortlet/Hire Bookings</t>
+          <t>Admin is told of every instant booking</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Pay-now card and live countdown</t>
+          <t>Express: ask up to 3 hotels at once (same-day stays)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>My Bookings and the Guest dashboard show where a booking stands in plain words with a live countdown. When the host confirms, a green card shows the exact amount and breakdown with a Pay now button; a wallet shortfall gives a clear message and a Top up link. An unpaid request can be withdrawn at any time at no cost. The page after sending a request says “Request sent — nothing has been charged”.</t>
+          <t>For a stay starting today, the guest can ask up to 2 more hotels with a free room in the same state. CHS relays each request. The first host to confirm wins and the other requests cancel on their own, with the other hosts and the guest told. The guest pays once, for the hotel they get.</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>My Bookings / Guest dashboard</t>
+          <t>Booking form (same-day dates)</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Admin → Shortlet/Hire Bookings shows the Express group</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Arrival confirmation and prompt payout</t>
+          <t>Peak pricing</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Booking is prepaid: the guest pays first, and the host is paid when the guest ARRIVES — not after the stay. From the check-in day the guest ticks a short checklist on their booking: they have arrived and can get in, the property matches its listing, each listed facility (or each facility booked, for a venue) is present and working, and everything is in good order, with an optional message. That releases the host's payout at once and sends the message to the host and to CHS. If something is wrong the guest reports a problem instead: the money stays held and CHS and the host are alerted. If the guest says nothing, the payout is released automatically 24 hours after the 2 pm check-in time unless a problem was reported. A host whose guest has arrived can ask CHS to release; CHS sees the request, whether the guest has confirmed, and releases with one tap. Older pay-first bookings are released by CHS from its list.</t>
+          <t>CHS keeps a calendar of busy periods (Christmas and New Year, Eid, Easter, Democracy Day). A host switches a period on for a listing with their own percentage and an optional minimum stay, and can add their own events. The guest sees the busy nights, the busy-period names and the full price before booking; where periods overlap, the highest uplift applies to that night.</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>My Bookings / Guest dashboard (guest); Owner &amp; Host dashboards (host)</t>
+          <t>Host dashboard → listing → Peak pricing; booking form price breakdown</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Admin → Shortlet/Hire Bookings → stays awaiting release</t>
+          <t>Admin → Hotel Controls → Peak periods</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>House rules for hotels, lodges, venues and hosts</t>
+          <t>Host cancels a confirmed booking: consequences</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Any shortlet, hotel, lodge, event-centre or other hire listing can carry a House Rules document, uploaded by the owner from the Owner dashboard or by a host from the Host dashboard. Guests must read and acknowledge it before they can send a booking request.</t>
+          <t>The guest is refunded in full and the cancelled dates stay blocked. The host pays the bank processing fee. First cancellation in 90 days is a warning, the second costs 10 percent of the booking value (taken from the wallet and later payouts), the third suspends the listing until CHS reviews it. The host sees the consequence before confirming and must give a reason with no contact details. Admins are alerted to help the guest rebook.</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Owner dashboard / Host dashboard → listing → House rules; booking form (guest)</t>
+          <t>Host dashboard → a confirmed booking → Cancel</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Admin → listing review</t>
+          <t>Admin → Hotel Controls → cancellations and Reinstate; settings host_default_penalty_pct and host_default_window_days</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Host requests panel</t>
+          <t>Digital check-in and front desk</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>A red panel at the very top of both the Owner and Host dashboards lists every request awaiting the host: the hotel, the guest's name with a CHS identity-verified mark and a CHS reference (never their phone number or ID), dates, expected arrival, what the host would receive, a countdown, and Confirm — dates are free / Decline. Urgent requests are flagged. The notification links to the right dashboard for the person's role.</t>
+          <t>Once a booking is confirmed the guest gets an arrival pass with a code (XXXX-XXXX), can fill in the registration card ahead of time, and on arrival day taps I've arrived (checked against the hotel location when the host has set one, within 1 km). The front desk is told. If the host set a self check-in code, it appears only after the guest taps I've arrived. Hosts and the front-desk staff they add see today's arrivals, verify a pass, check the guest in, and record a no-show from 12:00 the day after check-in (the host is paid under the cancellation terms, the deposit goes back to the guest, the room is freed).</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Owner dashboard / Host dashboard (top)</t>
+          <t>My Bookings (guest); Host dashboard → Front Desk (/host/arrivals); Host dashboard → Front-desk staff</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Admin can view any arrivals board</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Message review and contact-detail filter</t>
+          <t>Contact always through CHS (documents, tenants, landlords)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Messages between a guest and a host are reviewed by CHS before delivery until the booking is paid (one setting keeps review on for paid bookings too); the other side cannot read an unreviewed message, even by querying the database; messages cannot be written into the table directly. Phone numbers and email addresses are refused for everyone, always. The shared filter ignores ordinary dates, times and numbers but still catches disguised numbers, and also protects offers and the marketplace.</t>
+          <t>A buyer's delivery phone number is kept by CHS to coordinate the hand-over of sale documents; the seller never sees it, and the database refuses a direct read. Tenants and landlords likewise see no phone number for each other, only a message button.</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>My Bookings / Host dashboard (Messages)</t>
+          <t>Owner dashboard, My Rented Space, document delivery form</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Admin → Shortlet/Hire Bookings → message review</t>
+          <t>Admin → held funds shows the delivery contact for CHS to use</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Payment, commission and payout</t>
+          <t>Admin relay queue</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>The guest pays before arriving; CHS holds the money only until the guest arrives and confirms. Both CHS commissions — the guest's and the host's — are recorded as collected at the moment the guest pays, as with rent and sale. The host's net payout is released the moment the guest confirms arrival (see the next entry), by admin on a host's request, or automatically 24 hours after check-in; all three go through one routine that refuses anything not actually held and pays the host the price net of CHS's commission.</t>
+          <t>Every request comes to CHS first, in every lane — guest and host never deal directly. The queue lists requests in three groups (waiting to be relayed, with the host, waiting for the guest to pay), urgent first and in red, each with a countdown and the host's phone number. Admin relays with one tap and an optional note, or declines with a reason (the guest pays nothing). A short automatic relay remains only as a safety net if nobody acts, with an alert to admin.</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Wallet / My Bookings</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Admin → Escrow Oversight; Platform Earnings</t>
+          <t>Admin → Shortlet/Hire Bookings</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>Pay-now card and live countdown</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>My Bookings and the Guest dashboard show where a booking stands in plain words with a live countdown. When the host confirms, a green card shows the exact amount and breakdown with a Pay now button; a wallet shortfall gives a clear message and a Top up link. An unpaid request can be withdrawn at any time at no cost. The page after sending a request says “Request sent — nothing has been charged”.</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>My Bookings / Guest dashboard</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Arrival confirmation and prompt payout</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Booking is prepaid: the guest pays first, and the host is paid when the guest ARRIVES — not after the stay. From the check-in day the guest ticks a short checklist on their booking: they have arrived and can get in, the property matches its listing, each listed facility (or each facility booked, for a venue) is present and working, and everything is in good order, with an optional message. That releases the host's payout at once and sends the message to the host and to CHS. If something is wrong the guest reports a problem instead: the money stays held and CHS and the host are alerted. If the guest says nothing, the payout is released automatically 24 hours after the 2 pm check-in time unless a problem was reported. A host whose guest has arrived can ask CHS to release; CHS sees the request, whether the guest has confirmed, and releases with one tap. Older pay-first bookings are released by CHS from its list.</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>My Bookings / Guest dashboard (guest); Owner &amp; Host dashboards (host)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings → stays awaiting release</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>House rules for hotels, lodges, venues and hosts</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Any shortlet, hotel, lodge, event-centre or other hire listing can carry a House Rules document, uploaded by the owner from the Owner dashboard or by a host from the Host dashboard. Guests must read and acknowledge it before they can send a booking request.</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Owner dashboard / Host dashboard → listing → House rules; booking form (guest)</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Admin → listing review</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Host requests panel</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>A red panel at the very top of both the Owner and Host dashboards lists every request awaiting the host: the hotel, the guest's name with a CHS identity-verified mark and a CHS reference (never their phone number or ID), dates, expected arrival, what the host would receive, a countdown, and Confirm — dates are free / Decline. Urgent requests are flagged. The notification links to the right dashboard for the person's role.</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Owner dashboard / Host dashboard (top)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Message review and contact-detail filter</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Messages between a guest and a host are reviewed by CHS before delivery until the booking is paid (one setting keeps review on for paid bookings too); the other side cannot read an unreviewed message, even by querying the database; messages cannot be written into the table directly. Phone numbers and email addresses are refused for everyone, always. The shared filter ignores ordinary dates, times and numbers but still catches disguised numbers, and also protects offers and the marketplace.</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>My Bookings / Host dashboard (Messages)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings → message review</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Payment, commission and payout</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>The guest pays before arriving; CHS holds the money only until the guest arrives and confirms. Both CHS commissions — the guest's and the host's — are recorded as collected at the moment the guest pays, as with rent and sale. The host's net payout is released the moment the guest confirms arrival (see the next entry), by admin on a host's request, or automatically 24 hours after check-in; all three go through one routine that refuses anything not actually held and pays the host the price net of CHS's commission.</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Wallet / My Bookings</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Escrow Oversight; Platform Earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t>Cancellation and refunds</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>An unpaid request is withdrawn at no cost. A paid booking cancelled 48+ hours before check-in is refunded in full (and CHS keeps no commission); within 48 hours, 50%; on or after check-in, none; a booking the host never confirmed is always refunded in full; a security deposit is always returned. The part not refunded is split: the unrefunded stay price goes to the host as compensation for the dates held (less CHS's commission on it; the host's share is a setting, default 100%) and CHS keeps its service fee on it. The guest, host and admin are each told the exact amounts, and refund + host + CHS always equals what was paid. If a host fails to honour a confirmed booking, term 36 applies instead.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>My Bookings / Guest dashboard</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>Admin → Escrow Oversight</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>How it works</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Where to find it (user)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Where to find it (admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Installments held, then released by CHS</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>A mortgage installment never goes straight to the owner. It is debited from the buyer, held in the owner's CHS hold with the commission rows recorded, and appears in Admin → Rent-to-Own → Payments to release. Admin releases it to the owner's wallet, singly or all at once, and each release is written to the audit log.</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Buyer Mortgage page / Owner earnings</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Rent-to-Own → Payments to release</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Document handover for a mortgage</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>After the final payment the buyer asks for the documents (recipient, address, phone, method, maximum days). The owner uploads the documents for CHS to check; admin approves or asks for changes; the buyer receives the approved soft copy in the app; the owner then marks the hard copy as sent with a receipt or proof; the buyer taps I have received my documents. Every step notifies the others through CHS, and the buyer's delivery phone number is seen only by CHS.</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Buyer Mortgage page / Owner dashboard (Step 1 and Step 2) / Admin</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Rent-to-Own → document review and handover</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Final payment released by a super admin only</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>The buyer confirming receipt does not move money. It marks the handover as confirmed and alerts admin; the final payment stays held until a super admin releases it. A sub-admin sees a notice instead of the button. Without owner proof or buyer confirmation, a note of at least ten characters explaining how the handover was verified is required.</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Rent-to-Own</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Super admin only; audited as rto_final_released</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Auto-release tick box (off by default)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>A box at the top of the Rent-to-Own desk. Only a super admin can tick it, after a confirmation prompt, and each change is audit-logged. When ticked, the buyer's confirmation releases the final payment immediately; when not ticked, release is manual. Meant for busy periods with many releases due at once.</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Rent-to-Own</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Super admin only; setting rto_final_auto_release</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Reversal of a final release</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>A super admin can return an already released final payment to CHS hold with a written reason of at least ten characters. The money moves from the owner's wallet back into hold, the agreement returns to awaiting handover, the owner is notified and the reversal is audit-logged. It refuses if the owner has already moved the money.</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Database function used by super admin</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Super admin only; audited as rto_final_release_reversed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Host cancellation strikes</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>A host who cancels a confirmed booking that has not started must give a reason of at least ten characters without contact details. The guest is refunded in full, the dates stay blocked, and the bank fee is charged to the host. Within 90 days: strike 1 is a warning, strike 2 a 10% penalty collected from later payouts, strike 3 suspends the listing. Admin sees the strikes and can reinstate a listing with a note.</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Host dashboard / Admin</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Admin → host strikes and reinstate listing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Hotel digital check-in</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Each confirmed booking gets an arrival code. The guest fills a registration card, taps I have arrived (checked within 1 km of the hotel when its location is set) and sees the lockbox code only on stay days, each viewing audit-logged. The front desk (host, staff the host adds by phone, or admin) uses an arrivals board to verify the pass and check the guest in, or marks a no-show from noon the day after.</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Guest My Bookings / Host front desk</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Admin can act as front desk</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Notification bell on every dashboard</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Each role's own dashboard carries its own bell, and tapping a notification opens the exact page and item it is about, even when you are already on that page.</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Every dashboard</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Admin feed opens the matching admin tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Full timestamps on every event</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Every document, confirmation, notification, transaction, application and admin action shows its date AND time to the second in Nigerian time (WAT), using one shared formatter. The Mortgage admin panel shows a handover timeline: documents requested, uploaded, approved, marked sent, buyer confirmed (with the moment CHS was alerted) and final payment released. Plain calendar dates (a lease end, a check-in day) stay as dates.</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Every screen</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Audit log and admin panels show the same stamps</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Newest first everywhere</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Chats, transactions, requests, bookings, earnings and admin lists show the newest first. Upcoming due dates and scheduled inspection dates are the deliberate exception and stay soonest first.</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>All dashboards</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="3" t="n"/>
+      <c r="C12" s="3" t="n"/>
+      <c r="D12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n"/>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n"/>
+      <c r="D14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="3" t="n"/>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="3" t="n"/>
+      <c r="C16" s="3" t="n"/>
+      <c r="D16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
+      <c r="D17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
+++ b/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
@@ -24,6 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15. Admin Mediation Completed," sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16. Hotel, Lodge, Shortlet &amp; Ev" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17. Mortgage Through CHS, Manua" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18. Hospitality Suite Team, Pl" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3384,7 +3385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -3682,196 +3683,328 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Contact always through CHS (documents, tenants, landlords)</t>
+          <t>Housekeeping board (hotels)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>A buyer's delivery phone number is kept by CHS to coordinate the hand-over of sale documents; the seller never sees it, and the database refuses a direct read. Tenants and landlords likewise see no phone number for each other, only a message button.</t>
+          <t>Every room shows live as occupied, to clean, ready, inspected or out of order. A room whose guest has left (after noon Nigerian time) appears as to-clean by itself. Front-desk staff tap Cleaned, Inspected or Out of order, and each change records who did it and the exact date and time.</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Owner dashboard, My Rented Space, document delivery form</t>
+          <t>Host dashboard → listing → Hotel operations → Housekeeping</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Admin → held funds shows the delivery contact for CHS to use</t>
+          <t>Audit log</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Admin relay queue</t>
+          <t>Repairs and maintenance tickets (hotels)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Every request comes to CHS first, in every lane — guest and host never deal directly. The queue lists requests in three groups (waiting to be relayed, with the host, waiting for the guest to pay), urgent first and in red, each with a countdown and the host's phone number. Admin relays with one tap and an optional note, or declines with a reason (the guest pays nothing). A short automatic relay remains only as a safety net if nobody acts, with an alert to admin.</t>
+          <t>Staff log a fault against a room or the whole property with a priority; an urgent fault alerts the owner at once. A ticket moves from open to in progress to done, with the repair cost and a note, and every step carries its exact date and time.</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Host dashboard → listing → Hotel operations → Repairs</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Admin → Shortlet/Hire Bookings</t>
+          <t>Audit log</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Pay-now card and live countdown</t>
+          <t>Other income centres (hotels)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>My Bookings and the Guest dashboard show where a booking stands in plain words with a live countdown. When the host confirms, a green card shows the exact amount and breakdown with a Pay now button; a wallet shortfall gives a clear message and a Top up link. An unpaid request can be withdrawn at any time at no cost. The page after sending a request says “Request sent — nothing has been charged”.</t>
+          <t>Restaurant, bar, laundry, gym, events and walk-in rooms: staff record each sale with an amount and note; the entry is stamped with who and exactly when. A wrong entry is voided with a reason — it stays on the ledger, struck through, never erased.</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>My Bookings / Guest dashboard</t>
+          <t>Host dashboard → listing → Hotel operations → Money</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Audit log</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Arrival confirmation and prompt payout</t>
+          <t>Expenses (hotels, owner only)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Booking is prepaid: the guest pays first, and the host is paid when the guest ARRIVES — not after the stay. From the check-in day the guest ticks a short checklist on their booking: they have arrived and can get in, the property matches its listing, each listed facility (or each facility booked, for a venue) is present and working, and everything is in good order, with an optional message. That releases the host's payout at once and sends the message to the host and to CHS. If something is wrong the guest reports a problem instead: the money stays held and CHS and the host are alerted. If the guest says nothing, the payout is released automatically 24 hours after the 2 pm check-in time unless a problem was reported. A host whose guest has arrived can ask CHS to release; CHS sees the request, whether the guest has confirmed, and releases with one tap. Older pay-first bookings are released by CHS from its list.</t>
+          <t>The owner records salaries, utilities, food and drink, supplies, repairs, marketing, taxes and other costs, each stamped with who and when, voidable with a reason.</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>My Bookings / Guest dashboard (guest); Owner &amp; Host dashboards (host)</t>
+          <t>Host dashboard → listing → Hotel operations → Money</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Admin → Shortlet/Hire Bookings → stays awaiting release</t>
+          <t>Audit log</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>House rules for hotels, lodges, venues and hosts</t>
+          <t>Hotel financial report and ledger (owner only)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Any shortlet, hotel, lodge, event-centre or other hire listing can carry a House Rules document, uploaded by the owner from the Owner dashboard or by a host from the Host dashboard. Guests must read and acknowledge it before they can send a booking request.</t>
+          <t>For any date range up to a year: occupancy %, room-nights sold, average room rate (ADR), revenue per available room (RevPAR), room revenue less CHS commission, other income by centre, expenses by category, repair costs and the net result. A ledger lists every booking, income, expense and repair newest first and downloads as a CSV file.</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Owner dashboard / Host dashboard → listing → House rules; booking form (guest)</t>
+          <t>Host dashboard → listing → Hotel operations → Money</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Admin → listing review</t>
+          <t>Audit log</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Host requests panel</t>
+          <t>Guest welcome, thank-you and owner daily summary (hotels)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>A red panel at the very top of both the Owner and Host dashboards lists every request awaiting the host: the hotel, the guest's name with a CHS identity-verified mark and a CHS reference (never their phone number or ID), dates, expected arrival, what the host would receive, a countdown, and Confirm — dates are free / Decline. Urgent requests are flagged. The notification links to the right dashboard for the person's role.</t>
+          <t>At check-in the guest gets a welcome notification. After check-out they get a thank-you with a request to review. Each evening (8 pm Nigerian time) the owner gets one summary: arrivals, departures, guests in-house, rooms to clean, open repairs and other income today. These are in-app alerts now; WhatsApp delivery needs a WhatsApp Business account to be connected.</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Owner dashboard / Host dashboard (top)</t>
+          <t>Notification bell</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A — automatic</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Message review and contact-detail filter</t>
+          <t>Contact always through CHS (documents, tenants, landlords)</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Messages between a guest and a host are reviewed by CHS before delivery until the booking is paid (one setting keeps review on for paid bookings too); the other side cannot read an unreviewed message, even by querying the database; messages cannot be written into the table directly. Phone numbers and email addresses are refused for everyone, always. The shared filter ignores ordinary dates, times and numbers but still catches disguised numbers, and also protects offers and the marketplace.</t>
+          <t>A buyer's delivery phone number is kept by CHS to coordinate the hand-over of sale documents; the seller never sees it, and the database refuses a direct read. Tenants and landlords likewise see no phone number for each other, only a message button.</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>My Bookings / Host dashboard (Messages)</t>
+          <t>Owner dashboard, My Rented Space, document delivery form</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Admin → Shortlet/Hire Bookings → message review</t>
+          <t>Admin → held funds shows the delivery contact for CHS to use</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Payment, commission and payout</t>
+          <t>Admin relay queue</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>The guest pays before arriving; CHS holds the money only until the guest arrives and confirms. Both CHS commissions — the guest's and the host's — are recorded as collected at the moment the guest pays, as with rent and sale. The host's net payout is released the moment the guest confirms arrival (see the next entry), by admin on a host's request, or automatically 24 hours after check-in; all three go through one routine that refuses anything not actually held and pays the host the price net of CHS's commission.</t>
+          <t>Every request comes to CHS first, in every lane — guest and host never deal directly. The queue lists requests in three groups (waiting to be relayed, with the host, waiting for the guest to pay), urgent first and in red, each with a countdown and the host's phone number. Admin relays with one tap and an optional note, or declines with a reason (the guest pays nothing). A short automatic relay remains only as a safety net if nobody acts, with an alert to admin.</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Wallet / My Bookings</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Admin → Escrow Oversight; Platform Earnings</t>
+          <t>Admin → Shortlet/Hire Bookings</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>Pay-now card and live countdown</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>My Bookings and the Guest dashboard show where a booking stands in plain words with a live countdown. When the host confirms, a green card shows the exact amount and breakdown with a Pay now button; a wallet shortfall gives a clear message and a Top up link. An unpaid request can be withdrawn at any time at no cost. The page after sending a request says “Request sent — nothing has been charged”.</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>My Bookings / Guest dashboard</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Arrival confirmation and prompt payout</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Booking is prepaid: the guest pays first, and the host is paid when the guest ARRIVES — not after the stay. From the check-in day the guest ticks a short checklist on their booking: they have arrived and can get in, the property matches its listing, each listed facility (or each facility booked, for a venue) is present and working, and everything is in good order, with an optional message. That releases the host's payout at once and sends the message to the host and to CHS. If something is wrong the guest reports a problem instead: the money stays held and CHS and the host are alerted. If the guest says nothing, the payout is released automatically 24 hours after the 2 pm check-in time unless a problem was reported. A host whose guest has arrived can ask CHS to release; CHS sees the request, whether the guest has confirmed, and releases with one tap. Older pay-first bookings are released by CHS from its list.</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>My Bookings / Guest dashboard (guest); Owner &amp; Host dashboards (host)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings → stays awaiting release</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>House rules for hotels, lodges, venues and hosts</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Any shortlet, hotel, lodge, event-centre or other hire listing can carry a House Rules document, uploaded by the owner from the Owner dashboard or by a host from the Host dashboard. Guests must read and acknowledge it before they can send a booking request.</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Owner dashboard / Host dashboard → listing → House rules; booking form (guest)</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Admin → listing review</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Host requests panel</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>A red panel at the very top of both the Owner and Host dashboards lists every request awaiting the host: the hotel, the guest's name with a CHS identity-verified mark and a CHS reference (never their phone number or ID), dates, expected arrival, what the host would receive, a countdown, and Confirm — dates are free / Decline. Urgent requests are flagged. The notification links to the right dashboard for the person's role.</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Owner dashboard / Host dashboard (top)</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Message review and contact-detail filter</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Messages between a guest and a host are reviewed by CHS before delivery until the booking is paid (one setting keeps review on for paid bookings too); the other side cannot read an unreviewed message, even by querying the database; messages cannot be written into the table directly. Phone numbers and email addresses are refused for everyone, always. The shared filter ignores ordinary dates, times and numbers but still catches disguised numbers, and also protects offers and the marketplace.</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>My Bookings / Host dashboard (Messages)</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Shortlet/Hire Bookings → message review</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Payment, commission and payout</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>The guest pays before arriving; CHS holds the money only until the guest arrives and confirms. Both CHS commissions — the guest's and the host's — are recorded as collected at the moment the guest pays, as with rent and sale. The host's net payout is released the moment the guest confirms arrival (see the next entry), by admin on a host's request, or automatically 24 hours after check-in; all three go through one routine that refuses anything not actually held and pays the host the price net of CHS's commission.</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Wallet / My Bookings</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Escrow Oversight; Platform Earnings</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
           <t>Cancellation and refunds</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>An unpaid request is withdrawn at no cost. A paid booking cancelled 48+ hours before check-in is refunded in full (and CHS keeps no commission); within 48 hours, 50%; on or after check-in, none; a booking the host never confirmed is always refunded in full; a security deposit is always returned. The part not refunded is split: the unrefunded stay price goes to the host as compensation for the dates held (less CHS's commission on it; the host's share is a setting, default 100%) and CHS keeps its service fee on it. The guest, host and admin are each told the exact amounts, and refund + host + CHS always equals what was paid. If a host fails to honour a confirmed booking, term 36 applies instead.</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>My Bookings / Guest dashboard</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>Admin → Escrow Oversight</t>
         </is>
@@ -4098,52 +4231,68 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Full timestamps on every event</t>
+          <t>Event services request (ushers, caterer, live band, security, other)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Every document, confirmation, notification, transaction, application and admin action shows its date AND time to the second in Nigerian time (WAT), using one shared formatter. The Mortgage admin panel shows a handover timeline: documents requested, uploaded, approved, marked sent, buyer confirmed (with the moment CHS was alerted) and final payment released. Plain calendar dates (a lease end, a check-in day) stay as dates.</t>
+          <t>On every event-centre booking (priced-capacity form and the date-range form) the guest ticks the services they want: ushers (with a number), caterer, live band, security personnel (with a number), and a free-text line for anything else such as an MC, DJ, photographer or decoration. The request goes through CHS to the venue and is shown to the host with the booking request; nothing is charged until the venue confirms. Venues can also list priced facilities (lighting, sound, catering per guest, band, DJ, security, parking attendants, ushers) that add to the quotation.</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Every screen</t>
+          <t>Event-centre listing → booking form / Host booking requests</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Audit log and admin panels show the same stamps</t>
+          <t>Shortlet/Hire Bookings tab (relay queue)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>Full timestamps on every event</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Every document, confirmation, notification, transaction, application and admin action shows its date AND time to the second in Nigerian time (WAT), using one shared formatter. The Mortgage admin panel shows a handover timeline: documents requested, uploaded, approved, marked sent, buyer confirmed (with the moment CHS was alerted) and final payment released. Plain calendar dates (a lease end, a check-in day) stay as dates.</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Every screen</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Audit log and admin panels show the same stamps</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Newest first everywhere</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Chats, transactions, requests, bookings, earnings and admin lists show the newest first. Upcoming due dates and scheduled inspection dates are the deliberate exception and stay soonest first.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>All dashboards</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -4174,6 +4323,430 @@
       <c r="B17" s="3" t="n"/>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="3" t="n"/>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="3" t="n"/>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="3" t="n"/>
+      <c r="C22" s="3" t="n"/>
+      <c r="D22" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>How it works</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Where to find it (user)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Where to find it (admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Team roles for hotel, lodge and event-centre hosts</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>The owner adds staff by phone number as Manager, Front desk, Housekeeping, Kitchen/bar or Accountant, and can limit each to chosen properties. Each role sees only what it needs; nobody on a team sees the owner's wallet or earnings. Changing or removing a role is recorded.</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Host dashboard → My team</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Audit log</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Duties for staff</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>The owner or a manager assigns a duty to a team member with a priority and an optional due time. The person is notified, marks it done with a note, and the assigner is told. A duty can be cancelled by the owner or a manager. Every step carries the person's name and exact date and time; overdue duties show in red.</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Work page; notification bell</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Audit log</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Shift reports</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Any team member sends a morning, day, evening or night report. The owner and managers read every report; other staff see only their own. The owner is notified when one arrives.</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Work page</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Owner's daily summary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>The evening summary now also counts overdue duties and shift reports sent today.</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Notification bell</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>N/A — automatic</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Spreadsheet import with preview and undo</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Rooms and prices, income, or expenses from an Excel (.xlsx) or CSV file. Columns are matched by their headings and can be corrected; dates are read day-first; every row is checked; nothing is saved until the owner confirms. Imported rooms are switched off, and imported money entries voided, if the import is undone. Imported records keep their original date and also carry the import time.</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Host dashboard → Hotel operations → Import &amp; sync</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Audit log</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Two-way calendar sync (iCal)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>A private calendar link per room can be pasted into Booking.com, Airbnb or Google Calendar so they see nights booked on CHS (dates only, never guest details). Calendar links from other sites can be linked into a CHS room; Sync now blocks the dates booked there and reports any that clash with an existing booking. Dates later removed from the other calendar are flagged for the owner to release. Automatic refresh is not switched on yet.</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Host dashboard → Hotel operations → Import &amp; sync</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Audit log</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Event day control for event centres</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Each paid, confirmed event lists what the client asked for. The owner or a manager records the vendor for each service (ushers, caterer, live band, security, other) and confirms it, which tells the client the vendor's name (never the phone). A run sheet is built from what the client asked for and the team ticks tasks off; every tick records who and when. Tasks can be added, assigned to a person or skipped by the owner or a manager. On the Business plan once plans are switched on.</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Host dashboard and Work page → Event day control</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Audit log</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Plans: Listed, Pro and Business</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Listed is free. Pro and Business are paid from the CHS Wallet for 30 days and renew from the wallet until cancelled; switching up charges only the difference for the unused days. A failed renewal gives 7 days' grace, then the host moves to Listed and records stay readable and downloadable. Paid plans lower the CHS host commission by a set number of percentage points.</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Host dashboard → Plans</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Hotel Controls → Hospitality plans &amp; pilot</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Free pilot and master switch</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>The super admin grants a free pilot (limit 8 operators, 3 months) and sets plan prices and the commission cut. A master switch, off by default, decides whether Pro tools are restricted to paying hosts; while it is off every host can use every tool.</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Hotel Controls → Hospitality plans &amp; pilot</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Super admin only; Audit log</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Digital menu, room orders, sales, stock, recipes and assets</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Hotels keep a menu with prices and income departments. A checked-in guest orders to their room from My Bookings; staff mark it preparing, delivered and paid (cash, transfer, POS or charged to room). A counter sales screen records restaurant and bar sales. Paid sales post to the income ledger by department, delivery deducts stock through recipes, low stock alerts the owner, and an asset register keeps each item's condition history. Guests pay the hotel directly; CHS takes no commission on this.</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Host dashboard and Work → Hotel operations → Menu &amp; stock; guest: My Bookings → Order to your room</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Not shown to admin; Pro features (restricted only when the master switch is on)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Event quotations with a payment schedule</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>The venue sends the client a priced list of extra services with payment dates on or before the event; the client accepts or declines before it expires; the venue records each payment received, which adds to income. Paid directly to the venue, separate from the CHS booking payment, and CHS takes no commission on it.</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Host dashboard and Work → Event day control; client: My Bookings</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Not shown to admin; Business feature (restricted only when the master switch is on); Audit log</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>No hidden prices: complete listings only</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Every listing must show the real price, location, street address, at least five photos, a video, a description and a private contact number before it can go live. The form will not submit without them and the database refuses to approve an incomplete listing. Wording such as DM, inbox or call for price is refused, including on marketplace products and services (a service must show a starting price). Price changes on live listings are shown as a price history.</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>List a property, Edit listing, Owner dashboard (shows what is missing), property page (price history)</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Admin property review shows what is missing and risk warnings (new or unverified owner, possible duplicate, copied photos, unusual price)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>30-day availability confirmation</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Owners of for-sale, rent and lease listings confirm with one tap that the property is still available. A reminder goes out at 25 days and the listing is hidden from the public at 30 days until confirmed. Saving an edit also counts as confirming. Hotel, lodge and event-centre listings are kept current through their calendar.</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Owner dashboard (Confirm available)</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Daily scheduled task sends the reminders</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Report a listing</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Any signed-in person can report a listing for a hidden or wrong price, a fake or copied listing, already taken, scam behaviour or another reason. The owner is never told who reported. Admins dismiss, tell the owner to fix it, or take the listing down; the reporter is told the outcome and the action is logged.</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Property page (Report this listing)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Admin → Listing reports; Audit log</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Trust signals on a listing</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Each live listing shows price shown upfront, whether the owner's ID is verified, the year the owner joined, how recently availability was confirmed, and its price history when the price has changed. None of it reveals who the owner is.</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Property page</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Copied-photo detection</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>When photos are uploaded to a new listing, the browser computes a short fingerprint of each photo and CHS stores the fingerprint, not the photo. A photo that closely matches one already used by a different owner, even after resizing or recompression, raises a warning for the reviewer. Listings created before this was added are not covered.</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>List a property (automatic)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Admin property review: warning on the listing</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>

--- a/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
+++ b/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
@@ -16,15 +16,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Vendor &amp; Marketplace" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. Artisan" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. Admin &amp; Platform Management" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Estate Management, Rent to" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. Real Sale Payment, Escrow," sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Estate Management, Rent to " sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. Real Sale Payment, Escrow, " sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12. Round 3 Client Testing — Re" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13. Agent-Manager Tools, Host-G" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14. Marketplace Rebuild, Guaran" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15. Admin Mediation Completed," sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15. Admin Mediation Completed, " sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16. Hotel, Lodge, Shortlet &amp; Ev" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17. Mortgage Through CHS, Manua" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18. Hospitality Suite Team, Pl" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18. Hospitality Suite- Team, Pl" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19. Venues, Hotels, Groups, Ope" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +35,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,9 +47,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -59,11 +57,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002B2521"/>
+        <fgColor rgb="001F3A5F"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -71,19 +69,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -454,10 +463,10 @@
   <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,17 +497,17 @@
           <t>Registration with role selection</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Buyer, Tenant, Property Owner, Agent, Property Manager, or Commercial Developer — with role-specific extra fields (e.g. professional certificate upload for Managers).</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>New accounts land in Admin → Registrations, pending approval</t>
         </is>
@@ -510,17 +519,17 @@
           <t>NIN uniqueness check</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>A real National Identification Number can only ever be tied to one CHS account.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>N/A — enforced at registration</t>
         </is>
@@ -532,17 +541,17 @@
           <t>Multi-role linking</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>One real identity, one wallet, one login can hold several roles at once (e.g. Owner + Tenant) via "Link Account" rather than a second registration.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Link Account page — every role</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -554,17 +563,17 @@
           <t>Biometric login (Face ID / fingerprint)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Real WebAuthn — uses the device's own secure hardware; CHS never sees or stores the actual biometric data.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Login page + Profile setup — every role</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -576,17 +585,17 @@
           <t>Identity verification (name, gender, age bracket, state, address, occupation, phone, email + ID)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Real, full verification required before any commitment on the platform — an offer, rental application, booking, inspection, or professional engagement. The name typed is compared automatically against the registered name for the reviewing admin. Done once, covers everything after. A NIN is permanently locked to one account, enforced at the database.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Property page (on first commitment) + Profile — every role</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Admin → ID Verification (Registration &amp; Setup domain) — shows the name-match verdict and full details</t>
         </is>
@@ -598,17 +607,17 @@
           <t>Automated Verification System (AVS) — Phase 1: document text match</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>A real first-pass check admin can trigger with one button: reads the actual uploaded ID image using Claude's real vision capability, extracts the printed name and ID number, and compares them against what the applicant typed. A clean match is shown plainly; any discrepancy is flagged with both values shown side by side so admin reviews a specific problem rather than re-reading the whole document. Does not confirm the document is genuine or that a face matches — that remains a human judgment call, or a future Phase 2 using a licensed identity-verification provider (Dojah/VerifyMe/Youverify), a separate cost decision not yet made.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Admin → ID Verification — 🤖 Verify Automatically button on each submission</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Requires an ANTHROPIC_API_KEY secret to be configured on the Supabase project</t>
         </is>
@@ -620,17 +629,17 @@
           <t>Liveness / face verification</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Real document upload plus a genuine, real-time photo capture (never an uploaded photo) reviewed by CHS staff.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Registration / Profile — every role</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Admin → Face Verification (Registration &amp; Setup domain)</t>
         </is>
@@ -642,17 +651,17 @@
           <t>Editable profile with re-verification trigger</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Name, phone, address, and state are genuinely editable. A real name change automatically resets ID/liveness verification.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Profile page — every role</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Real notification to Super Admin on any name change</t>
         </is>
@@ -664,17 +673,17 @@
           <t>Payment safety notice — wallet only</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>The rule that every payment on CHS is made through the person's own CHS Wallet, and that nobody ever pays a person or a bank account, is shown to everyone: a slim line at the top of every page; a prominent card on the Wallet, Login and Registration pages; and a short line beside every pay button (booking pay cards, rent, rent-to-own, offers, inspections, and wherever the payment-protection notice appears). It is also in the FAQ, the in-app guide and the Users Guide, and was sent to every user as a notification. CHS staff and agents never ask anyone to pay into a personal account or share a PIN.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Every page · Wallet · Login · Registration · beside every pay button</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic</t>
         </is>
@@ -686,17 +695,17 @@
           <t>Wallet security layers (transfers and withdrawals)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Protection that proves the account holder is really the one moving money, and limits the damage if they are not. (1) A separate 6-digit transaction PIN, stored hashed, asked for on every transfer and bank withdrawal once set, locked for 30 minutes after 5 wrong tries (compulsory for everyone once CHS switches it on). (2) Only ID-verified users may send money to another CHS user. (3) Limits: per transfer, per day, per hour, and a lower cap on a first transfer to a new recipient for 24 hours. (4) Money received from another CHS user can be used inside CHS but cannot be withdrawn to a bank for 24 hours. (5) A daily withdrawal limit. (6) Instant alerts to the sender and the recipient; large transfers alert admins. (7) A one-tap Freeze my wallet for the account holder (only CHS can lift it). (8) Report this transfer: the amount is held in the recipient's wallet and admins can reverse it while the money is there. (9) Wallet rows are locked during a transfer and a balance can never go below zero. Every number is a setting. Second tranche: (10) Unfamiliar-device checks — the app registers each device; a device new to the account alerts the holder and, for 24 hours, a transfer or withdrawal from it needs a code texted to the phone (once SMS codes are switched on) or is capped at ₦50,000. (11) Texted one-time codes — 6 digits, hashed, valid 10 minutes, 5 tries, 3 requests per 10 minutes, delivered by SMS only (never shown in the app); required at or above ₦200,000 (transfers) / ₦100,000 (withdrawals) or from a new device when switched on; if the SMS cannot be sent the transaction is refused. (12) Money added by card cannot be withdrawn to a bank for 24 hours. (13) An automatic scan every 15 minutes flags unusual patterns (many senders to one wallet, a new account receiving a lot, money going in circles, rapid outflow, a locked PIN) for an admin to clear or freeze.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Wallet → Wallet security; transfer and withdrawal forms; beside every sent transfer</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Admin → Wallet Security (reports, reverse, dismiss, freeze recipient); settings in platform_settings</t>
         </is>
@@ -708,17 +717,17 @@
           <t>Seller's request to release sale money</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>After a property is paid for, the seller's proceeds (price less CHS commission) are held. They are released when the buyer confirms the documents arrived, when CHS confirms delivery, or when the seller asks: the seller taps Request release of my money on the Owner dashboard; CHS sees the request with the delivery record, verifies delivery from the platform's records or by phoning the buyer (recording which), then approves or declines with a reason; the buyer is told the seller says delivery is done so a false claim can be disputed. Every route releases exactly that sale's own held amount, refuses an unpaid or already-released sale, and never touches other money held in the same wallet.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard → sold property → Request release of my money</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Admin → Escrow Oversight → Property sale escrow</t>
         </is>
@@ -730,17 +739,17 @@
           <t>Rent to Own: the owner can decline</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>A request CHS has passed to the owner can be approved or declined. Declining needs a short reason (no contact details), which CHS passes to the buyer; nothing was charged. The owner sees the request at the top of their dashboard, with the CHS reference and never the buyer's phone number.</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard → Mortgage (Rent to Own) requests</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Admin → Rent-to-Own Requests</t>
         </is>
@@ -752,17 +761,17 @@
           <t>Wallet (main + rent savings + maintenance reserve)</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Three real sub-balances per user — a main spending balance plus two dedicated savings pots for rent renewal and maintenance costs.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Wallet page — every role</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Admin → Finance — search any user's real balances, freeze/unfreeze</t>
         </is>
@@ -774,17 +783,17 @@
           <t>Wallet funding via Paystack</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Real, secure card/bank/USSD payment; balance updates automatically once payment genuinely completes.</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Wallet page — every role</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -796,17 +805,17 @@
           <t>Wallet withdrawal to bank</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Only one linked bank account per wallet, for security. Real Paystack transfer to the verified account.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Wallet page — every role</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service, admin sees real withdrawal_requests records</t>
         </is>
@@ -818,17 +827,17 @@
           <t>Wallet-to-wallet transfer</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Send funds directly to another CHS user by phone or email — real-time lookup and instant transfer.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Wallet page — every role</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -840,17 +849,17 @@
           <t>Bank account linking with real-time verification</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>200+ real Nigerian banks with search; the account number is checked against the real bank network before it can ever be linked. Real 48-hour security window on any change.</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Wallet → Link bank account — every role</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service, real-time</t>
         </is>
@@ -862,17 +871,17 @@
           <t>Notification preferences</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Independent real toggles for offers, messages, and marketing notifications.</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Profile page — every role</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -884,17 +893,17 @@
           <t>Diaspora Mode</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>A real setting for CHS users managing property or transactions from outside Nigeria.</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Profile page — every role</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -906,17 +915,17 @@
           <t>Terms &amp; Conditions scroll-to-accept gate</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>A real, meaningful acceptance — the checkbox only unlocks after genuinely scrolling to the bottom. Required before any dashboard is reachable. The Terms carry a version number: when they change (Version 3, October 2026, rewrote term 11 on bookings), everyone is shown what is new and asked to accept once more. Every acceptance is logged permanently with the version and the exact time, and the log cannot be altered.</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>First login — every role</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>N/A — one-time gate per version</t>
         </is>
@@ -928,17 +937,17 @@
           <t>Role-specific first-dashboard guide + persistent Users Guide</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>A short popup on first dashboard visit, plus a full, always-accessible reference page.</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>First login popup + More menu → Users Guide</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>N/A — reference</t>
         </is>
@@ -950,17 +959,17 @@
           <t>Dark mode</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>A real, complete theme system across the whole app, with an app-wide fix ensuring form text stays readable in both modes.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Every page — every role</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>N/A — visual</t>
         </is>
@@ -972,17 +981,17 @@
           <t>PWA install + splash screen</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Installable as a real app on the home screen, with a proper full-screen splash and app icon.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Browser install prompt</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>N/A — visual</t>
         </is>
@@ -994,17 +1003,17 @@
           <t>Guest — its own real role</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>A genuine, separate role from Buyer, for booking a shortlet apartment or a hotel/lodge/event centre/car park stay — its own heading at registration and login, not merged into another role.</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Register / Login page — every role</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1016,17 +1025,17 @@
           <t>Account approval gate</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>A real, enforced rule: a newly registered account cannot use anything beyond the public homepage until CHS staff approve it — previously unenforced despite existing in the database.</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Every page — every role</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Admin → Registrations</t>
         </is>
@@ -1038,17 +1047,17 @@
           <t>Account suspension &amp; appeal</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Real admin tools to suspend a suspicious account with a documented reason, and a genuine appeal channel that stays reachable even while suspended.</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Suspended-account screen — every role</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview, Suspend a Real Account</t>
         </is>
@@ -1060,17 +1069,17 @@
           <t>Self-service account deactivation</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>A real, reversible way to temporarily deactivate your own account — nothing deleted, log back in any time to reactivate.</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Profile page — every role</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1082,17 +1091,17 @@
           <t>Automatic image compression</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Every property photo and profile picture is resized and re-compressed in the browser before upload — no action required, real storage savings confirmed by direct testing.</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Every photo upload — every role</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic</t>
         </is>
@@ -1104,17 +1113,17 @@
           <t>Real-time number validation (phone, NIN, ID, bank account)</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>One shared rulebook checks every phone number, NIN, passport, voter's card, driver's licence, and bank account number as it's typed, on submit, and again in the database itself — so a malformed number can never be saved from any screen.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Every form collecting a phone, ID, or account number — every role</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>N/A — enforced automatically; a malformed existing record is flagged on the ID review screen</t>
         </is>
@@ -1126,17 +1135,17 @@
           <t>Digital receipts</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>A real, printable receipt (Print/Save as PDF) for any transaction — rent, remittance, commission, sale — using the same reference number already generated for it.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>My Receipts page — every role</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1156,10 +1165,10 @@
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1190,17 +1199,17 @@
           <t>Estate Management</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>A real, bounded estate of many housing units under one manager, distinct from delegating individual properties one at a time.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Manager → My Estates</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview</t>
         </is>
@@ -1212,17 +1221,17 @@
           <t>Estate subscription</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Real monthly pricing that scales with unit count, and drops per-unit as an estate grows — paid directly from the manager's wallet.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Manager → My Estates → Subscribe</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1234,17 +1243,17 @@
           <t>Bulk unit onboarding</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Upload a real CSV to add many units at once instead of one at a time — the real answer to onboarding an estate of hundreds of units.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Manager → My Estates → [Estate]</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1256,17 +1265,17 @@
           <t>Estate service charges</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>A real, distinct-from-rent charge billed to every occupied unit at once; vacant units are automatically skipped.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Manager dashboard / Tenant dashboard</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1278,17 +1287,17 @@
           <t>Rent to Own / Mortgage</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A listing category for progressive ownership through monthly instalments, labelled “Mortgage (Rent to Own)” in the app. The buyer must be fully verified and gives their name, phone, occupation, source of funds and address before the request is sent. Every request and every owner answer goes to CHS first: admin relays the request to the owner or rejects it with a reason, and relays the owner's approval or decline to the buyer. The buyer can pay one instalment or any larger amount up to the full balance; every payment goes from the wallet to CHS (instalment + 5.5% buyer commission), is held, and is released to the owner (instalment − 4.5%) by admin, singly or with Release all. The final payment is held until the property documents are handed over. At 100% the property is marked sold. The owner sees the buyer only as a first name and initial plus a CHS reference, never the phone number or full name.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Property listing page / Buyer Mortgage page / Owner dashboard</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Admin → Rent-to-Own: every agreement newest first, with Payments to release</t>
         </is>
@@ -1300,17 +1309,17 @@
           <t>Reminder Engine</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>One real, generic escalation system: rent-due cadence, maintenance follow-up (artisan → manager), and shortlet guest-message escalation (host → admin) — multi-channel (in-app, SMS, email).</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic, background</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1322,17 +1331,17 @@
           <t>Shortlet/Hotel guest-host messaging</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Guest and host never deal with each other directly: every message goes through CHS. Until a booking is paid, each message waits for CHS review and the other side cannot read it; after payment it is delivered at once. Phone numbers and email addresses are refused at all times. The guest never sees who the host is; the host sees the guest's name and a CHS reference, never their phone number.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>My Bookings (guest) / Owner &amp; Host dashboards (host)</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Bookings → message review</t>
         </is>
@@ -1344,17 +1353,17 @@
           <t>Maintenance Reserve — real funding</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>An owner can fund their Maintenance Reserve directly from their Main Wallet for a real, larger repair; artisan payments draw from the Reserve first, and unused funds can be withdrawn back freely.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Wallet page</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1374,10 +1383,10 @@
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1408,17 +1417,17 @@
           <t>Real Sale purchase-price payment</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>The genuine mechanism for a buyer to pay a seller the actual purchase price — not just commission. A single, transparent checkout: the buyer's total automatically includes their own commission (shown as both a percentage and a real value), the seller's net automatically excludes theirs.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Property page, once an offer is accepted</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1430,17 +1439,17 @@
           <t>Real, sourced Sale legal documents</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Certificate of Occupancy, Deed of Assignment, Survey Plan, Governor's Consent, Tax Clearance Certificate, Sale Agreement, and (for a developed property) Building Plan Approval — sourced from genuine Nigerian legal references. Required at listing time; a buyer's payment is blocked until every one is CHS-verified.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>List a property (Sale)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Face Verification tab (Sale documents)</t>
         </is>
@@ -1452,17 +1461,17 @@
           <t>Escrow hold on sale proceeds</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>A seller's real proceeds are visible in their wallet the instant a buyer pays, but not withdrawable until CHS confirms the real, physical legal documents have been transferred to the buyer.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Wallet page</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Admin → Registrations tab (Confirm legal transfer)</t>
         </is>
@@ -1474,17 +1483,17 @@
           <t>Real, admin-reviewed identity verification</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>A buyer's ID submission previously self-certified the instant the form was filled in. Now creates a genuine pending record, reviewed and approved by real CHS staff before it counts.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Making an offer (if not yet verified)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Admin → Registrations tab</t>
         </is>
@@ -1496,17 +1505,17 @@
           <t>Mobile logout</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A working logout in the persistent bottom navigation's More menu — previously only reachable from the homepage.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Bottom nav → More</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1518,17 +1527,17 @@
           <t>Context-aware House Rules</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Only appears for Rent, Lease, Shortlet, and Rent to Own listings — no longer shown on a Sale listing where it never applied.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1540,17 +1549,17 @@
           <t>Real, progressive nearby-properties matching</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>The "similar properties" advertising system now genuinely widens from exact area → LGA → state, and matches property type, rather than matching the whole state regardless of relevance.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Property detail page</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1562,17 +1571,17 @@
           <t>Seller response note on an offer</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>A real, optional message a seller can attach when accepting or declining an offer — delivered directly to the buyer's notification, matching the note a buyer could already leave.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1584,17 +1593,17 @@
           <t>Rent countdown and 90-day non-renewal notice</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>A real, live day-count to next rent on the tenant dashboard, and a genuine notice mechanism that honestly records whether notice was given within or after the requested 90-day window.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1614,10 +1623,10 @@
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1648,17 +1657,17 @@
           <t>Verification review moved to the right place</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>A real, repeated complaint — buyer ID verification submissions "vanished." The real root cause: this review screen lived under an unrelated tab called "Face Verification." Moved into "Registrations," where it's actually found.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Registrations tab</t>
         </is>
@@ -1670,17 +1679,17 @@
           <t>Gender field and a respectful greeting</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>A real gender field at registration — the homepage now greets "Hi Mr. Samson" / "Hi Miss Jennifer" instead of a bare first name.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Register page; Homepage</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1692,17 +1701,17 @@
           <t>Dynamic, per-role comprehension questionnaire</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Real, separate question banks for Buyer, Guest, Tenant, Owner, Agent, and Manager — each genuinely testing that role's own real Terms &amp; Conditions clauses, not one static quiz for everyone.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1714,17 +1723,17 @@
           <t>Required-field markers and auto-scroll-to-error</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>A real red asterisk on every genuinely required field; submitting an incomplete form now scrolls straight to the exact missing field and highlights it in red.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1736,17 +1745,17 @@
           <t>Real State → LGA multi-select for agent coverage area</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A genuine checklist of every real LGA in the agent's state, plus a "Statewide" shortcut that selects them all in one click.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Register page (Agent)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1758,17 +1767,17 @@
           <t>"Others" registration category for artisans, market sellers, and service providers</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>A real, new registration option leading to a genuine "choose your category" page, bridging straight into the existing Artisan and Vendor application forms that were previously unreachable from registration.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Register page; Login page</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1780,17 +1789,17 @@
           <t>Real login for Artisans and Vendors/Service Providers</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Confirmed and fixed a genuine gap: someone approved as an Artisan or Vendor had no way to log back in as themselves. Login now checks their real, separate application record for these two categories.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Login page</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1802,17 +1811,17 @@
           <t>CHS-specific inspection-fee question</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Reworded to specifically ask about a CHS agent acting on CHS's own commission structure — CHS cannot control what an independent agent charges their own client.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1824,17 +1833,17 @@
           <t>Independent agent fee builder and real Total Package</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>An agent listing a property can add any number of named, real fee lines (Custom fee, Legal fee, Agent fee, etc.) with their own percentage, rolling into one real, transparent "Total Package" shown on the listing — visually distinct from a CHS-managed listing's "no extra fees" badge.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>List a property (Agent); Property detail page</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1846,17 +1855,17 @@
           <t>Real, live admin notification bell</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>A genuine, real-time notification bell with an unread badge — database-level triggers now automatically notify admin the instant a new registration or ID verification comes in, regardless of which part of the app created it.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Admin dashboard header</t>
         </is>
@@ -1868,17 +1877,17 @@
           <t>Real shortlet booking data fix</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Found and fixed the actual cause of shortlet bookings failing outright — 20 of 22 real listings were missing their nightly price. Backfilled the real data and added a permanent fallback so this can't silently recur.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Property detail page (Guest)</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1890,17 +1899,17 @@
           <t>Correct role-based landing after login/registration</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Fixed two real, separate bugs sending every role to the generic homepage — the registration redirect, and a completely separate Face ID/fingerprint login path that ignored role entirely.</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Login page; Register page</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1912,17 +1921,17 @@
           <t>Staff login, made discoverable and functional</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Confirmed the Manage-My-Team and staff-reporting features already existed; found and fixed the real, missing piece — a brand-new staff member had no role to register under. "Staff / Employee" is now a real registration option.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Register page; Login page; /staff</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1934,17 +1943,17 @@
           <t>Real "My Properties &amp; Owners Register"</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>A genuine register of every property and owner under an agent/manager's real management — property, address, owner name, owner phone, and agreed commission rate — parallel to the existing tenant register.</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -1956,17 +1965,17 @@
           <t>Real one-step-back navigation</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Fixed a hardcoded "back to homepage" link repeated across 15 real sub-pages — each now genuinely returns one real step, not straight to the homepage.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Every sub-page — every role</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1978,17 +1987,17 @@
           <t>Detailed, consequential guarantor form</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Added real relationship-to-applicant, guarantor address, guarantor occupation, and a genuine, plain-language consent statement — not just a bare name and phone number.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Rental application (Tenant)</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2000,17 +2009,17 @@
           <t>Real, complete rental application review for admin</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Admin can now see full applicant details (occupation, address, income, ID, uploaded document) and full guarantor details, plus which real property and owner it's for — genuine vetting is now possible before forwarding.</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Admin → Applications tab</t>
         </is>
@@ -2022,17 +2031,17 @@
           <t>CHS-mediated owner decision on rental applications</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>An owner's approve/decline is now recorded, not finalized immediately — CHS admin reviews and relays the real, final decision to the applicant, keeping CHS genuinely in the loop both ways.</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard; Admin → Applications tab</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Admin → Applications tab</t>
         </is>
@@ -2052,10 +2061,10 @@
   <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2086,17 +2095,17 @@
           <t>Real team/staff system</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>An agent or manager can invite genuine, separate staff accounts, assign a role label, and see each one's real daily activity report.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard → Manage My Team</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2108,17 +2117,17 @@
           <t>Team/staff subscription</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Free for up to 2 real staff; a real subscription required from the 3rd, tiered by staff count, with exact multi-month discounts (6 months paid → 8 months of real access; 12 paid → 18).</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard → Manage My Team</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2130,17 +2139,17 @@
           <t>Real tenant register and property/owner register</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Per-agent, searchable registers with real ID documents attached, replacing an informal spreadsheet.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Admin → Tenant Register Oversight</t>
         </is>
@@ -2152,17 +2161,17 @@
           <t>Expense tracking, owner remittance, digital receipts</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Real income/expense entries, a real flow for remitting collected rent to the actual owner, and auto-generated digital receipts for completed transactions.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Agent/Manager dashboard → Expenses</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2174,17 +2183,17 @@
           <t>Independent agent commission model and custom fee builder</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A real, adjustable per-owner commission rate, plus any number of named custom fee lines rolling into one transparent Total Package.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard; List a property (Agent)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2196,17 +2205,17 @@
           <t>Host and Guest as real, separate roles</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Split from Owner/Buyer with their own dedicated dashboards, built the same way as every other role.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>/host; /guest</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2218,17 +2227,17 @@
           <t>Real shortlet/hire request-to-book flow</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Superseded by the request-first flow (section 16). History: first rebuilt so a guest saw the true, full cost before committing and a host had to accept or decline; the guest was then charged at request time. Since October 2026 nothing is charged until the host has confirmed the dates.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Property page (Shortlet/Hire)</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Bookings</t>
         </is>
@@ -2240,17 +2249,17 @@
           <t>Real host payout</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Released deliberately by admin, net of the host's own commission — the same CHS-mediated pattern used for sale-proceeds release.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Deposits &amp; payouts</t>
         </is>
@@ -2262,17 +2271,17 @@
           <t>Two-way ratings</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Guest and host can each rate the other once, after a confirmed stay.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Guest dashboard; Host dashboard</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2284,17 +2293,17 @@
           <t>Real, stated cancellation policy</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Server-enforced: full refund 48+ hours before check-in, 50% within 48 hours, none after.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Guest dashboard</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2306,17 +2315,17 @@
           <t>Flexible security deposit</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Host-toggled per listing; applies only to a genuinely first-time guest and auto-waives after their 3rd real rating. Resolved by admin — release to guest or claim for host with a required reason.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>List a property (Shortlet/Hire)</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Deposits</t>
         </is>
@@ -2328,17 +2337,17 @@
           <t>House-rules attestation</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>A guest must now see and check a box agreeing to a property's real house rules before requesting to book — closing a gap where the feature existed for hosts but was invisible to guests.</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Shortlet/Hire booking form</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2350,17 +2359,17 @@
           <t>Dispute-filing for Guest and Host</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>A working dispute form already existed for Tenant/Owner; now genuinely reachable from Guest and Host dashboards too.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Guest dashboard; Host dashboard</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Admin → Disputes tab</t>
         </is>
@@ -2372,17 +2381,17 @@
           <t>Developer as a real, separate role</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Could previously register but had no login path and no dashboard at all. Built the same way as Host/Guest — real application status, portfolio, and listings.</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>/developer</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2394,17 +2403,17 @@
           <t>Real ID-number field per document type</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Fixed a genuine bug: choosing any ID type other than NIN had nowhere to enter that document's own number — the system was silently saving the person's NIN instead. A real, conditional number field now appears per ID type.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Register page</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2416,17 +2425,17 @@
           <t>Multi-role KYC review fix</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Admin's document review only ever checked a person's primary role, missing real credentials attached to a secondary role — found and fixed against a real, in-house test case.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Admin → Registrations tab</t>
         </is>
@@ -2438,17 +2447,17 @@
           <t>Fresh, live document links</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Document links previously relied on a URL signed once and stored permanently — a real structural fragility. Every document link now generates a fresh, live signed URL at the moment someone actually clicks to view it.</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Throughout admin and owner/host document review</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2460,17 +2469,17 @@
           <t>Property reference numbers and admin search</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Every property now has a real, permanent reference number (PROP-000001 style), backfilled for every existing property. A real admin search finds any property by reference, title, or the real owner's name/phone.</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Admin → Properties tab</t>
         </is>
@@ -2482,17 +2491,17 @@
           <t>Real PIN reset</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Phone + NIN verification, since the platform has no email/SMS infrastructure. Did not exist in any form before this.</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Login page → Forgot your PIN?</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2504,17 +2513,17 @@
           <t>Real FAQ page</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Written from CHS's own actual Terms &amp; Conditions and features, not copied from another platform.</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>More menu → Help &amp; FAQs</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2526,17 +2535,17 @@
           <t>Add a role without logging out, plus a role switcher</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>An already-authenticated session now skips the phone/PIN re-verification entirely when adding a role. Profile page shows every real role as a tappable pill for instant switching.</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Profile page → Add another role</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -2548,17 +2557,17 @@
           <t>Desktop splash screen fix</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Reproduced directly with a real screenshot before fixing — a background image built for a phone's tall aspect ratio was being cropped into an unrecognizable dark sliver on a wide desktop screen. Mobile confirmed untouched.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Login page (first load)</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2570,17 +2579,17 @@
           <t>Four new per-role color themes</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Host, Guest, Developer, and Staff — previously quietly borrowing another role's colors — now each have their own genuinely distinct color identity.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>/host; /guest; /developer; /staff</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2600,10 +2609,10 @@
   <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2634,17 +2643,17 @@
           <t>Redesigned receipt and payment voucher</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>A real, branded document — gradient header, a genuine watermark seal, proper serif typography — replacing a plain data table, per direct client feedback.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>/receipt/[reference]</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2656,17 +2665,17 @@
           <t>Real, tiered artisan commission</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>6% for labor under ₦100,000, 8.5% at or above, on labor only — never on materials procured separately. Replaces an earlier flat 10%.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic on job payment</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2678,17 +2687,17 @@
           <t>Marketplace: admin-mediated, contact-filtered messaging</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Every quote request and vendor response is held for real CHS review — a phone number or email in either direction is caught and blocked automatically — before the other party ever sees it.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Marketplace → Request a quote</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Admin → Marketplace Moderation</t>
         </is>
@@ -2700,17 +2709,17 @@
           <t>Marketplace: real, escrow-backed payment</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Accepting an approved quote charges the buyer the real price plus 6%, held in escrow; the vendor receives the price net of 4% only once CHS confirms delivery. Full refund available if a deal falls through.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>My Requests → Accept &amp; Pay</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Admin → Marketplace Moderation</t>
         </is>
@@ -2722,17 +2731,17 @@
           <t>Marketplace: detailed product listings</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A product is described the way established marketplaces describe goods: brand, model, condition (new / refurbished / used), price and unit, stock quantity, SKU, a specification set that is different for each category (for Electronics: product type, size or capacity, features, power, voltage, energy rating, dimensions, weight, what is in the box; for Furniture: type, material, dimensions, assembly, style; and so on), the options a buyer chooses (colour, size, capacity …), warranty, delivery information and up to six photos. Required fields are marked. A service provider instead gives licence, years in operation, team size, response time, availability and what is included.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Vendor dashboard → Add a listing</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Admin → Marketplace</t>
         </is>
@@ -2744,17 +2753,17 @@
           <t>Marketplace: stock and automatic sold-out</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Each listing carries a stock count. When the stock reaches zero the listing is marked Sold out by itself, and it reopens when restocked. The vendor dashboard shows a clear Active / Sold out status badge with an editable stock figure, separate from the manual 'Mark as sold out' action.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Vendor dashboard</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic</t>
         </is>
@@ -2766,17 +2775,17 @@
           <t>Marketplace: orders record what was bought</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>An order records the quantity, the options the buyer chose (colour, size …) and the delivery address, takes stock off, and refuses more than is in stock, an option the vendor does not offer, a missing address, or a product from a vendor CHS has not verified. The buyer sees brand, specification, warranty, delivery information and stock on a details sheet before paying from the wallet.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Marketplace → View details &amp; buy</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Admin → Marketplace Moderation</t>
         </is>
@@ -2788,17 +2797,17 @@
           <t>Marketplace: real direct "Buy Now"</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Sort by price and buy the cheapest listing directly at its own fixed price — no negotiation, no messages to moderate. Same real 6%/4% split and escrow protection.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Marketplace → Buy now</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Admin → Marketplace Moderation</t>
         </is>
@@ -2810,17 +2819,17 @@
           <t>Sister marketplace link (Unify Market Central)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>A real, admin-editable link for procurement CHS's own marketplace doesn't cover — still real, verified sellers, still under CHS's own jurisdiction.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Marketplace; Construction Roadmap; Owner → Maintenance</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview → Edit Real Contact Details</t>
         </is>
@@ -2832,17 +2841,17 @@
           <t>Rental application: real applicant detail shown to owner</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>The owner's review card previously showed only the guarantor's name, phone, and move-in date. Now shows the applicant's real name, ID-verified status, occupation, income, employer, and current address — every field already being collected, now actually displayed.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard → Rental applications</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2854,17 +2863,17 @@
           <t>Independent guarantor verification</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>The applicant provides only the guarantor's name and phone. The guarantor completes every other real field about themselves — address, occupation, relationship, their own ID, and their own typed-name consent — via a private, single-use link, requiring no CHS account. The application cannot reach the owner until this is done.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>New applicant flow → real link sent to guarantor → /guarantor-confirm/[token]</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2876,17 +2885,17 @@
           <t>Event Centre: real capacity tiers and priced facilities</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Real, host-set price tiers by guest count, and a real priced facilities list (lighting, sound, catering per guest, live band, DJ, decoration, generator, security, parking attendants, ushers/event staff) with a live-calculated quotation as the guest selects.</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Event Centre booking form</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Host → Real Event Pricing (/event-pricing/[propertyId])</t>
         </is>
@@ -2898,17 +2907,17 @@
           <t>Event-day add-on requests</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>A real request for music band, caterer, and/or ushers (with a count) on any hire/event booking, visible directly on the host's own dashboard.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Hire/Event booking form</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2920,17 +2929,17 @@
           <t>Real payment regression fixes — rent and Rent-to-Own</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Both previously charged only the base amount, silently omitting the payer's own real, already-invoiced commission. Both now compute and charge the true total in one real payment, shown to the payer beforehand.</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard → Pay rent; Rent-to-Own installment payment</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2942,17 +2951,17 @@
           <t>Stale, uncollected commission alert</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>A real, visible warning on Admin → Finance for any commission invoiced but genuinely uncollected for 2+ hours — an early warning against the exact regression pattern found and fixed above.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Admin → Finance</t>
         </is>
@@ -2964,17 +2973,17 @@
           <t>Clickable notifications with real navigation</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>A rental application's full decision chain — owner decides, CHS relays, tenant is told — now carries a real, working link at every step, straight to the relevant page.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Notification bell, any role</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Notification bell</t>
         </is>
@@ -2986,17 +2995,17 @@
           <t>Real-time notification delivery</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>The notifications table is now genuinely part of Supabase's real-time publication — confirmed missing before, and the actual cause of alerts never appearing without a manual refresh. A real, visible toast now appears the instant a new notification arrives.</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Any dashboard, any role</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Any dashboard</t>
         </is>
@@ -3008,17 +3017,17 @@
           <t>My Applications</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Every real rental application and purchase offer a buyer/tenant has made, queued permanently the moment they apply — no more scrolling the homepage to find it again.</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>/my-applications</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -3030,17 +3039,17 @@
           <t>Recent Applications (owner)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Every real application received across every property, most recent first, regardless of how far down the property list it sits.</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard → Recent Applications</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -3052,17 +3061,17 @@
           <t>Platform Earnings</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>A real, dedicated view of every collected commission — payer name, amount, and timestamp.</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Admin → Platform Earnings</t>
         </is>
@@ -3074,17 +3083,17 @@
           <t>Rent Savings relocated</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Confirmed the tenant dashboard already showed this correctly; removed the redundant duplicate from the general homepage.</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3104,10 +3113,10 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3138,17 +3147,17 @@
           <t>Admin review gate: rental applications and offers, both directions</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>A buyer's offer, and separately an owner's accept/decline decision on that offer, previously reached the other party directly with zero CHS review. Real 'awaiting admin review' and 'owner decided, pending relay' statuses now gate both, matching the marketplace's own real pattern.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Offer submission; owner's accept/decline</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Offer Review</t>
         </is>
@@ -3160,17 +3169,17 @@
           <t>Buyer bio-data required at offer submission</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Real name, phone, occupation, and source of funds — previously an offer required none of this. Shown to admin for real verification; deliberately kept off the owner's own screen, where contact stays mediated through the real message thread instead.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Property page → Make an offer</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Offer Review</t>
         </is>
@@ -3182,17 +3191,17 @@
           <t>Real document review at the point of listing approval</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>The screen where admin approves a new listing previously showed only the title and location, with zero visibility into the real uploaded legal documents. Every document now shows directly on the approval card, with its own view link and verify/reject action — and for Sale properties, the 'Verify' button is genuinely disabled, not just a warning, until every document and the owner's own ID are confirmed verified.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Admin → Properties</t>
         </is>
@@ -3204,17 +3213,17 @@
           <t>Category-aware bedroom display</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Land and other non-residential categories no longer show a bedroom count, regardless of what any individual record's data happens to contain — a real, permanent, shared safeguard rather than a one-off data fix.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Any property listing/detail page</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3226,17 +3235,17 @@
           <t>Real bedroom/bathroom/toilet/room dropdowns</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Replacing plain number inputs with real, selectable dropdowns; a genuinely new, separate toilets count (previously conflated with bathrooms); a repeatable 'Others' facility field for anything not covered.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>List a property</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3248,17 +3257,17 @@
           <t>Processed History</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>A real, permanent archive of every rental application, offer, property listing, and registration CHS has ever decided on — nothing disappears once approved or rejected, the same principle as an old message staying in a real inbox.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Admin → Processed History</t>
         </is>
@@ -3270,17 +3279,17 @@
           <t>Audit Trail</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>A real, permanent, tamper-evident log — no update or delete permission exists for anyone, by design. Covers property decisions, dispute rulings, escrow fund release, account suspension, every admin relay action, referral payouts, marketplace moderation, and agent management changes. Genuinely ongoing — not yet every action in the app.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Admin → Audit Log</t>
         </is>
@@ -3292,17 +3301,17 @@
           <t>Feature Explainer (InfoTip)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>A real, reusable, mobile-first tap/hover explainer, live on 16+ previously-confusing terms across buyer, owner, and tenant screens — commission, escrow, guarantor, CHS Agent ID, rent auto-pay, and others. Genuinely ongoing across the app's 100+ features.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Throughout the app, next to the relevant term</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3314,17 +3323,17 @@
           <t>Property manager listing access</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Managers previously could not list a property at all; agents already could. Fixed to match the identical, existing pattern — no separate database restriction ever existed, only a frontend role gate that had never included managers.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>List a property</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3336,17 +3345,17 @@
           <t>Real room-video system</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>A genuine, cost-free alternative to a paid virtual-tour service. Record or upload a short, real video per room on a new or existing listing; a buyer/tenant can request a specific additional video if unsatisfied, and track that request's real status. Every video plays directly on the property page.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>List/edit a property; Property page → Request a video</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3358,17 +3367,17 @@
           <t>Document Site</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Every current reference document — User's Guide, Terms &amp; Conditions, Feature Catalog, Handover Notes, Fix Tracker, Property Manager Guide, System Documentation — bundled directly into the app for one-tap download.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Admin → Document Site</t>
         </is>
@@ -3388,10 +3397,10 @@
   <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3422,17 +3431,17 @@
           <t>Availability calendar for guests</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Before asking to book, a guest sees every date as available (green, with ‘n left’ where a place has several rooms), requested by another guest (amber, may reopen) or booked (red, crossed out). A guest can check out on the day the next guest arrives. A banner guides the steps — tap arrival, then departure; tapping a later date extends the stay, a date inside it shortens it, and Clear dates resets. It refreshes every minute and clears chosen dates that someone else takes meanwhile, with an explanation. Guests see dates and counts only, never another guest's details. Event centres and halls use the same calendar one day at a time.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Property page → booking form — Buyer / Guest</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -3444,17 +3453,17 @@
           <t>Rooms and room types</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Each hotel, lodge, shortlet or venue listing has individual rooms, grouped into types (Executive, Standard…) with an optional own nightly price and maximum guests. Hosts create rooms in bulk (type “101-112, 201, 204”). A guest picks a type and the system assigns a free room, named in My Bookings once the booking is paid.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Host dashboard → Rooms &amp; calendar</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Bookings</t>
         </is>
@@ -3466,17 +3475,17 @@
           <t>Double-booking guard</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Two guests can never hold the same room on the same night — enforced inside the database, so no screen, timing or shortcut can get around it. Back-to-back stays are allowed. The dates are held from the moment a request is sent, before anything else happens; if they are gone the request fails and the guest is not charged.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Automatic — every booking</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Automatic</t>
         </is>
@@ -3488,17 +3497,17 @@
           <t>Host Rooms &amp; Calendar console</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>A hotel-style chart (rooms down the side, 14 days across). The host records walk-in guests, blocks rooms, or marks every free room unavailable for a period (“Fully booked or closed”). A guest's booking or request cannot be deleted from here; a room with upcoming guests cannot be switched off. One tap — “My calendar is accurate” — confirms a listing, or all of a host's listings at once. A listing's placeholder room can be renamed to a real room number.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Host dashboard / Owner dashboard → Rooms &amp; Calendar</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Bookings → stale-calendar alert</t>
         </is>
@@ -3510,17 +3519,17 @@
           <t>Calendar reminders and stale-calendar alert</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Hosts receive a reminder at 7 am Nigerian time, once a day, until they confirm their calendar. Admin sees a red list of every active hotel, lodge or venue whose calendar has not been confirmed in 3+ days, with the host's phone, number of rooms and pending requests.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Host notification</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Bookings</t>
         </is>
@@ -3532,17 +3541,17 @@
           <t>Request-first booking order</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>The guest sends a request and nothing is charged; CHS relays it to the host; the host confirms the dates are free; the guest then pays within a short window; only then are the dates confirmed. The price is fixed when the request is sent. Every stage holds the dates and has a deadline; overdue stages settle themselves every 5 minutes (an unanswered or unpaid request lapses with nothing to refund; an older request paid at request time is refunded exactly).</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Property page → My Bookings — Buyer / Guest</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Bookings</t>
         </is>
@@ -3554,17 +3563,17 @@
           <t>Urgency lanes and time limits</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>How long each step may take depends on how soon the stay starts (Nigerian time). Standard (more than 3 days away): CHS relays within 4 hours at most, the host has 24 hours, the guest 6 hours to pay. Soon (1–3 days): 30 minutes, 6 hours, 2 hours. Express (today): 10 minutes, 30 minutes, 20 minutes, and an expected arrival time is required. For Soon and Express the guest's wallet must already hold the full amount when the request is sent. Every figure is an adjustable setting.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Booking form + My Bookings</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Platform settings (booking_*)</t>
         </is>
@@ -3576,17 +3585,17 @@
           <t>Instant Confirm (hotels)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>A host can switch on Instant Confirm for a listing. A guest then sees Book now: they pay from their CHS wallet at once and the room is confirmed with no waiting and no admin relay. It is live only while the host's calendar has been confirmed in the last 12 hours, and never for a suspended or inactive listing; otherwise guests see the normal request flow. The host is still paid only after the guest arrives and confirms.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Host dashboard → listing → Instant Confirm; booking form → Book now</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Admin is told of every instant booking</t>
         </is>
@@ -3598,17 +3607,17 @@
           <t>Express: ask up to 3 hotels at once (same-day stays)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>For a stay starting today, the guest can ask up to 2 more hotels with a free room in the same state. CHS relays each request. The first host to confirm wins and the other requests cancel on their own, with the other hosts and the guest told. The guest pays once, for the hotel they get.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Booking form (same-day dates)</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Bookings shows the Express group</t>
         </is>
@@ -3620,17 +3629,17 @@
           <t>Peak pricing</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>CHS keeps a calendar of busy periods (Christmas and New Year, Eid, Easter, Democracy Day). A host switches a period on for a listing with their own percentage and an optional minimum stay, and can add their own events. The guest sees the busy nights, the busy-period names and the full price before booking; where periods overlap, the highest uplift applies to that night.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Host dashboard → listing → Peak pricing; booking form price breakdown</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Admin → Hotel Controls → Peak periods</t>
         </is>
@@ -3642,17 +3651,17 @@
           <t>Host cancels a confirmed booking: consequences</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>The guest is refunded in full and the cancelled dates stay blocked. The host pays the bank processing fee. First cancellation in 90 days is a warning, the second costs 10 percent of the booking value (taken from the wallet and later payouts), the third suspends the listing until CHS reviews it. The host sees the consequence before confirming and must give a reason with no contact details. Admins are alerted to help the guest rebook.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Host dashboard → a confirmed booking → Cancel</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Admin → Hotel Controls → cancellations and Reinstate; settings host_default_penalty_pct and host_default_window_days</t>
         </is>
@@ -3664,17 +3673,17 @@
           <t>Digital check-in and front desk</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Once a booking is confirmed the guest gets an arrival pass with a code (XXXX-XXXX), can fill in the registration card ahead of time, and on arrival day taps I've arrived (checked against the hotel location when the host has set one, within 1 km). The front desk is told. If the host set a self check-in code, it appears only after the guest taps I've arrived. Hosts and the front-desk staff they add see today's arrivals, verify a pass, check the guest in, and record a no-show from 12:00 the day after check-in (the host is paid under the cancellation terms, the deposit goes back to the guest, the room is freed).</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>My Bookings (guest); Host dashboard → Front Desk (/host/arrivals); Host dashboard → Front-desk staff</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Admin can view any arrivals board</t>
         </is>
@@ -3686,17 +3695,17 @@
           <t>Housekeeping board (hotels)</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Every room shows live as occupied, to clean, ready, inspected or out of order. A room whose guest has left (after noon Nigerian time) appears as to-clean by itself. Front-desk staff tap Cleaned, Inspected or Out of order, and each change records who did it and the exact date and time.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Host dashboard → listing → Hotel operations → Housekeeping</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
@@ -3708,17 +3717,17 @@
           <t>Repairs and maintenance tickets (hotels)</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Staff log a fault against a room or the whole property with a priority; an urgent fault alerts the owner at once. A ticket moves from open to in progress to done, with the repair cost and a note, and every step carries its exact date and time.</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Host dashboard → listing → Hotel operations → Repairs</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
@@ -3730,17 +3739,17 @@
           <t>Other income centres (hotels)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Restaurant, bar, laundry, gym, events and walk-in rooms: staff record each sale with an amount and note; the entry is stamped with who and exactly when. A wrong entry is voided with a reason — it stays on the ledger, struck through, never erased.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Host dashboard → listing → Hotel operations → Money</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
@@ -3752,17 +3761,17 @@
           <t>Expenses (hotels, owner only)</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>The owner records salaries, utilities, food and drink, supplies, repairs, marketing, taxes and other costs, each stamped with who and when, voidable with a reason.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Host dashboard → listing → Hotel operations → Money</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
@@ -3774,17 +3783,17 @@
           <t>Hotel financial report and ledger (owner only)</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>For any date range up to a year: occupancy %, room-nights sold, average room rate (ADR), revenue per available room (RevPAR), room revenue less CHS commission, other income by centre, expenses by category, repair costs and the net result. A ledger lists every booking, income, expense and repair newest first and downloads as a CSV file.</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Host dashboard → listing → Hotel operations → Money</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
@@ -3796,17 +3805,17 @@
           <t>Guest welcome, thank-you and owner daily summary (hotels)</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>At check-in the guest gets a welcome notification. After check-out they get a thank-you with a request to review. Each evening (8 pm Nigerian time) the owner gets one summary: arrivals, departures, guests in-house, rooms to clean, open repairs and other income today. These are in-app alerts now; WhatsApp delivery needs a WhatsApp Business account to be connected.</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Notification bell</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic</t>
         </is>
@@ -3818,17 +3827,17 @@
           <t>Contact always through CHS (documents, tenants, landlords)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>A buyer's delivery phone number is kept by CHS to coordinate the hand-over of sale documents; the seller never sees it, and the database refuses a direct read. Tenants and landlords likewise see no phone number for each other, only a message button.</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard, My Rented Space, document delivery form</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Admin → held funds shows the delivery contact for CHS to use</t>
         </is>
@@ -3840,17 +3849,17 @@
           <t>Admin relay queue</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Every request comes to CHS first, in every lane — guest and host never deal directly. The queue lists requests in three groups (waiting to be relayed, with the host, waiting for the guest to pay), urgent first and in red, each with a countdown and the host's phone number. Admin relays with one tap and an optional note, or declines with a reason (the guest pays nothing). A short automatic relay remains only as a safety net if nobody acts, with an alert to admin.</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Bookings</t>
         </is>
@@ -3862,17 +3871,17 @@
           <t>Pay-now card and live countdown</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>My Bookings and the Guest dashboard show where a booking stands in plain words with a live countdown. When the host confirms, a green card shows the exact amount and breakdown with a Pay now button; a wallet shortfall gives a clear message and a Top up link. An unpaid request can be withdrawn at any time at no cost. The page after sending a request says “Request sent — nothing has been charged”.</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>My Bookings / Guest dashboard</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3884,17 +3893,17 @@
           <t>Arrival confirmation and prompt payout</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Booking is prepaid: the guest pays first, and the host is paid when the guest ARRIVES — not after the stay. From the check-in day the guest ticks a short checklist on their booking: they have arrived and can get in, the property matches its listing, each listed facility (or each facility booked, for a venue) is present and working, and everything is in good order, with an optional message. That releases the host's payout at once and sends the message to the host and to CHS. If something is wrong the guest reports a problem instead: the money stays held and CHS and the host are alerted. If the guest says nothing, the payout is released automatically 24 hours after the 2 pm check-in time unless a problem was reported. A host whose guest has arrived can ask CHS to release; CHS sees the request, whether the guest has confirmed, and releases with one tap. Older pay-first bookings are released by CHS from its list.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>My Bookings / Guest dashboard (guest); Owner &amp; Host dashboards (host)</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Bookings → stays awaiting release</t>
         </is>
@@ -3906,17 +3915,17 @@
           <t>House rules for hotels, lodges, venues and hosts</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Any shortlet, hotel, lodge, event-centre or other hire listing can carry a House Rules document, uploaded by the owner from the Owner dashboard or by a host from the Host dashboard. Guests must read and acknowledge it before they can send a booking request.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard / Host dashboard → listing → House rules; booking form (guest)</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Admin → listing review</t>
         </is>
@@ -3928,17 +3937,17 @@
           <t>Host requests panel</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>A red panel at the very top of both the Owner and Host dashboards lists every request awaiting the host: the hotel, the guest's name with a CHS identity-verified mark and a CHS reference (never their phone number or ID), dates, expected arrival, what the host would receive, a countdown, and Confirm — dates are free / Decline. Urgent requests are flagged. The notification links to the right dashboard for the person's role.</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard / Host dashboard (top)</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3950,17 +3959,17 @@
           <t>Message review and contact-detail filter</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Messages between a guest and a host are reviewed by CHS before delivery until the booking is paid (one setting keeps review on for paid bookings too); the other side cannot read an unreviewed message, even by querying the database; messages cannot be written into the table directly. Phone numbers and email addresses are refused for everyone, always. The shared filter ignores ordinary dates, times and numbers but still catches disguised numbers, and also protects offers and the marketplace.</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>My Bookings / Host dashboard (Messages)</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Bookings → message review</t>
         </is>
@@ -3972,17 +3981,17 @@
           <t>Payment, commission and payout</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>The guest pays before arriving; CHS holds the money only until the guest arrives and confirms. Both CHS commissions — the guest's and the host's — are recorded as collected at the moment the guest pays, as with rent and sale. The host's net payout is released the moment the guest confirms arrival (see the next entry), by admin on a host's request, or automatically 24 hours after check-in; all three go through one routine that refuses anything not actually held and pays the host the price net of CHS's commission.</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Wallet / My Bookings</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Admin → Escrow Oversight; Platform Earnings</t>
         </is>
@@ -3994,17 +4003,17 @@
           <t>Cancellation and refunds</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>An unpaid request is withdrawn at no cost. A paid booking cancelled 48+ hours before check-in is refunded in full (and CHS keeps no commission); within 48 hours, 50%; on or after check-in, none; a booking the host never confirmed is always refunded in full; a security deposit is always returned. The part not refunded is split: the unrefunded stay price goes to the host as compensation for the dates held (less CHS's commission on it; the host's share is a setting, default 100%) and CHS keeps its service fee on it. The guest, host and admin are each told the exact amounts, and refund + host + CHS always equals what was paid. If a host fails to honour a confirmed booking, term 36 applies instead.</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>My Bookings / Guest dashboard</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Admin → Escrow Oversight</t>
         </is>
@@ -4021,13 +4030,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4058,17 +4067,17 @@
           <t>Installments held, then released by CHS</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>A mortgage installment never goes straight to the owner. It is debited from the buyer, held in the owner's CHS hold with the commission rows recorded, and appears in Admin → Rent-to-Own → Payments to release. Admin releases it to the owner's wallet, singly or all at once, and each release is written to the audit log.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Buyer Mortgage page / Owner earnings</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Rent-to-Own → Payments to release</t>
         </is>
@@ -4080,17 +4089,17 @@
           <t>Document handover for a mortgage</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>After the final payment the buyer asks for the documents (recipient, address, phone, method, maximum days). The owner uploads the documents for CHS to check; admin approves or asks for changes; the buyer receives the approved soft copy in the app; the owner then marks the hard copy as sent with a receipt or proof; the buyer taps I have received my documents. Every step notifies the others through CHS, and the buyer's delivery phone number is seen only by CHS.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Buyer Mortgage page / Owner dashboard (Step 1 and Step 2) / Admin</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Rent-to-Own → document review and handover</t>
         </is>
@@ -4102,17 +4111,17 @@
           <t>Final payment released by a super admin only</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>The buyer confirming receipt does not move money. It marks the handover as confirmed and alerts admin; the final payment stays held until a super admin releases it. A sub-admin sees a notice instead of the button. Without owner proof or buyer confirmation, a note of at least ten characters explaining how the handover was verified is required.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Admin → Rent-to-Own</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Super admin only; audited as rto_final_released</t>
         </is>
@@ -4124,17 +4133,17 @@
           <t>Auto-release tick box (off by default)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>A box at the top of the Rent-to-Own desk. Only a super admin can tick it, after a confirmation prompt, and each change is audit-logged. When ticked, the buyer's confirmation releases the final payment immediately; when not ticked, release is manual. Meant for busy periods with many releases due at once.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Admin → Rent-to-Own</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Super admin only; setting rto_final_auto_release</t>
         </is>
@@ -4146,17 +4155,17 @@
           <t>Reversal of a final release</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A super admin can return an already released final payment to CHS hold with a written reason of at least ten characters. The money moves from the owner's wallet back into hold, the agreement returns to awaiting handover, the owner is notified and the reversal is audit-logged. It refuses if the owner has already moved the money.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Database function used by super admin</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Super admin only; audited as rto_final_release_reversed</t>
         </is>
@@ -4168,17 +4177,17 @@
           <t>Host cancellation strikes</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>A host who cancels a confirmed booking that has not started must give a reason of at least ten characters without contact details. The guest is refunded in full, the dates stay blocked, and the bank fee is charged to the host. Within 90 days: strike 1 is a warning, strike 2 a 10% penalty collected from later payouts, strike 3 suspends the listing. Admin sees the strikes and can reinstate a listing with a note.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Host dashboard / Admin</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Admin → host strikes and reinstate listing</t>
         </is>
@@ -4190,17 +4199,17 @@
           <t>Hotel digital check-in</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Each confirmed booking gets an arrival code. The guest fills a registration card, taps I have arrived (checked within 1 km of the hotel when its location is set) and sees the lockbox code only on stay days, each viewing audit-logged. The front desk (host, staff the host adds by phone, or admin) uses an arrivals board to verify the pass and check the guest in, or marks a no-show from noon the day after.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Guest My Bookings / Host front desk</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Admin can act as front desk</t>
         </is>
@@ -4212,17 +4221,17 @@
           <t>Notification bell on every dashboard</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Each role's own dashboard carries its own bell, and tapping a notification opens the exact page and item it is about, even when you are already on that page.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Every dashboard</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Admin feed opens the matching admin tab</t>
         </is>
@@ -4234,17 +4243,17 @@
           <t>Event services request (ushers, caterer, live band, security, other)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>On every event-centre booking (priced-capacity form and the date-range form) the guest ticks the services they want: ushers (with a number), caterer, live band, security personnel (with a number), and a free-text line for anything else such as an MC, DJ, photographer or decoration. The request goes through CHS to the venue and is shown to the host with the booking request; nothing is charged until the venue confirms. Venues can also list priced facilities (lighting, sound, catering per guest, band, DJ, security, parking attendants, ushers) that add to the quotation.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Event-centre listing → booking form / Host booking requests</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Shortlet/Hire Bookings tab (relay queue)</t>
         </is>
@@ -4256,17 +4265,17 @@
           <t>Full timestamps on every event</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Every document, confirmation, notification, transaction, application and admin action shows its date AND time to the second in Nigerian time (WAT), using one shared formatter. The Mortgage admin panel shows a handover timeline: documents requested, uploaded, approved, marked sent, buyer confirmed (with the moment CHS was alerted) and final payment released. Plain calendar dates (a lease end, a check-in day) stay as dates.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Every screen</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Audit log and admin panels show the same stamps</t>
         </is>
@@ -4278,81 +4287,21 @@
           <t>Newest first everywhere</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Chats, transactions, requests, bookings, earnings and admin lists show the newest first. Upcoming due dates and scheduled inspection dates are the deliberate exception and stay soonest first.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>All dashboards</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4365,13 +4314,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4402,17 +4351,17 @@
           <t>Team roles for hotel, lodge and event-centre hosts</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>The owner adds staff by phone number as Manager, Front desk, Housekeeping, Kitchen/bar or Accountant, and can limit each to chosen properties. Each role sees only what it needs; nobody on a team sees the owner's wallet or earnings. Changing or removing a role is recorded.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Host dashboard → My team</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
@@ -4424,17 +4373,17 @@
           <t>Duties for staff</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>The owner or a manager assigns a duty to a team member with a priority and an optional due time. The person is notified, marks it done with a note, and the assigner is told. A duty can be cancelled by the owner or a manager. Every step carries the person's name and exact date and time; overdue duties show in red.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Work page; notification bell</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
@@ -4446,17 +4395,17 @@
           <t>Shift reports</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Any team member sends a morning, day, evening or night report. The owner and managers read every report; other staff see only their own. The owner is notified when one arrives.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Work page</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4468,17 +4417,17 @@
           <t>Owner's daily summary</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>The evening summary now also counts overdue duties and shift reports sent today.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Notification bell</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic</t>
         </is>
@@ -4490,17 +4439,17 @@
           <t>Spreadsheet import with preview and undo</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Rooms and prices, income, or expenses from an Excel (.xlsx) or CSV file. Columns are matched by their headings and can be corrected; dates are read day-first; every row is checked; nothing is saved until the owner confirms. Imported rooms are switched off, and imported money entries voided, if the import is undone. Imported records keep their original date and also carry the import time.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Host dashboard → Hotel operations → Import &amp; sync</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
@@ -4512,17 +4461,17 @@
           <t>Two-way calendar sync (iCal)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>A private calendar link per room can be pasted into Booking.com, Airbnb or Google Calendar so they see nights booked on CHS (dates only, never guest details). Calendar links from other sites can be linked into a CHS room; Sync now blocks the dates booked there and reports any that clash with an existing booking. Dates later removed from the other calendar are flagged for the owner to release. Automatic refresh is not switched on yet.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Host dashboard → Hotel operations → Import &amp; sync</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
@@ -4534,17 +4483,17 @@
           <t>Event day control for event centres</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Each paid, confirmed event lists what the client asked for. The owner or a manager records the vendor for each service (ushers, caterer, live band, security, other) and confirms it, which tells the client the vendor's name (never the phone). A run sheet is built from what the client asked for and the team ticks tasks off; every tick records who and when. Tasks can be added, assigned to a person or skipped by the owner or a manager. On the Business plan once plans are switched on.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Host dashboard and Work page → Event day control</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Audit log</t>
         </is>
@@ -4556,17 +4505,17 @@
           <t>Plans: Listed, Pro and Business</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Listed is free. Pro and Business are paid from the CHS Wallet for 30 days and renew from the wallet until cancelled; switching up charges only the difference for the unused days. A failed renewal gives 7 days' grace, then the host moves to Listed and records stay readable and downloadable. Paid plans lower the CHS host commission by a set number of percentage points.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Host dashboard → Plans</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Admin → Hotel Controls → Hospitality plans &amp; pilot</t>
         </is>
@@ -4578,17 +4527,17 @@
           <t>Free pilot and master switch</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>The super admin grants a free pilot (limit 8 operators, 3 months) and sets plan prices and the commission cut. A master switch, off by default, decides whether Pro tools are restricted to paying hosts; while it is off every host can use every tool.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Admin → Hotel Controls → Hospitality plans &amp; pilot</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Super admin only; Audit log</t>
         </is>
@@ -4600,17 +4549,17 @@
           <t>Digital menu, room orders, sales, stock, recipes and assets</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Hotels keep a menu with prices and income departments. A checked-in guest orders to their room from My Bookings; staff mark it preparing, delivered and paid (cash, transfer, POS or charged to room). A counter sales screen records restaurant and bar sales. Paid sales post to the income ledger by department, delivery deducts stock through recipes, low stock alerts the owner, and an asset register keeps each item's condition history. Guests pay the hotel directly; CHS takes no commission on this.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Host dashboard and Work → Hotel operations → Menu &amp; stock; guest: My Bookings → Order to your room</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Not shown to admin; Pro features (restricted only when the master switch is on)</t>
         </is>
@@ -4622,17 +4571,17 @@
           <t>Event quotations with a payment schedule</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>The venue sends the client a priced list of extra services with payment dates on or before the event; the client accepts or declines before it expires; the venue records each payment received, which adds to income. Paid directly to the venue, separate from the CHS booking payment, and CHS takes no commission on it.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Host dashboard and Work → Event day control; client: My Bookings</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Not shown to admin; Business feature (restricted only when the master switch is on); Audit log</t>
         </is>
@@ -4644,17 +4593,17 @@
           <t>No hidden prices: complete listings only</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Every listing must show the real price, location, street address, at least five photos, a video, a description and a private contact number before it can go live. The form will not submit without them and the database refuses to approve an incomplete listing. Wording such as DM, inbox or call for price is refused, including on marketplace products and services (a service must show a starting price). Price changes on live listings are shown as a price history.</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>List a property, Edit listing, Owner dashboard (shows what is missing), property page (price history)</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Admin property review shows what is missing and risk warnings (new or unverified owner, possible duplicate, copied photos, unusual price)</t>
         </is>
@@ -4666,17 +4615,17 @@
           <t>30-day availability confirmation</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Owners of for-sale, rent and lease listings confirm with one tap that the property is still available. A reminder goes out at 25 days and the listing is hidden from the public at 30 days until confirmed. Saving an edit also counts as confirming. Hotel, lodge and event-centre listings are kept current through their calendar.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard (Confirm available)</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Daily scheduled task sends the reminders</t>
         </is>
@@ -4688,17 +4637,17 @@
           <t>Report a listing</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Any signed-in person can report a listing for a hidden or wrong price, a fake or copied listing, already taken, scam behaviour or another reason. The owner is never told who reported. Admins dismiss, tell the owner to fix it, or take the listing down; the reporter is told the outcome and the action is logged.</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Property page (Report this listing)</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Admin → Listing reports; Audit log</t>
         </is>
@@ -4710,17 +4659,17 @@
           <t>Trust signals on a listing</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Each live listing shows price shown upfront, whether the owner's ID is verified, the year the owner joined, how recently availability was confirmed, and its price history when the price has changed. None of it reveals who the owner is.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Property page</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
@@ -4732,51 +4681,723 @@
           <t>Copied-photo detection</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>When photos are uploaded to a new listing, the browser computes a short fingerprint of each photo and CHS stores the fingerprint, not the photo. A photo that closely matches one already used by a different owner, even after resizing or recompression, raises a warning for the reviewer. Listings created before this was added are not covered.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>List a property (automatic)</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Admin property review: warning on the listing</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>CHS stamp and tag ID</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>CHS admins award a listing one of two stamps: Managed &amp; Advertised by CHS, or Advertised by CHS. A unique tag such as CHS-100002-3 is created automatically the first time and kept if the stamp is later removed and given back. Owners and agents cannot set or change the stamp or tag. The stamp shows as a corner label on listing cards, a banner with the tag on the listing page, and a printable sign.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Property cards, property page, Managed by CHS page</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Admin → CHS stamp; Audit log</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Check a CHS tag</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Anyone, without logging in, types a tag from a signboard, flyer or forwarded advert and sees whether CHS issued it, whether it is still active, and which property it belongs to. A mistyped tag is recognised as a typing error. A tag that was never issued, or whose stamp was removed, is shown as not genuine, so a copied badge cannot pass.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>/verify-chs and /verify-chs/(tag)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Managed by CHS search</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>A button on the home page and a tick box in the search panel show only CHS-stamped listings, and CHS-stamped listings are always loaded and sorted ahead of unstamped ones. The Managed by CHS page explains the stamps and lists every stamped property.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Home page, Search &amp; filter, /chs-managed</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Move-in cost breakdown</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Every rent listing shows what a tenant pays to move in: rent, the CHS service fee, and any fees the lister declared, added up into one total. On a CHS-managed listing it states there is no agent, legal, RCD or inspection fee. On other listings it tells the tenant to ask for every fee in writing.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Property page (rent listings)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Printable CHS sign</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>For a stamped property, a printable sheet with the CHS seal, the tag, and a QR code that opens the tag check page, for signboards, flyers and status posts.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Admin → CHS stamp → Printable stamp sheet</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Admin → CHS stamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Rent by instalments</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>On a CHS-managed rental the owner can allow quarterly or monthly rent (full-year is always allowed). The tenant picks a plan at first payment or within 30 days of renewal, sees the schedule and pays each instalment into escrow. The management fee is taken in equal parts, reminders go out before and after each due date, and CHS does not guarantee an unpaid instalment.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Owner page (My Properties), My Rented Space, listing page cost card</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Overdue instalments notify admins</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Viewing time slots</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>An owner sets weekly viewing windows (day, hours, slot length) and dates they are away. A visitor booking an inspection then picks one free slot instead of suggesting any time. Each slot can be booked once, booked slots disappear from the list, and either side can move a visit to another free slot. Confirmed visits get reminders a day before and a few hours before. The owner sees a warning if a visitor has missed earlier visits. A property with no windows set works as before.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Owner page (My Properties), Book inspection form, My Inspections</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>CHS-approved agent badge</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Only for registered companies and firms (CAC company, ESVARBON firm or QSRBN firm); individuals cannot hold it. The database refuses approval unless KYC is complete and under 12 months old, the firm has at least 10 income-generating transactions on CHS in the last 180 days, its registration is current, it accepted the badge terms, and a CHS officer ticked eight manual checks (ID/NIN/face match, address, directors' KYC, register check, office, two references, adverse record, fee conduct). Valid 12 months; it hides itself on lapse, expired registration, stale KYC or suspension, and admins can remove it with a reason. Anyone can check an agent ID without logging in.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Agent dashboard (application), Admin &gt; CHS stamp, property page strip, /verify-agent</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Admin &gt; CHS stamp &gt; CHS-approved agent badge</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Owner at-a-glance summary</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>At the top of the owner dashboard, one card across all of an owner's properties: what needs them (past visits to mark, overdue instalments, applications, offers, questions, visits this week, tenancies ending, notices), the money (wallet, escrow, rent awaiting release, rent released in the last 30 days, annual rent under lease) and a row per property, busiest first. Read-only, from one database call.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Owner dashboard (top)</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Ask CHS to manage this property</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>On each of their properties an owner can press Ask CHS to manage this property, choose rent, shortlet, sale and/or hotel or commercial, say in what capacity they act, upload the required documents, read the full terms (scroll to the end), answer three short questions, and tick to accept. The request goes to CHS. The owner can withdraw it while pending, and can later ask CHS to stop managing the property.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>My Properties (owner)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Admin → CHS stamp (top of page)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Approve CHS management and stamp</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Admin sees each request with the owner's ID status, capacity, uploaded documents, purposes, fees shown and the time the terms were accepted. Approval needs a tick that the documents were checked, and for a hotel the agreed base fee, incentive fee and term. Approve turns on the Managed &amp; Advertised by CHS stamp and issues the tag (the listing must be verified first). Decline needs a reason. When an arrangement ends, one button removes the stamp. The owner is told each time and every action is audit-logged.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Admin → CHS stamp</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Admin → CHS stamp; Audit log</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Management fee replaces the owner-side fee</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>On a CHS-managed rent listing the owner pays the 10% management fee instead of the standard 4% owner-side fee; on a CHS-managed sale the seller pays the tiered sale-negotiation fee (8% down to 3%) instead of 6%. Tenant and buyer fees are unchanged. The owner's earnings screen shows the fee that applies. Renewal-year commission and host-side shortlet and hotel booking commission are not yet adjusted in code; the terms promise a credit on the statement.</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Owner earnings, tenancy approval, sale commission</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Platform settings: managed_rent_fee_pct, managed_rent_fee_min</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>How it works</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Where to find it (user)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Where to find it (admin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Event-centre advance (60%)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>After the guest pays, CHS holds the money. About 48 hours before the event it releases an advance (default 60%, 0 = off, never above 90%) of what the venue will earn (booking price less the venue's service charge) to the venue's wallet. The balance is released after the event. Settings: event_advance_pct and event_advance_release_hours.</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Host wallet; Host console</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Admin → Event Centres → Release advance now (pays it early)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Advance on event services</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Each service the guest buys for an event (ushers, catering, band, security) pays the venue, or the provider CHS found, an advance before the event and the balance after. Services paid after the hall advance get their advance straight away.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Host console; guest booking</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Admin → Service sourcing → payouts (advance and balance buttons for CHS-sourced providers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Advance clawback on cancellation</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>If an event is cancelled or refunded after an advance was paid, the advance is taken back from the venue's wallet before the guest's refund is worked out. Any shortfall is recorded as owed to CHS and admin is alerted.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Automatic</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Admin → Event Centres (recover-due shown)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Event risk class</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Each event is marked routine, managed or enhanced from its type (for example concerts, festivals, political events) and size (200+ and 1,000+ guests) so staff know which need a closer look.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Not shown to guests</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Admin → Event Centres (badge)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Event booking documents</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>The organiser attaches documents (permit, police clearance, ID, programme) to an event booking, up to 20, stored privately. Only the organiser, the venue and admin can open them, through a short-lived link. A removed document is hidden, not erased.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Booking → Documents (guest); Host console (venue)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Admin → Event Centres (document count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Licensed capacity</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>A venue states its licensed capacity; admin verifies it against the operating permit (changing it clears the verification). A booking for more guests than the capacity is refused by the database and the booking form.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Event pricing page; booking form</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Admin → Event Centres → verify capacity</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Venue profile</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Parking spaces, power backup and fire-safety notes, shown to guests before they book. Contact details are refused.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Event pricing page; booking form</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Seating layouts and diagrams</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>The venue lists the layouts it can set up (banquet, theatre, classroom, U-shape, standing, boardroom) and may set the most guests each holds. The guest picks one from small diagrams under Services and changes; one too small for the guest count is greyed out and refused. The venue is notified and sees the choice.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Venue profile; Services and changes; Host console</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Several rooms in one request</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>A guest chooses the number of rooms, adults and children. Each room is its own booking, linked as a room group; the host confirms them and the guest sees 'Room 2 of 3'.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Booking form; Bookings</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Admin → Hotels &amp; Lodges (live)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Pay all rooms at once</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Pays every awaiting room of a linked group in one step after checking the wallet covers the total.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>My bookings</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Hotel stay extras</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Breakfast, half board, full board, extra bed, airport pickup, laundry, early check-in, late check-out, cleaning and baby cot are requested through CHS; the host answers with a price and the guest pays through CHS.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Extras and changes</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Admin → Service sourcing</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Public rating summary</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>A property page shows its average and number of ratings. A guest can rate only after the stay has started, and a rating with contact details is refused.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Property page</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Search by dates</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Pick check-in and check-out on the home page; only hotels, lodges and shortlets free on every night are shown.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Home page</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Accessibility filter and tags</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Hosts tick accessibility features when listing (for example step-free access); guests filter on them.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>List property; Home page</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Weekly and monthly discounts</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>A host offers a weekly discount (7+ nights) and a monthly discount (28+ nights), up to 50%. The price shows the gross, the discount line and the discounted total; CHS's fees are worked out on the discounted price.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Host page → Stay offers; booking form</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Group and corporate enquiries</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>A guest sends a group enquiry (name, organisation, guests, rooms, dates, purpose, message) to the host through CHS. Contact details are refused and five a day is the limit. The host reads them under Stay offers.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Property and hotel pages; Host page</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Open fields and stadiums</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>New hire categories with a ground-details profile: surface, floodlights, toilets, changing rooms, safe crowd limit, rain plan, noise or curfew rules, safety notes. Guests see it on the property page.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>List property; Host page; Property page; Guest page tabs</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>VAT recording on CHS fees</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>OFF by default. When a super admin switches it on (a tax ID is required), VAT is treated as included in each CHS fee collected: guest and host amounts do not change. Each fee gets a ledger entry with its VAT part; a refund reverses it. Monthly report with CSV: fees collected, VAT to remit, fee excluding VAT, VAT reversed. Fees collected before the switch are not back-filled. Not a tax filing; the accountant confirms rate and registration.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Admin → Financial → VAT on CHS fees</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4792,10 +5413,10 @@
   <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4826,17 +5447,17 @@
           <t>Location + price search</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Filter by state, LGA, area, property type, minimum bedrooms, and a real minimum/maximum price range.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Homepage search — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4848,17 +5469,17 @@
           <t>Rent / Sale / Shortlet tabs</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Real filtering of the whole catalog by purpose.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Homepage — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4870,17 +5491,17 @@
           <t>Saved Properties &amp; Saved Searches</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Save individual listings, or save a whole search to be matched automatically as new listings arrive.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Saved page — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -4892,17 +5513,17 @@
           <t>Making an offer (sale)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Propose a real price directly to the owner; goes through a real CHS Sale Approvals checkpoint before anything moves to escrow.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Property detail page — Buyer</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Admin → Sale Approvals (Owner/Buyer/Tenant domain)</t>
         </is>
@@ -4914,17 +5535,17 @@
           <t>Rental application + independent guarantor confirmation</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A real application, screened by CHS staff before the owner ever sees it. The applicant provides only their guarantor's name and phone number; the guarantor completes everything else — address, occupation, their own ID, a real proof of address, and a signed confirmation — independently, through their own private link, and cannot share the applicant's surname.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Property detail page — Tenant; guarantor's own link</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Admin → Applications (Owner/Buyer/Tenant domain)</t>
         </is>
@@ -4936,17 +5557,17 @@
           <t>Inspection booking + transport fee</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>A physical inspection is a last resort: photographs, room videos and requests for more of either are free. If a buyer or tenant still insists on visiting, the WHOLE round-trip transport cost is theirs — not split with the owner, not carried by CHS — at ₦150 per km each way, from where the CHS agent actually sets off. Booking takes nothing; CHS assigns an agent and records their takeoff point and distance, which fixes the final cost. The requester then pays it FROM THEIR WALLET (My Inspections); it is held until the visit and released to the agent (also if the requester does not attend). Refunded in full if the owner or CHS cancels or the requester cancels 12+ hours ahead; inside 12 hours it goes to the agent. A visit not paid for 2 hours before it is due lapses with nothing charged. A genuine 12-hour minimum notice is enforced by the database itself.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Property detail page — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Admin → Inspections (Owner/Buyer/Tenant domain)</t>
         </is>
@@ -4958,17 +5579,17 @@
           <t>Buyer/Tenant Readiness Score</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>A real questionnaire (timeline, funds ready, decision-maker) plus verification and inspection-attendance history — shown to owners, never a fee or gate.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Inspection booking form — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>N/A — computed live</t>
         </is>
@@ -4980,17 +5601,17 @@
           <t>Shortlet booking</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Booked request-first: the guest picks dates on the availability calendar and sends a request — nothing is charged. CHS passes it to the host, who confirms the dates are free; the guest then pays within a short window and the payment is held in escrow until check-in is confirmed. Real guest verification required. See section 16 for the full flow.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Property detail page → My Bookings — Buyer / Guest</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Bookings</t>
         </is>
@@ -5002,17 +5623,17 @@
           <t>Rent-to-Own</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Where offered, a real monthly amount counting toward eventual ownership, shown directly on the listing.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Property detail page — Buyer</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>N/A — set by owner at listing time</t>
         </is>
@@ -5024,17 +5645,17 @@
           <t>House Rules acknowledgment</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>A real, documented agreement a tenant acknowledges as part of their tenancy.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard, per tenancy</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>N/A — set by owner</t>
         </is>
@@ -5046,17 +5667,17 @@
           <t>Property Condition Report</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Documented and photographed at move-in — real evidence-based liability instead of a caution-fee guess.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Condition Report page — Tenant</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5068,17 +5689,17 @@
           <t>Formal Notices</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Real formal communications (e.g. rent reminders, lease notices) from owner/CHS, viewable and expandable.</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>N/A — sent by owner/CHS</t>
         </is>
@@ -5090,17 +5711,17 @@
           <t>Owner–tenant message thread</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>A real, direct messaging channel per tenancy.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard, per tenancy</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5112,17 +5733,17 @@
           <t>Raise a Dispute</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>A real, two-sided dispute process — CHS's internal resolution is the first step before arbitration or courts.</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard + Owner dashboard</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Admin → Disputes (Customer Care domain)</t>
         </is>
@@ -5134,17 +5755,17 @@
           <t>Talk to an Agent (Concierge)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>Describe a property need in free text or voice instead of using search filters — a real request CHS follows up on personally.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Bottom nav → Property request — Buyer / Tenant</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Admin → Concierge, within Owner/Buyer/Tenant domain</t>
         </is>
@@ -5156,17 +5777,17 @@
           <t>Urgent &amp; Emergency Sale browsing</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Real, discounted, time-boxed listings shown in a dedicated homepage row with the real deadline.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Homepage — Buyer</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>N/A — browsing only</t>
         </is>
@@ -5178,17 +5799,17 @@
           <t>Market data (average prices, demand trend)</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Real, genuine data (not placeholder figures) on current prices and search-driven demand patterns.</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Bottom nav → Average prices / Demand trend</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5200,17 +5821,17 @@
           <t>Engage CHS — buy a construction project</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Full request flow with real specifications, document checklist, two-way chat, and the Construction Roadmap tool.</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Engage CHS page — Buyer / Owner</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Admin → Engage CHS (Super Admin only)</t>
         </is>
@@ -5222,17 +5843,17 @@
           <t>Hotel, Event Centre, Hall, Car Park, Cinema &amp; Recreational/Sports booking</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>A real request-first booking flow — not a rental application — for any genuine guest venue, correctly categorized and commissioned: send a request (nothing charged), CHS relays it, the venue confirms, the guest pays within a short window. A business-lease “hire” listing (e.g. a filling station) correctly stays on the rental-application path instead.</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Property detail page → My Bookings — Buyer / Guest</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Admin → Shortlet/Hire Bookings</t>
         </is>
@@ -5244,17 +5865,17 @@
           <t>Auto-pay rent from a dedicated savings wallet</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>An optional, real toggle — rent pays itself the moment it's due from a separate Rent Savings balance, or stays fully manual if left off.</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard, per tenancy</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5266,17 +5887,17 @@
           <t>Rent held in real escrow</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Paid rent is not released to the landlord immediately. Held until the tenant files a genuinely clean move-in report, or 14 days pass with nothing raised — the same real protection a buyer's money gets. An open fault or a flagged report item pauses release for admin review.</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Tenant &amp; Owner dashboards, wallet — Tenant / Owner</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Admin → Escrow Oversight (Owner/Buyer/Tenant domain) — release early, or review a flagged hold</t>
         </is>
@@ -5288,17 +5909,17 @@
           <t>Subsequent-year rent — no repeat tenant commission</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>The system now genuinely knows a renewal from a first payment. From year two onward, the tenant pays CHS nothing further — only the landlord, at a real, reduced 3%. Shown live on both the tenant's and owner's rent countdown.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Tenant &amp; Owner dashboards, rent countdown</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic</t>
         </is>
@@ -5310,17 +5931,17 @@
           <t>Move-out condition report + real court affidavit</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>A genuine move-out counterpart to the existing move-in report, with a real, required court-issued affidavit upload — now actually visible to the landlord, which it never was before.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Condition Report page — Tenant; visible on Owner dashboard</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5332,17 +5953,17 @@
           <t>Non-renewal notice with a real message</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>A genuine optional message sent to the landlord along with the notice — previously a bare, wordless click.</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Tenant dashboard, per tenancy</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5354,17 +5975,17 @@
           <t>Real street address on every listing</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>A required, specific address (e.g. "House 12, Shagari Road") — not just a general neighborhood — visible on the tenant's own dashboard and usable for real fault/payment tracing.</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>List a property form; Tenant dashboard</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Admin analytics, traceable by real address</t>
         </is>
@@ -5384,10 +6005,10 @@
   <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5418,17 +6039,17 @@
           <t>List a property</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Photos, location, price, purpose, bedrooms, and special terms (rent-to-own, house rules). Starts unverified.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard → List a property</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Properties (Owner/Buyer/Tenant domain)</t>
         </is>
@@ -5440,17 +6061,17 @@
           <t>Property verification</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>CHS reviews every listing before it's publicly visible — the real meaning behind "CHS Verified."</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Properties (Owner/Buyer/Tenant domain)</t>
         </is>
@@ -5462,17 +6083,17 @@
           <t>Fixed-tier promotion (7/30/90-Day Boost)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>One-off paid tier, debited directly from the wallet.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Promote page, per listing</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5484,17 +6105,17 @@
           <t>Credit-based promotion (pause anytime)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Real, shared credit balance across every listing; each listing charged separately per real day it's on, based on real location/size cost. Real ranking (Category A–D + literal Top 10/20 position) against the same real local market.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Promote page, per listing</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic, database-driven</t>
         </is>
@@ -5506,17 +6127,17 @@
           <t>Urgent &amp; Emergency Sale activation</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Requires the listing already verified and owner ID-verified. Real original price, discount, and deadline shown to buyers.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard → 🚨 Urgent Sale</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Notified via general notifications on activation</t>
         </is>
@@ -5528,17 +6149,17 @@
           <t>Managing offers &amp; rental applications</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Real accept/reject decisions on real, CHS-screened offers and applications.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Admin → Sale Approvals / Applications</t>
         </is>
@@ -5550,17 +6171,17 @@
           <t>Inspection management + Readiness Score visibility</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>See each real requester's readiness score; mark real attendance/no-show after the scheduled time passes.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard, per property</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Admin → Inspections</t>
         </is>
@@ -5572,17 +6193,17 @@
           <t>Delegating to a Property Manager</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Hands maintenance and certain approvals to a registered Manager; reversible any time.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5594,17 +6215,17 @@
           <t>Property analytics</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Real view counts, inspection counts, and interest counts — not fixed placeholder numbers.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Analytics page, per listing</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5616,17 +6237,17 @@
           <t>Editing a live listing</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Real edits to an already-published property.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Edit listing page</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5638,17 +6259,17 @@
           <t>Engage CHS for a professional service</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Full Property Management, Sale Negotiation, Construction Monitoring, Project Management, Renovation — each with its own real terms and fee schedule.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Engage CHS page — Owner</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Admin → Engage CHS (Super Admin only)</t>
         </is>
@@ -5660,17 +6281,17 @@
           <t>Download verified sale documents</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>The actual, CHS-verified legal documents (Certificate of Occupancy, Deed of Assignment, etc.) genuinely downloadable by a paying buyer directly — previously only ever tracked as a physical-dispatch status with no real digital access.</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Property detail page, after payment — Buyer</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5682,17 +6303,17 @@
           <t>Accept an offer at negotiated terms, mid-chat</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>A real conversion point that didn't exist before — accept at a different final price than the original offer, with an optional condition (e.g. a payment deadline), directly from the ongoing negotiation.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard, per offer</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5712,10 +6333,10 @@
   <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5746,17 +6367,17 @@
           <t>Unique referral link</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>A real code (e.g. CHS-AG-0024) automatically attached to every property link generated — always opens the property directly on CHS.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5768,17 +6389,17 @@
           <t>Automatic commission attribution</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>If a referred visitor completes a real transaction on that property, CHS automatically attributes and credits the commission.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Referral fees (Agent Relations domain)</t>
         </is>
@@ -5790,17 +6411,17 @@
           <t>Real referral tracking (masked for privacy)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Real deal stage, earnings this month, and total earned — served from a privacy-conscious masked view.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Admin → Referral fees</t>
         </is>
@@ -5812,17 +6433,17 @@
           <t>Managing an agent-managed property's own commission</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>For a property under full agent authority, set your own real market rate (e.g. 10-15%) with the client — CHS charges the client nothing extra, taking a real, capped 3% only from your own earnings.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard, per managed property</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5834,17 +6455,17 @@
           <t>Per-owner commission rate — one real, standing rate</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>A genuine, editable rate per real owner relationship, not re-entered per property — reviewable and adjustable any time, applying automatically to every property you manage for that owner, including new ones.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard → Your Real Commission Rate Per Owner</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5856,17 +6477,17 @@
           <t>Digital remittance to an owner's wallet</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Rent collected in person, remitted straight into the real owner's wallet with your agreed commission auto-deducted — a real, permanent reference either side can point to.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard → Remit Collected Rent to an Owner</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Admin → Finance, real remittances table</t>
         </is>
@@ -5878,17 +6499,17 @@
           <t>A real tenant register</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Full biodata, property details, and a real auto-generated reference number (e.g. TEN-000001) for every tenant you manage — plus real ID and selfie verification.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>My Tenant Register page</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5900,17 +6521,17 @@
           <t>A real mini-admin — your own team</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Add real, separate staff accounts by phone number, assign a role, and see their genuine daily activity reports — the same kind of oversight CHS itself runs on.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard → Manage My Team</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5922,17 +6543,17 @@
           <t>Multiple linked bank accounts</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Up to 4 real, Paystack-verified bank accounts — a genuine business need for agents working across multiple banking relationships, unlike every other role which stays single-account.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Profile → Linked bank accounts</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5944,17 +6565,17 @@
           <t>Expenses &amp; income tracking</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Real salary, rent, transport, logistics, and commission income entries — a genuine net position, not just a spending log.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>My Expenses &amp; Income page</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5966,17 +6587,17 @@
           <t>My real activity report</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>A genuine, date-range (week/month/quarter) report of commission earned, deals closed, and tenancies managed.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Agent dashboard → Generate my activity report</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -5996,10 +6617,10 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6030,17 +6651,17 @@
           <t>Delegated property management</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Owners can delegate specific properties; maintenance and certain approvals route to the manager directly.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Manager dashboard</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -6052,17 +6673,17 @@
           <t>Management termination</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>An owner can reverse delegation any time, handing responsibilities back.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Owner dashboard (trigger) / Manager dashboard (effect)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -6074,17 +6695,17 @@
           <t>Posting a maintenance job for quotation</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Real job posts that verified artisans can quote on, ranked by a transparent rating/reliability/experience/equipment formula.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Manager dashboard</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Admin → Maintenance (Artisan/Developer/PM/Vendor domain)</t>
         </is>
@@ -6096,17 +6717,17 @@
           <t>Rating an artisan</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Real, genuine ratings after a completed job.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Manager dashboard, per completed job</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -6118,17 +6739,17 @@
           <t>Owner-occupier support in estates</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Register a real occupant who owns their unit outright (no tenancy) alongside genuine tenants in the same estate — correctly counted in occupancy and included in service-charge billing.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Manager dashboard, per estate unit</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -6140,17 +6761,17 @@
           <t>Per-owner commission rate, digital remittance, tenant register, mini-admin team, multiple bank accounts, expenses tracking</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Every real business tool built for agents this round applies identically to managers — the same standing per-owner rate, the same digital remittance, the same tenant register and team system.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Manager dashboard — same real pages as Agent</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -6162,17 +6783,17 @@
           <t>My real activity report — across all my estates</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>A genuine, date-range report of new tenancies, service charges billed and collected, and maintenance resolved across every estate you manage.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>My Estates page → Generate my activity report</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -6192,10 +6813,10 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6226,17 +6847,17 @@
           <t>Developer registration &amp; review</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>A real application reviewed by CHS before projects go live.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Register / Developer dashboard</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Developers (Artisan/Developer/PM/Vendor domain)</t>
         </is>
@@ -6248,17 +6869,17 @@
           <t>Listing development projects</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Estates, instalment plans, and investment plans.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Developer dashboard</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Developers</t>
         </is>
@@ -6278,10 +6899,10 @@
   <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6312,17 +6933,17 @@
           <t>Vendor registration &amp; verification</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Three clearly separate sign-up paths: ARTISAN (trades such as plumbing and electrical), VENDOR (sells goods: Interior Design, Furniture, Bedding &amp; Textiles, Electronics &amp; Home Appliances, Kitchen, Building Materials) and SERVICE PROVIDER (Security, Cleaning, Fumigation &amp; Pest Control, Facilities Maintenance). Each shows only its own categories. State and LGA are dropdowns (the LGA list follows the chosen state), a service provider ticks the states it covers, and required fields are marked. Every registration alerts the responsible admins automatically (bell notification, a marker on the Vendors / Artisans tab), and CHS reviews it under Verification before the listings go public.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Become a Vendor / Vendor dashboard</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Vendors (Artisan/Developer/PM/Vendor domain)</t>
         </is>
@@ -6334,17 +6955,17 @@
           <t>Listing products &amp; bundles</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Real materials/services catalog, browsable by category on the Marketplace.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Vendor dashboard (list) + Marketplace page (browse)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -6356,17 +6977,17 @@
           <t>Service quote requests</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Real incoming requests for a quote on a specific service.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Vendor dashboard</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -6378,17 +6999,17 @@
           <t>Referral fee tracking</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Real fees on deals connected through the Marketplace.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Vendor dashboard</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Admin → Referral fees</t>
         </is>
@@ -6408,10 +7029,10 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6442,17 +7063,17 @@
           <t>Artisan registration &amp; verification</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Real trades, years of experience, certification, and equipment tier (with photo/receipt backing) — reviewed before quoting is allowed.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Become an Artisan / Artisan dashboard</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Artisans (Artisan/Developer/PM/Vendor domain)</t>
         </is>
@@ -6464,17 +7085,17 @@
           <t>Quoting on maintenance jobs</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Real quotes ranked by a transparent formula: rating/reliability first, experience second, equipment third.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Artisan dashboard</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Maintenance</t>
         </is>
@@ -6486,17 +7107,17 @@
           <t>Full-management job priority</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>For any property under full CHS management, maintenance work goes first and exclusively to verified CHS Maintenance Agents.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Automatic — Artisan</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>N/A — automatic</t>
         </is>
@@ -6508,17 +7129,17 @@
           <t>Job dispute resolution</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Either the artisan or the client can raise a genuine, two-sided dispute about a completed job.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Artisan dashboard</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Admin → Disputes</t>
         </is>
@@ -6530,17 +7151,17 @@
           <t>Ratings received</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Real, visible rating history.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Artisan dashboard</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>N/A — self-service</t>
         </is>
@@ -6560,10 +7181,10 @@
   <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6594,17 +7215,17 @@
           <t>Super Admin role</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>One real account, practically involved in every part of the platform — handles Finance and Engage CHS directly, and ratifies every sub-admin's high-stakes decision.</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Admin dashboard</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview</t>
         </is>
@@ -6616,17 +7237,17 @@
           <t>Five real sub-admin domains</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Customer Care, Registration &amp; Setup, Owner/Buyer/Tenant, Agent Relations, Artisan/Developer/PM/Vendor — each sub-admin only sees and acts within their own domain, enforced at the database level.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Admin dashboard, tab-gated per domain</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview → Assign an admin role</t>
         </is>
@@ -6638,17 +7259,17 @@
           <t>Code-based admin login approval</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>A sub-admin's correct password alone isn't enough — a real code is generated and sent to the Super Admin, who must approve that specific login.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Sub-admin login flow</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview — pending login approvals</t>
         </is>
@@ -6660,17 +7281,17 @@
           <t>High-stakes approval queue</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Routine sub-admin actions apply immediately; financial and verification decisions are held pending real Super Admin sign-off.</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Admin dashboard, across relevant tabs</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview — pending sub-admin actions</t>
         </is>
@@ -6682,17 +7303,17 @@
           <t>Trace an Account</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Search any real user by phone/email/name and see their full wallet balance + transaction history, promotion credits + active promotions, construction roadmap unlocks, linked bank account, and Engage CHS requests — all in one place. The real fix for resolving a support issue ("I paid but nothing happened") the way a phone network traces an account from just a phone number.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Admin → 🔎 Trace an Account (Super Admin only)</t>
         </is>
@@ -6704,17 +7325,17 @@
           <t>Sub-admin action history</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>A real, permanent audit log of every resolved sub-admin request — previously, once approved or rejected, a request simply vanished with no record.</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview → View sub-admin action history</t>
         </is>
@@ -6726,17 +7347,17 @@
           <t>Pre-launch admin test mode</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Super Admin can preview any real dashboard using their own account, never a real user's data, with a visible banner the whole time.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>N/A — testing tool</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview → Switch role for testing</t>
         </is>
@@ -6748,17 +7369,17 @@
           <t>Finance</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Search any real user's wallet, view all three real balances, freeze/unfreeze.</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Admin → Finance</t>
         </is>
@@ -6770,17 +7391,17 @@
           <t>Sale Approvals</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>The real checkpoint between an accepted offer and money moving to escrow.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Admin → Sale Approvals</t>
         </is>
@@ -6792,17 +7413,17 @@
           <t>Face Verification (Liveness)</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Real human review of each real-time capture.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Admin → Face Verification</t>
         </is>
@@ -6814,17 +7435,17 @@
           <t>Registrations</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Approve or reject new real accounts.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Admin → Registrations</t>
         </is>
@@ -6836,17 +7457,17 @@
           <t>Applications</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Real rental application review before an owner ever sees it.</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Admin → Applications</t>
         </is>
@@ -6858,17 +7479,17 @@
           <t>Properties</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Real listing verification before it's publicly visible.</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Admin → Properties</t>
         </is>
@@ -6880,17 +7501,17 @@
           <t>Disputes</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Real, two-sided dispute resolution across tenancies and artisan jobs.</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Admin → Disputes</t>
         </is>
@@ -6902,17 +7523,17 @@
           <t>Feedback</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>General platform suggestions/complaints, not tied to a specific transaction.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Admin → Feedback</t>
         </is>
@@ -6924,17 +7545,17 @@
           <t>Engage CHS</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Real professional-service requests: specifications, document checklist, two-way chat, roadmap access — Super Admin only, per direct instruction.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Admin → Engage CHS</t>
         </is>
@@ -6946,17 +7567,17 @@
           <t>Vendors</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Real marketplace vendor verification.</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Admin → Vendors</t>
         </is>
@@ -6968,17 +7589,17 @@
           <t>Referral fees</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Real agent/vendor commission tracking and payout, routed through the approval queue.</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Admin → Referral fees</t>
         </is>
@@ -6990,17 +7611,17 @@
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Real fault report routing to the right artisan/manager.</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Admin → Maintenance</t>
         </is>
@@ -7012,17 +7633,17 @@
           <t>Artisans</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Real trade/equipment verification before an artisan can quote.</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Admin → Artisans</t>
         </is>
@@ -7034,17 +7655,17 @@
           <t>Inspections</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>Real upcoming inspection oversight across the whole platform.</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Admin → Inspections</t>
         </is>
@@ -7056,17 +7677,17 @@
           <t>Developers</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Real developer application review.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Admin → Developers</t>
         </is>
@@ -7078,17 +7699,17 @@
           <t>Real, date-range analytics report</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>A genuine, filterable (today/week/month/quarter) record of properties sold, new tenancies, shortlet bookings, new listings, new users, and total commission revenue by transaction type — not just a live, un-datable snapshot.</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Admin → Analytics</t>
         </is>
@@ -7100,17 +7721,17 @@
           <t>Suspend a real account, with a genuine appeal process</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Suspend by phone number with a required, documented reason; a real appeal queue to approve (reinstate) or deny.</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview</t>
         </is>
@@ -7122,17 +7743,17 @@
           <t>CHS staff daily report</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Any real internal admin staff member can submit their own daily activity report, visible to the super admin.</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>N/A — admin only</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview → Submit My Daily Report</t>
         </is>
@@ -7144,17 +7765,17 @@
           <t>Critical data-protection fixes</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>A direct security audit found and closed a real, proven exposure — any logged-in user could previously read another user's NIN, phone, and ID documents. Fixed at both the database and file-storage level, re-verified after the fix.</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>N/A — platform-wide</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>See the separate Security Audit report</t>
         </is>
@@ -7166,17 +7787,17 @@
           <t>Missing database indexes added</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Dozens of real foreign-key columns had no index — invisible at small scale, a genuine slowdown waiting to happen as real data grows. Added across every high-traffic table.</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>N/A — platform-wide</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>See the separate Scalability Assessment report</t>
         </is>
@@ -7188,17 +7809,17 @@
           <t>Real, editable Contact Us details</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Four real, distinct contact emails (Support, Inquiry, Engage CHS, Admin) and two real phone numbers — genuinely admin-editable at any time, not hardcoded into the app.</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>More menu → Contact us — every role</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Admin → Overview → Edit Real Contact Details</t>
         </is>

--- a/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
+++ b/chs-v2/public/documents/CHS_FEATURE_CATALOG_SEGMENTED.xlsx
@@ -4972,7 +4972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5380,20 +5380,42 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>Management of hotels, event centres and open venues</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>A hotel, lodge, event centre, open field, stadium or similar venue can be handed to CHS from the Host page. Required: proof of ownership (plus co-owner consent, power of attorney or company papers as the capacity needs), the operating permit or licence stating the licensed capacity, public liability insurance and, for event and open venues, a fire safety certificate. The database refuses the request without them. An admin checks the documents and records the agreed base fee, incentive fee and term before approval. On approval the property carries the Managed &amp; Advertised stamp and its bookings carry no host-side commission (the management fee replaces it); the price shown to guests agrees.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Host page; Owner page</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Admin → CHS stamp (approve; tick documents checked; record fee and term)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>VAT recording on CHS fees</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>OFF by default. When a super admin switches it on (a tax ID is required), VAT is treated as included in each CHS fee collected: guest and host amounts do not change. Each fee gets a ledger entry with its VAT part; a refund reverses it. Monthly report with CSV: fees collected, VAT to remit, fee excluding VAT, VAT reversed. Fees collected before the switch are not back-filled. Not a tax filing; the accountant confirms rate and registration.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Admin → Financial → VAT on CHS fees</t>
         </is>
